--- a/premise/data/additional_inventories/lci-carbon-capture.xlsx
+++ b/premise/data/additional_inventories/lci-carbon-capture.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/Github/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA28BFAD-10F0-114B-A8B4-C331D85F0120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4F2CD5-055C-3F46-AA42-8D857D2E85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34920" yWindow="80" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="22980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DAC" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DAC!$A$1:$V$621</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DAC!$A$1:$V$620</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2642" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2637" uniqueCount="321">
   <si>
     <t>Activity</t>
   </si>
@@ -629,9 +629,6 @@
   </si>
   <si>
     <t>concrete, normal strength</t>
-  </si>
-  <si>
-    <t>market for spent anion exchange resin from potable water production</t>
   </si>
   <si>
     <t>Originally 3.7 MJ, without heat recovery. 0.4 MJ using heat from teh MSWI plant. However, when doing so, 40% of teh heat is lost and cannot be redistributed to the heating district system. Hence, we add this loss to the amount of external heat needed.</t>
@@ -1012,14 +1009,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.0E+00"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="0.0E+00"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ * #,##0.000_ ;_ * \-#,##0.000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="171" formatCode="0.00000"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -1139,13 +1136,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1155,29 +1152,29 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1187,9 +1184,11 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1505,7 +1504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V658"/>
+  <dimension ref="A1:V657"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
@@ -1538,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -1554,7 +1553,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -1634,10 +1633,10 @@
         <v>173</v>
       </c>
       <c r="K12" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>182</v>
@@ -1661,7 +1660,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -1882,7 +1881,7 @@
         <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -1900,7 +1899,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B22">
         <v>6.28</v>
@@ -1918,7 +1917,7 @@
         <v>162</v>
       </c>
       <c r="H22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -1959,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -1975,7 +1974,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -2055,10 +2054,10 @@
         <v>173</v>
       </c>
       <c r="K34" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L34" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>182</v>
@@ -2066,7 +2065,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -2081,7 +2080,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -2302,7 +2301,7 @@
         <v>78</v>
       </c>
       <c r="H43" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I43">
         <v>5</v>
@@ -2320,7 +2319,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B44">
         <v>6.28</v>
@@ -2338,7 +2337,7 @@
         <v>162</v>
       </c>
       <c r="H44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -2402,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
@@ -2418,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
@@ -2498,10 +2497,10 @@
         <v>173</v>
       </c>
       <c r="K57" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L57" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L57" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>182</v>
@@ -2509,7 +2508,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -2524,7 +2523,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
@@ -2745,7 +2744,7 @@
         <v>78</v>
       </c>
       <c r="H66" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I66">
         <v>5</v>
@@ -2781,7 +2780,7 @@
         <v>188</v>
       </c>
       <c r="H67" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I67">
         <v>5</v>
@@ -2822,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.2">
@@ -2838,7 +2837,7 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.2">
@@ -2918,10 +2917,10 @@
         <v>173</v>
       </c>
       <c r="K79" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L79" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L79" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>182</v>
@@ -2929,7 +2928,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -2944,7 +2943,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.2">
@@ -3165,7 +3164,7 @@
         <v>78</v>
       </c>
       <c r="H88" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I88">
         <v>5</v>
@@ -3201,7 +3200,7 @@
         <v>188</v>
       </c>
       <c r="H89" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I89">
         <v>5</v>
@@ -3265,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
@@ -3281,7 +3280,7 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
@@ -3361,10 +3360,10 @@
         <v>173</v>
       </c>
       <c r="K102" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L102" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L102" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M102" s="5" t="s">
         <v>182</v>
@@ -3372,7 +3371,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -3387,7 +3386,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.2">
@@ -3608,7 +3607,7 @@
         <v>78</v>
       </c>
       <c r="H111" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I111">
         <v>5</v>
@@ -3645,7 +3644,7 @@
         <v>78</v>
       </c>
       <c r="H112" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I112">
         <v>5</v>
@@ -3688,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.2">
@@ -3704,7 +3703,7 @@
         <v>2</v>
       </c>
       <c r="B117" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.2">
@@ -3784,10 +3783,10 @@
         <v>173</v>
       </c>
       <c r="K124" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L124" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L124" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M124" s="5" t="s">
         <v>182</v>
@@ -3795,7 +3794,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -3810,7 +3809,7 @@
         <v>15</v>
       </c>
       <c r="G125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.2">
@@ -4031,7 +4030,7 @@
         <v>78</v>
       </c>
       <c r="H133" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I133">
         <v>5</v>
@@ -4068,7 +4067,7 @@
         <v>78</v>
       </c>
       <c r="H134" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I134">
         <v>5</v>
@@ -4182,7 +4181,7 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4645,65 +4644,65 @@
     </row>
     <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B166">
         <f>78380*20</f>
         <v>1567600</v>
       </c>
       <c r="D166" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E166" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F166" t="s">
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B167">
         <f>78380</f>
         <v>78380</v>
       </c>
       <c r="D167" t="s">
+        <v>204</v>
+      </c>
+      <c r="E167" t="s">
         <v>205</v>
-      </c>
-      <c r="E167" t="s">
-        <v>206</v>
       </c>
       <c r="F167" t="s">
         <v>20</v>
       </c>
       <c r="H167" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B168">
         <f>78380</f>
         <v>78380</v>
       </c>
       <c r="D168" t="s">
+        <v>204</v>
+      </c>
+      <c r="E168" t="s">
         <v>205</v>
-      </c>
-      <c r="E168" t="s">
-        <v>206</v>
       </c>
       <c r="F168" t="s">
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="169" spans="1:19" ht="16" x14ac:dyDescent="0.2">
@@ -5005,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="191" spans="1:19" x14ac:dyDescent="0.2">
@@ -5021,7 +5020,7 @@
         <v>2</v>
       </c>
       <c r="B192" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.2">
@@ -5101,10 +5100,10 @@
         <v>173</v>
       </c>
       <c r="K199" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L199" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L199" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M199" s="5" t="s">
         <v>182</v>
@@ -5112,7 +5111,7 @@
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -5127,7 +5126,7 @@
         <v>15</v>
       </c>
       <c r="G200" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="201" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5266,7 +5265,7 @@
         <v>78</v>
       </c>
       <c r="H204" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I204">
         <v>5</v>
@@ -5283,7 +5282,7 @@
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B205">
         <v>5.4</v>
@@ -5301,7 +5300,7 @@
         <v>162</v>
       </c>
       <c r="H205" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I205">
         <v>5</v>
@@ -5341,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.2">
@@ -5357,7 +5356,7 @@
         <v>2</v>
       </c>
       <c r="B210" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.2">
@@ -5389,7 +5388,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.2">
@@ -5397,7 +5396,7 @@
         <v>18</v>
       </c>
       <c r="B215" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5437,10 +5436,10 @@
         <v>173</v>
       </c>
       <c r="K217" t="s">
+        <v>215</v>
+      </c>
+      <c r="L217" t="s">
         <v>216</v>
-      </c>
-      <c r="L217" t="s">
-        <v>217</v>
       </c>
       <c r="M217" s="5" t="s">
         <v>182</v>
@@ -5448,7 +5447,7 @@
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -5463,7 +5462,7 @@
         <v>15</v>
       </c>
       <c r="G218" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5602,7 +5601,7 @@
         <v>78</v>
       </c>
       <c r="H222" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I222">
         <v>5</v>
@@ -5619,7 +5618,7 @@
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B223">
         <v>5.4</v>
@@ -5637,7 +5636,7 @@
         <v>162</v>
       </c>
       <c r="H223" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I223">
         <v>5</v>
@@ -5700,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.2">
@@ -5716,7 +5715,7 @@
         <v>2</v>
       </c>
       <c r="B229" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.2">
@@ -5796,10 +5795,10 @@
         <v>173</v>
       </c>
       <c r="K236" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L236" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L236" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M236" s="5" t="s">
         <v>182</v>
@@ -5807,7 +5806,7 @@
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -5822,7 +5821,7 @@
         <v>15</v>
       </c>
       <c r="G237" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -5961,7 +5960,7 @@
         <v>78</v>
       </c>
       <c r="H241" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I241">
         <v>5</v>
@@ -5978,7 +5977,7 @@
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B242">
         <v>5.4</v>
@@ -5993,10 +5992,10 @@
         <v>16</v>
       </c>
       <c r="G242" t="s">
+        <v>250</v>
+      </c>
+      <c r="H242" t="s">
         <v>251</v>
-      </c>
-      <c r="H242" t="s">
-        <v>252</v>
       </c>
       <c r="I242">
         <v>5</v>
@@ -6036,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.2">
@@ -6052,7 +6051,7 @@
         <v>2</v>
       </c>
       <c r="B247" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.2">
@@ -6084,7 +6083,7 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.2">
@@ -6092,7 +6091,7 @@
         <v>18</v>
       </c>
       <c r="B252" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6132,10 +6131,10 @@
         <v>173</v>
       </c>
       <c r="K254" t="s">
+        <v>215</v>
+      </c>
+      <c r="L254" t="s">
         <v>216</v>
-      </c>
-      <c r="L254" t="s">
-        <v>217</v>
       </c>
       <c r="M254" s="5" t="s">
         <v>182</v>
@@ -6143,7 +6142,7 @@
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -6158,7 +6157,7 @@
         <v>15</v>
       </c>
       <c r="G255" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="256" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6297,7 +6296,7 @@
         <v>78</v>
       </c>
       <c r="H259" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I259">
         <v>5</v>
@@ -6314,7 +6313,7 @@
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B260">
         <v>5.4</v>
@@ -6329,10 +6328,10 @@
         <v>16</v>
       </c>
       <c r="G260" t="s">
+        <v>250</v>
+      </c>
+      <c r="H260" t="s">
         <v>251</v>
-      </c>
-      <c r="H260" t="s">
-        <v>252</v>
       </c>
       <c r="I260">
         <v>5</v>
@@ -6395,7 +6394,7 @@
         <v>0</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.2">
@@ -6411,7 +6410,7 @@
         <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.2">
@@ -6491,10 +6490,10 @@
         <v>173</v>
       </c>
       <c r="K273" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L273" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L273" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M273" s="5" t="s">
         <v>182</v>
@@ -6502,7 +6501,7 @@
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -6517,7 +6516,7 @@
         <v>15</v>
       </c>
       <c r="G274" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6656,7 +6655,7 @@
         <v>78</v>
       </c>
       <c r="H278" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I278">
         <v>5</v>
@@ -6691,7 +6690,7 @@
         <v>188</v>
       </c>
       <c r="H279" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I279">
         <v>5</v>
@@ -6731,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.2">
@@ -6747,7 +6746,7 @@
         <v>2</v>
       </c>
       <c r="B284" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.2">
@@ -6779,7 +6778,7 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.2">
@@ -6787,7 +6786,7 @@
         <v>18</v>
       </c>
       <c r="B289" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6827,10 +6826,10 @@
         <v>173</v>
       </c>
       <c r="K291" t="s">
+        <v>215</v>
+      </c>
+      <c r="L291" t="s">
         <v>216</v>
-      </c>
-      <c r="L291" t="s">
-        <v>217</v>
       </c>
       <c r="M291" s="5" t="s">
         <v>182</v>
@@ -6838,7 +6837,7 @@
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -6853,7 +6852,7 @@
         <v>15</v>
       </c>
       <c r="G292" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="293" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -6992,7 +6991,7 @@
         <v>78</v>
       </c>
       <c r="H296" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I296">
         <v>5</v>
@@ -7027,7 +7026,7 @@
         <v>188</v>
       </c>
       <c r="H297" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I297">
         <v>5</v>
@@ -7090,7 +7089,7 @@
         <v>0</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.2">
@@ -7106,7 +7105,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.2">
@@ -7186,10 +7185,10 @@
         <v>173</v>
       </c>
       <c r="K310" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L310" s="5" t="s">
         <v>216</v>
-      </c>
-      <c r="L310" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="M310" s="5" t="s">
         <v>182</v>
@@ -7197,7 +7196,7 @@
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B311">
         <v>1</v>
@@ -7212,7 +7211,7 @@
         <v>15</v>
       </c>
       <c r="G311" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -7351,7 +7350,7 @@
         <v>78</v>
       </c>
       <c r="H315" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I315">
         <v>5</v>
@@ -7387,7 +7386,7 @@
         <v>78</v>
       </c>
       <c r="H316" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I316">
         <v>5</v>
@@ -7430,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.2">
@@ -7446,7 +7445,7 @@
         <v>2</v>
       </c>
       <c r="B321" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.2">
@@ -7478,7 +7477,7 @@
         <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.2">
@@ -7486,7 +7485,7 @@
         <v>18</v>
       </c>
       <c r="B326" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="327" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -7526,10 +7525,10 @@
         <v>173</v>
       </c>
       <c r="K328" t="s">
+        <v>215</v>
+      </c>
+      <c r="L328" t="s">
         <v>216</v>
-      </c>
-      <c r="L328" t="s">
-        <v>217</v>
       </c>
       <c r="M328" s="5" t="s">
         <v>182</v>
@@ -7537,7 +7536,7 @@
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B329">
         <v>1</v>
@@ -7552,7 +7551,7 @@
         <v>15</v>
       </c>
       <c r="G329" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="330" spans="1:13" ht="16" x14ac:dyDescent="0.2">
@@ -7691,7 +7690,7 @@
         <v>78</v>
       </c>
       <c r="H333" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I333">
         <v>5</v>
@@ -7727,7 +7726,7 @@
         <v>78</v>
       </c>
       <c r="H334" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I334">
         <v>5</v>
@@ -7841,15 +7840,15 @@
         <v>9</v>
       </c>
       <c r="B344" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>18</v>
       </c>
-      <c r="B345" t="s">
-        <v>222</v>
+      <c r="B345" s="41" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="346" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -7907,7 +7906,7 @@
       <c r="A349" t="s">
         <v>194</v>
       </c>
-      <c r="B349">
+      <c r="B349" s="40">
         <v>8000</v>
       </c>
       <c r="C349" t="s">
@@ -7930,7 +7929,7 @@
       <c r="A350" t="s">
         <v>103</v>
       </c>
-      <c r="B350">
+      <c r="B350" s="40">
         <v>942000</v>
       </c>
       <c r="C350" t="s">
@@ -7953,7 +7952,7 @@
       <c r="A351" t="s">
         <v>194</v>
       </c>
-      <c r="B351">
+      <c r="B351" s="40">
         <v>6000</v>
       </c>
       <c r="C351" t="s">
@@ -7976,7 +7975,7 @@
       <c r="A352" t="s">
         <v>103</v>
       </c>
-      <c r="B352">
+      <c r="B352" s="40">
         <v>548000.00000000012</v>
       </c>
       <c r="C352" t="s">
@@ -7999,7 +7998,7 @@
       <c r="A353" t="s">
         <v>42</v>
       </c>
-      <c r="B353">
+      <c r="B353" s="40">
         <v>120000</v>
       </c>
       <c r="C353" t="s">
@@ -8022,7 +8021,7 @@
       <c r="A354" t="s">
         <v>115</v>
       </c>
-      <c r="B354">
+      <c r="B354" s="40">
         <v>16000</v>
       </c>
       <c r="C354" t="s">
@@ -8045,7 +8044,7 @@
       <c r="A355" t="s">
         <v>59</v>
       </c>
-      <c r="B355">
+      <c r="B355" s="40">
         <v>276000.00000000006</v>
       </c>
       <c r="C355" t="s">
@@ -8068,7 +8067,7 @@
       <c r="A356" t="s">
         <v>43</v>
       </c>
-      <c r="B356">
+      <c r="B356" s="40">
         <v>224000</v>
       </c>
       <c r="C356" t="s">
@@ -8091,7 +8090,7 @@
       <c r="A357" t="s">
         <v>115</v>
       </c>
-      <c r="B357">
+      <c r="B357" s="40">
         <v>10000</v>
       </c>
       <c r="C357" t="s">
@@ -8114,7 +8113,7 @@
       <c r="A358" t="s">
         <v>116</v>
       </c>
-      <c r="B358">
+      <c r="B358" s="40">
         <v>12000</v>
       </c>
       <c r="C358" t="s">
@@ -8137,7 +8136,7 @@
       <c r="A359" t="s">
         <v>152</v>
       </c>
-      <c r="B359">
+      <c r="B359" s="40">
         <v>10000</v>
       </c>
       <c r="C359" t="s">
@@ -8160,7 +8159,7 @@
       <c r="A360" t="s">
         <v>58</v>
       </c>
-      <c r="B360">
+      <c r="B360" s="40">
         <v>160000</v>
       </c>
       <c r="C360" t="s">
@@ -8183,7 +8182,7 @@
       <c r="A361" t="s">
         <v>117</v>
       </c>
-      <c r="B361">
+      <c r="B361" s="40">
         <v>10000</v>
       </c>
       <c r="C361" t="s">
@@ -8206,7 +8205,7 @@
       <c r="A362" t="s">
         <v>43</v>
       </c>
-      <c r="B362">
+      <c r="B362" s="40">
         <v>338000</v>
       </c>
       <c r="C362" t="s">
@@ -8229,7 +8228,7 @@
       <c r="A363" t="s">
         <v>42</v>
       </c>
-      <c r="B363">
+      <c r="B363" s="40">
         <v>28000</v>
       </c>
       <c r="C363" t="s">
@@ -8252,7 +8251,7 @@
       <c r="A364" t="s">
         <v>121</v>
       </c>
-      <c r="B364">
+      <c r="B364" s="40">
         <v>94000</v>
       </c>
       <c r="C364" t="s">
@@ -8275,7 +8274,7 @@
       <c r="A365" t="s">
         <v>116</v>
       </c>
-      <c r="B365">
+      <c r="B365" s="40">
         <v>10000</v>
       </c>
       <c r="C365" t="s">
@@ -8298,7 +8297,7 @@
       <c r="A366" t="s">
         <v>152</v>
       </c>
-      <c r="B366">
+      <c r="B366" s="40">
         <v>10000</v>
       </c>
       <c r="C366" t="s">
@@ -8321,7 +8320,7 @@
       <c r="A367" t="s">
         <v>43</v>
       </c>
-      <c r="B367">
+      <c r="B367" s="40">
         <v>22000</v>
       </c>
       <c r="C367" t="s">
@@ -8344,7 +8343,7 @@
       <c r="A368" t="s">
         <v>42</v>
       </c>
-      <c r="B368">
+      <c r="B368" s="40">
         <v>12000</v>
       </c>
       <c r="C368" t="s">
@@ -8365,65 +8364,65 @@
     </row>
     <row r="369" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B369">
         <f>7838*20</f>
         <v>156760</v>
       </c>
       <c r="D369" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E369" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F369" t="s">
         <v>20</v>
       </c>
       <c r="H369" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="370" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B370">
         <f>7838</f>
         <v>7838</v>
       </c>
       <c r="D370" t="s">
+        <v>204</v>
+      </c>
+      <c r="E370" t="s">
         <v>205</v>
-      </c>
-      <c r="E370" t="s">
-        <v>206</v>
       </c>
       <c r="F370" t="s">
         <v>20</v>
       </c>
       <c r="H370" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="371" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B371">
         <f>7838</f>
         <v>7838</v>
       </c>
       <c r="D371" t="s">
+        <v>204</v>
+      </c>
+      <c r="E371" t="s">
         <v>205</v>
-      </c>
-      <c r="E371" t="s">
-        <v>206</v>
       </c>
       <c r="F371" t="s">
         <v>20</v>
       </c>
       <c r="H371" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="372" spans="1:19" x14ac:dyDescent="0.2">
@@ -8490,7 +8489,7 @@
         <v>18</v>
       </c>
       <c r="B380" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="381" spans="1:19" ht="16" x14ac:dyDescent="0.2">
@@ -8548,8 +8547,9 @@
       <c r="A384" t="s">
         <v>65</v>
       </c>
-      <c r="B384">
-        <v>-29400000</v>
+      <c r="B384" s="11">
+        <f>-1*(B349+B351)*2200</f>
+        <v>-30800000</v>
       </c>
       <c r="C384" t="s">
         <v>131</v>
@@ -8557,6 +8557,7 @@
       <c r="D384" t="s">
         <v>6</v>
       </c>
+      <c r="E384" s="11"/>
       <c r="F384" t="s">
         <v>16</v>
       </c>
@@ -8571,7 +8572,8 @@
         <v>66</v>
       </c>
       <c r="B385">
-        <v>-2140000</v>
+        <f>-1*(B350+B352+B353+B355+B362+B363+B367+B368)</f>
+        <v>-2286000</v>
       </c>
       <c r="C385" t="s">
         <v>21</v>
@@ -8593,6 +8595,7 @@
         <v>67</v>
       </c>
       <c r="B386">
+        <f>-1*(B358+B364+B365)</f>
         <v>-116000</v>
       </c>
       <c r="C386" t="s">
@@ -8615,7 +8618,8 @@
         <v>72</v>
       </c>
       <c r="B387">
-        <v>-143999.99999999997</v>
+        <f>-1*(B360)</f>
+        <v>-160000</v>
       </c>
       <c r="C387" t="s">
         <v>8</v>
@@ -8632,13 +8636,14 @@
     </row>
     <row r="388" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="B388">
-        <v>-6000000</v>
+        <f>-1*(B359+B366)</f>
+        <v>-20000</v>
       </c>
       <c r="C388" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="D388" t="s">
         <v>6</v>
@@ -8647,15 +8652,16 @@
         <v>16</v>
       </c>
       <c r="G388" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
     </row>
     <row r="389" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B389">
-        <v>-20000</v>
+        <f>-1*(B357+B354)</f>
+        <v>-26000</v>
       </c>
       <c r="C389" t="s">
         <v>131</v>
@@ -8667,133 +8673,133 @@
         <v>16</v>
       </c>
       <c r="G389" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A390" t="s">
-        <v>130</v>
-      </c>
-      <c r="B390">
-        <v>-26000</v>
-      </c>
-      <c r="C390" t="s">
-        <v>131</v>
-      </c>
-      <c r="D390" t="s">
-        <v>6</v>
-      </c>
-      <c r="F390" t="s">
-        <v>16</v>
-      </c>
-      <c r="G390" t="s">
         <v>150</v>
       </c>
     </row>
+    <row r="390" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="G390" s="7"/>
+    </row>
     <row r="391" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="G391" s="7"/>
-    </row>
-    <row r="392" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A392" s="1" t="s">
+      <c r="A391" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B392" s="1" t="s">
+      <c r="B391" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A392" t="s">
+        <v>1</v>
+      </c>
+      <c r="B392">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>1</v>
-      </c>
-      <c r="B393">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="394" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>2</v>
-      </c>
-      <c r="B394" s="7" t="s">
-        <v>80</v>
+        <v>3</v>
+      </c>
+      <c r="B394" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="395" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B395" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="396" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B396" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B397" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
     </row>
     <row r="398" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
+        <v>18</v>
+      </c>
+      <c r="B398" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A399" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A400" t="s">
+        <v>11</v>
+      </c>
+      <c r="B400" t="s">
+        <v>12</v>
+      </c>
+      <c r="C400" t="s">
+        <v>7</v>
+      </c>
+      <c r="D400" t="s">
+        <v>5</v>
+      </c>
+      <c r="E400" t="s">
+        <v>13</v>
+      </c>
+      <c r="F400" t="s">
+        <v>3</v>
+      </c>
+      <c r="G400" t="s">
+        <v>2</v>
+      </c>
+      <c r="H400" t="s">
         <v>9</v>
       </c>
-      <c r="B398" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
-        <v>18</v>
-      </c>
-      <c r="B399" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="400" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A400" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="401" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>11</v>
-      </c>
-      <c r="B401" t="s">
-        <v>12</v>
+        <v>79</v>
+      </c>
+      <c r="B401">
+        <v>1</v>
       </c>
       <c r="C401" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D401" t="s">
-        <v>5</v>
-      </c>
-      <c r="E401" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F401" t="s">
-        <v>3</v>
-      </c>
-      <c r="G401" t="s">
-        <v>2</v>
-      </c>
-      <c r="H401" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="G401" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="402" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="B402">
-        <v>1</v>
+        <v>0.36</v>
       </c>
       <c r="C402" t="s">
         <v>8</v>
@@ -8802,227 +8808,241 @@
         <v>6</v>
       </c>
       <c r="F402" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G402" s="7" t="s">
-        <v>80</v>
+        <v>212</v>
+      </c>
+      <c r="H402" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="403" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
+        <v>217</v>
+      </c>
+      <c r="B403">
+        <v>0.64</v>
+      </c>
+      <c r="C403" t="s">
+        <v>8</v>
+      </c>
+      <c r="D403" t="s">
+        <v>6</v>
+      </c>
+      <c r="F403" t="s">
+        <v>16</v>
+      </c>
+      <c r="G403" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H403" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A404" t="s">
+        <v>25</v>
+      </c>
+      <c r="B404">
+        <v>-1</v>
+      </c>
+      <c r="C404" t="s">
+        <v>26</v>
+      </c>
+      <c r="D404" t="s">
+        <v>6</v>
+      </c>
+      <c r="F404" t="s">
+        <v>16</v>
+      </c>
+      <c r="G404" t="s">
+        <v>27</v>
+      </c>
+      <c r="H404" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A405" s="2"/>
+      <c r="J405" s="2"/>
+    </row>
+    <row r="406" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A406" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A407" t="s">
+        <v>1</v>
+      </c>
+      <c r="B407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A408" t="s">
+        <v>2</v>
+      </c>
+      <c r="B408" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="B403">
-        <v>0.36</v>
-      </c>
-      <c r="C403" t="s">
-        <v>8</v>
-      </c>
-      <c r="D403" t="s">
-        <v>6</v>
-      </c>
-      <c r="F403" t="s">
-        <v>16</v>
-      </c>
-      <c r="G403" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="H403" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="404" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
-        <v>218</v>
-      </c>
-      <c r="B404">
-        <v>0.64</v>
-      </c>
-      <c r="C404" t="s">
-        <v>8</v>
-      </c>
-      <c r="D404" t="s">
-        <v>6</v>
-      </c>
-      <c r="F404" t="s">
-        <v>16</v>
-      </c>
-      <c r="G404" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="H404" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
-        <v>25</v>
-      </c>
-      <c r="B405">
-        <v>-1</v>
-      </c>
-      <c r="C405" t="s">
-        <v>26</v>
-      </c>
-      <c r="D405" t="s">
-        <v>6</v>
-      </c>
-      <c r="F405" t="s">
-        <v>16</v>
-      </c>
-      <c r="G405" t="s">
-        <v>27</v>
-      </c>
-      <c r="H405" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="406" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A406" s="2"/>
-      <c r="J406" s="2"/>
-    </row>
-    <row r="407" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A407" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B407" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A408" t="s">
-        <v>1</v>
-      </c>
-      <c r="B408">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="409" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>2</v>
-      </c>
-      <c r="B409" s="22" t="s">
-        <v>213</v>
+        <v>3</v>
+      </c>
+      <c r="B409" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B410" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B411" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B412" t="s">
-        <v>8</v>
+        <v>214</v>
       </c>
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
+        <v>18</v>
+      </c>
+      <c r="B413" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A414" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A415" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B415" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D415" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E415" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F415" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G415" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H415" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B413" t="s">
+      <c r="I415" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="J415" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="K415" s="5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A414" t="s">
-        <v>18</v>
-      </c>
-      <c r="B414" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="415" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A415" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A416" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B416" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C416" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D416" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E416" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F416" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G416" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H416" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I416" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J416" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="K416" s="5" t="s">
+      <c r="L415" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="L416" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="M416" s="5" t="s">
+      <c r="M415" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="417" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A417" t="str">
-        <f>B407</f>
+    <row r="416" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A416" t="str">
+        <f>B406</f>
         <v>polyethyleneimine (PEI) production, for sorbent-based direct air capture system</v>
       </c>
-      <c r="B417">
-        <v>1</v>
+      <c r="B416">
+        <v>1</v>
+      </c>
+      <c r="C416" t="s">
+        <v>8</v>
+      </c>
+      <c r="D416" t="s">
+        <v>6</v>
+      </c>
+      <c r="F416" t="s">
+        <v>15</v>
+      </c>
+      <c r="G416" s="7" t="str">
+        <f>B408</f>
+        <v>polyethyleneimine</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A417" t="s">
+        <v>90</v>
+      </c>
+      <c r="B417" s="38">
+        <f t="shared" ref="B417:B427" si="0">AVERAGE(K417:L417)</f>
+        <v>1.9749999999999999</v>
       </c>
       <c r="C417" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D417" t="s">
         <v>6</v>
       </c>
       <c r="F417" t="s">
-        <v>15</v>
-      </c>
-      <c r="G417" s="7" t="str">
-        <f>B409</f>
-        <v>polyethyleneimine</v>
+        <v>16</v>
+      </c>
+      <c r="G417" t="s">
+        <v>141</v>
+      </c>
+      <c r="I417">
+        <v>5</v>
+      </c>
+      <c r="J417">
+        <f>B417</f>
+        <v>1.9749999999999999</v>
+      </c>
+      <c r="K417">
+        <v>1.42</v>
+      </c>
+      <c r="L417">
+        <v>2.5299999999999998</v>
       </c>
     </row>
     <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>90</v>
-      </c>
-      <c r="B418" s="38">
-        <f t="shared" ref="B418:B428" si="0">AVERAGE(K418:L418)</f>
-        <v>1.9749999999999999</v>
+        <v>82</v>
+      </c>
+      <c r="B418">
+        <f t="shared" si="0"/>
+        <v>3.1749999999999998</v>
       </c>
       <c r="C418" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D418" t="s">
         <v>6</v>
@@ -9031,32 +9051,32 @@
         <v>16</v>
       </c>
       <c r="G418" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="I418">
         <v>5</v>
       </c>
       <c r="J418">
-        <f>B418</f>
-        <v>1.9749999999999999</v>
+        <f t="shared" ref="J418:J427" si="1">B418</f>
+        <v>3.1749999999999998</v>
       </c>
       <c r="K418">
-        <v>1.42</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="L418">
-        <v>2.5299999999999998</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B419">
         <f t="shared" si="0"/>
-        <v>3.1749999999999998</v>
+        <v>2.59</v>
       </c>
       <c r="C419" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D419" t="s">
         <v>6</v>
@@ -9065,32 +9085,32 @@
         <v>16</v>
       </c>
       <c r="G419" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="I419">
         <v>5</v>
       </c>
       <c r="J419">
-        <f t="shared" ref="J419:J428" si="1">B419</f>
-        <v>3.1749999999999998</v>
+        <f t="shared" si="1"/>
+        <v>2.59</v>
       </c>
       <c r="K419">
-        <v>2.2799999999999998</v>
+        <v>1.86</v>
       </c>
       <c r="L419">
-        <v>4.07</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B420">
         <f t="shared" si="0"/>
-        <v>2.59</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="C420" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D420" t="s">
         <v>6</v>
@@ -9099,32 +9119,32 @@
         <v>16</v>
       </c>
       <c r="G420" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I420">
         <v>5</v>
       </c>
       <c r="J420">
         <f t="shared" si="1"/>
-        <v>2.59</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="K420">
-        <v>1.86</v>
+        <v>0.16</v>
       </c>
       <c r="L420">
-        <v>3.32</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B421">
         <f t="shared" si="0"/>
         <v>0.19500000000000001</v>
       </c>
       <c r="C421" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D421" t="s">
         <v>6</v>
@@ -9133,7 +9153,7 @@
         <v>16</v>
       </c>
       <c r="G421" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I421">
         <v>5</v>
@@ -9151,11 +9171,11 @@
     </row>
     <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B422">
         <f t="shared" si="0"/>
-        <v>0.19500000000000001</v>
+        <v>0.11570000000000008</v>
       </c>
       <c r="C422" t="s">
         <v>17</v>
@@ -9167,32 +9187,37 @@
         <v>16</v>
       </c>
       <c r="G422" t="s">
-        <v>142</v>
+        <v>144</v>
+      </c>
+      <c r="H422" t="s">
+        <v>220</v>
       </c>
       <c r="I422">
         <v>5</v>
       </c>
       <c r="J422">
         <f t="shared" si="1"/>
-        <v>0.19500000000000001</v>
+        <v>0.11570000000000008</v>
       </c>
       <c r="K422">
-        <v>0.16</v>
+        <f>2.84*(1-99%)</f>
+        <v>2.8400000000000022E-2</v>
       </c>
       <c r="L422">
-        <v>0.23</v>
+        <f>4.06*(1-95%)</f>
+        <v>0.20300000000000015</v>
       </c>
     </row>
     <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B423">
         <f t="shared" si="0"/>
-        <v>0.11570000000000008</v>
+        <v>1.3817000000000013</v>
       </c>
       <c r="C423" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D423" t="s">
         <v>6</v>
@@ -9201,34 +9226,34 @@
         <v>16</v>
       </c>
       <c r="G423" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H423" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I423">
         <v>5</v>
       </c>
       <c r="J423">
         <f t="shared" si="1"/>
-        <v>0.11570000000000008</v>
+        <v>1.3817000000000013</v>
       </c>
       <c r="K423">
-        <f>2.84*(1-99%)</f>
-        <v>2.8400000000000022E-2</v>
+        <f>33.94*(1-99%)</f>
+        <v>0.33940000000000026</v>
       </c>
       <c r="L423">
-        <f>4.06*(1-95%)</f>
-        <v>0.20300000000000015</v>
+        <f>48.48*(1-95%)</f>
+        <v>2.4240000000000022</v>
       </c>
     </row>
     <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B424">
         <f t="shared" si="0"/>
-        <v>1.3817000000000013</v>
+        <v>14.559999999999999</v>
       </c>
       <c r="C424" t="s">
         <v>26</v>
@@ -9240,305 +9265,288 @@
         <v>16</v>
       </c>
       <c r="G424" t="s">
-        <v>145</v>
-      </c>
-      <c r="H424" t="s">
-        <v>221</v>
+        <v>89</v>
       </c>
       <c r="I424">
         <v>5</v>
       </c>
       <c r="J424">
         <f t="shared" si="1"/>
-        <v>1.3817000000000013</v>
+        <v>14.559999999999999</v>
       </c>
       <c r="K424">
-        <f>33.94*(1-99%)</f>
-        <v>0.33940000000000026</v>
+        <v>11.99</v>
       </c>
       <c r="L424">
-        <f>48.48*(1-95%)</f>
-        <v>2.4240000000000022</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B425">
         <f t="shared" si="0"/>
-        <v>14.559999999999999</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="C425" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D425" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F425" t="s">
         <v>16</v>
       </c>
       <c r="G425" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="I425">
         <v>5</v>
       </c>
       <c r="J425">
         <f t="shared" si="1"/>
-        <v>14.559999999999999</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="K425">
-        <v>11.99</v>
+        <v>0.27</v>
       </c>
       <c r="L425">
-        <v>17.13</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="B426">
         <f t="shared" si="0"/>
-        <v>0.34499999999999997</v>
+        <v>7.4749999999999996</v>
       </c>
       <c r="C426" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D426" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F426" t="s">
         <v>16</v>
       </c>
       <c r="G426" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I426">
         <v>5</v>
       </c>
       <c r="J426">
         <f t="shared" si="1"/>
-        <v>0.34499999999999997</v>
+        <v>7.4749999999999996</v>
       </c>
       <c r="K426">
-        <v>0.27</v>
+        <v>2.35</v>
       </c>
       <c r="L426">
-        <v>0.42</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B427">
         <f t="shared" si="0"/>
-        <v>7.4749999999999996</v>
+        <v>-1.5</v>
       </c>
       <c r="C427" t="s">
         <v>131</v>
       </c>
       <c r="D427" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F427" t="s">
         <v>16</v>
       </c>
       <c r="G427" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="I427">
         <v>5</v>
       </c>
       <c r="J427">
         <f t="shared" si="1"/>
-        <v>7.4749999999999996</v>
+        <v>-1.5</v>
       </c>
       <c r="K427">
-        <v>2.35</v>
+        <v>-2.63</v>
       </c>
       <c r="L427">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A428" t="s">
-        <v>73</v>
-      </c>
-      <c r="B428">
-        <f t="shared" si="0"/>
-        <v>-1.5</v>
-      </c>
-      <c r="C428" t="s">
-        <v>131</v>
-      </c>
-      <c r="D428" t="s">
-        <v>6</v>
-      </c>
-      <c r="F428" t="s">
-        <v>16</v>
-      </c>
-      <c r="G428" t="s">
-        <v>140</v>
-      </c>
-      <c r="I428">
-        <v>5</v>
-      </c>
-      <c r="J428">
-        <f t="shared" si="1"/>
-        <v>-1.5</v>
-      </c>
-      <c r="K428">
-        <v>-2.63</v>
-      </c>
-      <c r="L428">
         <v>-0.37</v>
       </c>
-      <c r="M428" t="b">
-        <v>1</v>
-      </c>
+      <c r="M427" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A428" s="2"/>
+      <c r="J428" s="2"/>
     </row>
     <row r="429" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A429" s="2"/>
-      <c r="J429" s="2"/>
-    </row>
-    <row r="430" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A430" s="1" t="s">
+      <c r="A429" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B430" s="1" t="s">
+      <c r="B429" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A430" t="s">
+        <v>1</v>
+      </c>
+      <c r="B430">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A431" t="s">
+        <v>2</v>
+      </c>
+      <c r="B431" s="22" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>1</v>
-      </c>
-      <c r="B431">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>2</v>
-      </c>
-      <c r="B432" s="22" t="s">
-        <v>219</v>
+        <v>3</v>
+      </c>
+      <c r="B432" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="433" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B433" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="434" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B434" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="435" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B435" t="s">
-        <v>8</v>
+        <v>219</v>
       </c>
     </row>
     <row r="436" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
+        <v>18</v>
+      </c>
+      <c r="B436" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="437" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A437" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="438" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A438" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B438" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C438" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D438" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E438" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F438" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G438" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H438" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B436" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A437" t="s">
-        <v>18</v>
-      </c>
-      <c r="B437" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="438" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A438" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A439" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B439" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C439" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D439" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E439" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F439" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G439" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H439" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I439" s="5" t="s">
+      <c r="I438" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J439" s="5" t="s">
+      <c r="J438" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="K439" s="5" t="s">
+      <c r="K438" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L438" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="L439" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="440" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A440" t="str">
-        <f>B430</f>
+    </row>
+    <row r="439" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A439" t="str">
+        <f>B429</f>
         <v>silica gel production, for sorbent-based direct air capture system</v>
       </c>
+      <c r="B439">
+        <v>1</v>
+      </c>
+      <c r="C439" t="s">
+        <v>8</v>
+      </c>
+      <c r="D439" t="s">
+        <v>6</v>
+      </c>
+      <c r="F439" t="s">
+        <v>15</v>
+      </c>
+      <c r="G439" s="7" t="str">
+        <f>B431</f>
+        <v>silica gel</v>
+      </c>
+    </row>
+    <row r="440" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A440" t="s">
+        <v>81</v>
+      </c>
       <c r="B440">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="C440" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D440" t="s">
         <v>6</v>
       </c>
       <c r="F440" t="s">
-        <v>15</v>
-      </c>
-      <c r="G440" s="7" t="str">
-        <f>B432</f>
-        <v>silica gel</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G440" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q440" s="4"/>
+      <c r="S440" s="4"/>
     </row>
     <row r="441" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B441">
-        <v>3.9</v>
+        <v>0.66</v>
       </c>
       <c r="C441" t="s">
         <v>26</v>
@@ -9550,271 +9558,272 @@
         <v>16</v>
       </c>
       <c r="G441" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q441" s="4"/>
-      <c r="S441" s="4"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="442" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B442">
-        <v>0.66</v>
+        <v>19.5</v>
       </c>
       <c r="C442" t="s">
         <v>26</v>
       </c>
       <c r="D442" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F442" t="s">
         <v>16</v>
       </c>
       <c r="G442" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="I442">
+        <v>5</v>
+      </c>
+      <c r="J442">
+        <f>B442</f>
+        <v>19.5</v>
+      </c>
+      <c r="K442">
+        <v>15</v>
+      </c>
+      <c r="L442">
+        <v>24</v>
       </c>
     </row>
     <row r="443" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B443">
-        <v>19.5</v>
+        <v>40</v>
       </c>
       <c r="C443" t="s">
         <v>26</v>
       </c>
       <c r="D443" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F443" t="s">
         <v>16</v>
       </c>
       <c r="G443" t="s">
-        <v>88</v>
-      </c>
-      <c r="I443">
-        <v>5</v>
-      </c>
-      <c r="J443">
-        <f>B443</f>
-        <v>19.5</v>
-      </c>
-      <c r="K443">
-        <v>15</v>
-      </c>
-      <c r="L443">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="444" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="B444">
-        <v>40</v>
+        <f>-35/1000</f>
+        <v>-3.5000000000000003E-2</v>
       </c>
       <c r="C444" t="s">
         <v>26</v>
       </c>
       <c r="D444" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F444" t="s">
         <v>16</v>
       </c>
       <c r="G444" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="445" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+      <c r="M444" s="2"/>
+    </row>
+    <row r="445" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>195</v>
-      </c>
-      <c r="B445">
-        <f>-35/1000</f>
-        <v>-3.5000000000000003E-2</v>
-      </c>
-      <c r="C445" t="s">
-        <v>26</v>
+        <v>148</v>
+      </c>
+      <c r="B445" s="6">
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="D445" t="s">
+        <v>6</v>
+      </c>
+      <c r="E445" t="s">
+        <v>85</v>
+      </c>
+      <c r="F445" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="446" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A446" s="2"/>
+      <c r="J446" s="2"/>
+    </row>
+    <row r="447" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A447" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="448" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A448" t="s">
+        <v>1</v>
+      </c>
+      <c r="B448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A449" t="s">
+        <v>2</v>
+      </c>
+      <c r="B449" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A450" t="s">
+        <v>3</v>
+      </c>
+      <c r="B450" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A451" t="s">
+        <v>5</v>
+      </c>
+      <c r="B451" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A452" t="s">
+        <v>7</v>
+      </c>
+      <c r="B452" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A453" t="s">
+        <v>9</v>
+      </c>
+      <c r="B453" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A454" t="s">
+        <v>18</v>
+      </c>
+      <c r="B454" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="455" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A455" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A456" t="s">
+        <v>11</v>
+      </c>
+      <c r="B456" t="s">
+        <v>12</v>
+      </c>
+      <c r="C456" t="s">
+        <v>7</v>
+      </c>
+      <c r="D456" t="s">
+        <v>5</v>
+      </c>
+      <c r="E456" t="s">
+        <v>13</v>
+      </c>
+      <c r="F456" t="s">
+        <v>3</v>
+      </c>
+      <c r="G456" t="s">
+        <v>2</v>
+      </c>
+      <c r="H456" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A457" t="s">
+        <v>97</v>
+      </c>
+      <c r="B457">
+        <v>1</v>
+      </c>
+      <c r="C457" t="s">
+        <v>8</v>
+      </c>
+      <c r="D457" t="s">
+        <v>6</v>
+      </c>
+      <c r="F457" t="s">
+        <v>15</v>
+      </c>
+      <c r="G457" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A458" t="s">
+        <v>194</v>
+      </c>
+      <c r="B458">
+        <v>9.9999999999999986E-10</v>
+      </c>
+      <c r="C458" t="s">
+        <v>21</v>
+      </c>
+      <c r="D458" t="s">
         <v>49</v>
       </c>
-      <c r="F445" t="s">
-        <v>16</v>
-      </c>
-      <c r="G445" t="s">
-        <v>149</v>
-      </c>
-      <c r="M445" s="2"/>
-    </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A446" t="s">
-        <v>148</v>
-      </c>
-      <c r="B446" s="6">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="D446" t="s">
-        <v>6</v>
-      </c>
-      <c r="E446" t="s">
-        <v>85</v>
-      </c>
-      <c r="F446" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="447" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A447" s="2"/>
-      <c r="J447" s="2"/>
-    </row>
-    <row r="448" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A448" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B448" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A449" t="s">
-        <v>1</v>
-      </c>
-      <c r="B449">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="450" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A450" t="s">
-        <v>2</v>
-      </c>
-      <c r="B450" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A451" t="s">
-        <v>3</v>
-      </c>
-      <c r="B451" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A452" t="s">
-        <v>5</v>
-      </c>
-      <c r="B452" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A453" t="s">
-        <v>7</v>
-      </c>
-      <c r="B453" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A454" t="s">
-        <v>9</v>
-      </c>
-      <c r="B454" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A455" t="s">
-        <v>18</v>
-      </c>
-      <c r="B455" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="456" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A456" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A457" t="s">
-        <v>11</v>
-      </c>
-      <c r="B457" t="s">
-        <v>12</v>
-      </c>
-      <c r="C457" t="s">
-        <v>7</v>
-      </c>
-      <c r="D457" t="s">
-        <v>5</v>
-      </c>
-      <c r="E457" t="s">
-        <v>13</v>
-      </c>
-      <c r="F457" t="s">
-        <v>3</v>
-      </c>
-      <c r="G457" t="s">
-        <v>2</v>
-      </c>
-      <c r="H457" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="458" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A458" t="s">
-        <v>97</v>
-      </c>
-      <c r="B458">
-        <v>1</v>
-      </c>
-      <c r="C458" t="s">
-        <v>8</v>
-      </c>
-      <c r="D458" t="s">
-        <v>6</v>
-      </c>
       <c r="F458" t="s">
-        <v>15</v>
-      </c>
-      <c r="G458" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="G458" t="s">
+        <v>196</v>
+      </c>
+      <c r="H458" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="B459">
-        <v>9.9999999999999986E-10</v>
+        <v>1.0000000000000001E-7</v>
       </c>
       <c r="C459" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D459" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="F459" t="s">
         <v>16</v>
       </c>
       <c r="G459" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="H459" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>152</v>
+        <v>42</v>
       </c>
       <c r="B460">
-        <v>1.0000000000000001E-7</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C460" t="s">
         <v>17</v>
@@ -9826,18 +9835,18 @@
         <v>16</v>
       </c>
       <c r="G460" t="s">
-        <v>153</v>
+        <v>30</v>
       </c>
       <c r="H460" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="B461">
-        <v>9.9999999999999995E-7</v>
+        <v>2.9999999999999999E-7</v>
       </c>
       <c r="C461" t="s">
         <v>17</v>
@@ -9849,90 +9858,91 @@
         <v>16</v>
       </c>
       <c r="G461" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="H461" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="B462">
-        <v>2.9999999999999999E-7</v>
+        <v>3.1999999999999999E-5</v>
       </c>
       <c r="C462" t="s">
         <v>17</v>
       </c>
       <c r="D462" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F462" t="s">
         <v>16</v>
       </c>
       <c r="G462" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="H462" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="B463">
-        <v>3.1999999999999999E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C463" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D463" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F463" t="s">
         <v>16</v>
       </c>
       <c r="G463" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="H463" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="B464">
-        <v>9.9999999999999995E-7</v>
+        <v>1.0400000000000001E-3</v>
       </c>
       <c r="C464" t="s">
-        <v>8</v>
-      </c>
-      <c r="D464" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="D464" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="F464" t="s">
         <v>16</v>
       </c>
       <c r="G464" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="H464" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="465" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="J464" s="2"/>
+    </row>
+    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B465">
-        <v>1.0400000000000001E-3</v>
+        <v>1.3000000000000002E-4</v>
       </c>
       <c r="C465" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D465" s="10" t="s">
         <v>6</v>
@@ -9941,16 +9951,15 @@
         <v>16</v>
       </c>
       <c r="G465" t="s">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="H465" t="s">
         <v>107</v>
       </c>
-      <c r="J465" s="2"/>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B466">
         <v>1.3000000000000002E-4</v>
@@ -9965,7 +9974,7 @@
         <v>16</v>
       </c>
       <c r="G466" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="H466" t="s">
         <v>107</v>
@@ -9973,10 +9982,10 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B467">
-        <v>1.3000000000000002E-4</v>
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="C467" t="s">
         <v>17</v>
@@ -9988,7 +9997,7 @@
         <v>16</v>
       </c>
       <c r="G467" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H467" t="s">
         <v>107</v>
@@ -9996,10 +10005,10 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B468">
-        <v>1.1999999999999999E-6</v>
+        <v>2.5000000000000002E-6</v>
       </c>
       <c r="C468" t="s">
         <v>17</v>
@@ -10011,7 +10020,7 @@
         <v>16</v>
       </c>
       <c r="G468" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H468" t="s">
         <v>107</v>
@@ -10019,22 +10028,22 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="B469">
-        <v>2.5000000000000002E-6</v>
+        <v>1.8E-3</v>
       </c>
       <c r="C469" t="s">
         <v>17</v>
       </c>
       <c r="D469" s="10" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F469" t="s">
         <v>16</v>
       </c>
       <c r="G469" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="H469" t="s">
         <v>107</v>
@@ -10042,22 +10051,22 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
       <c r="B470">
-        <v>1.8E-3</v>
+        <v>1.1999999999999999E-4</v>
       </c>
       <c r="C470" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D470" s="10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F470" t="s">
         <v>16</v>
       </c>
       <c r="G470" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="H470" t="s">
         <v>107</v>
@@ -10065,59 +10074,59 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>35</v>
-      </c>
-      <c r="B471">
-        <v>1.1999999999999999E-4</v>
+        <v>106</v>
+      </c>
+      <c r="B471" s="6">
+        <v>8.2000000000000001E-11</v>
       </c>
       <c r="C471" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D471" s="10" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="F471" t="s">
         <v>16</v>
       </c>
       <c r="G471" t="s">
-        <v>36</v>
+        <v>133</v>
       </c>
       <c r="H471" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>106</v>
-      </c>
-      <c r="B472" s="6">
-        <v>8.2000000000000001E-11</v>
+        <v>102</v>
+      </c>
+      <c r="B472">
+        <v>3.3E-3</v>
       </c>
       <c r="C472" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D472" s="10" t="s">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="F472" t="s">
         <v>16</v>
       </c>
       <c r="G472" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H472" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>102</v>
-      </c>
-      <c r="B473">
-        <v>3.3E-3</v>
+        <v>59</v>
+      </c>
+      <c r="B473" s="2">
+        <v>1.7E-5</v>
       </c>
       <c r="C473" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D473" s="10" t="s">
         <v>6</v>
@@ -10126,18 +10135,18 @@
         <v>16</v>
       </c>
       <c r="G473" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H473" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="474" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>59</v>
-      </c>
-      <c r="B474" s="2">
-        <v>1.7E-5</v>
+        <v>42</v>
+      </c>
+      <c r="B474">
+        <v>3.6999999999999998E-5</v>
       </c>
       <c r="C474" t="s">
         <v>17</v>
@@ -10149,7 +10158,7 @@
         <v>16</v>
       </c>
       <c r="G474" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="H474" t="s">
         <v>108</v>
@@ -10157,22 +10166,22 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="B475">
-        <v>3.6999999999999998E-5</v>
+        <v>4.8E-8</v>
       </c>
       <c r="C475" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D475" s="10" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F475" t="s">
         <v>16</v>
       </c>
       <c r="G475" t="s">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="H475" t="s">
         <v>108</v>
@@ -10180,22 +10189,22 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="B476">
-        <v>4.8E-8</v>
+        <v>1.9E-6</v>
       </c>
       <c r="C476" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D476" s="10" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="F476" t="s">
         <v>16</v>
       </c>
       <c r="G476" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="H476" t="s">
         <v>108</v>
@@ -10203,22 +10212,22 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="B477">
-        <v>1.9E-6</v>
+        <v>3.4000000000000002E-4</v>
       </c>
       <c r="C477" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D477" s="10" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F477" t="s">
         <v>16</v>
       </c>
       <c r="G477" t="s">
-        <v>153</v>
+        <v>36</v>
       </c>
       <c r="H477" t="s">
         <v>108</v>
@@ -10226,59 +10235,59 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="B478">
-        <v>3.4000000000000002E-4</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="C478" t="s">
         <v>8</v>
       </c>
       <c r="D478" s="10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F478" t="s">
         <v>16</v>
       </c>
       <c r="G478" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H478" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B479">
-        <v>0.11799999999999999</v>
+        <v>-4.4000000000000003E-3</v>
       </c>
       <c r="C479" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D479" s="10" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F479" t="s">
         <v>16</v>
       </c>
       <c r="G479" t="s">
-        <v>78</v>
+        <v>161</v>
       </c>
       <c r="H479" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B480">
-        <v>-4.4000000000000003E-3</v>
+        <v>-2.5999999999999998E-4</v>
       </c>
       <c r="C480" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="D480" s="10" t="s">
         <v>6</v>
@@ -10287,21 +10296,22 @@
         <v>16</v>
       </c>
       <c r="G480" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H480" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="481" spans="1:20" ht="16" x14ac:dyDescent="0.2">
+      <c r="J480" s="2"/>
+    </row>
+    <row r="481" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="B481">
-        <v>-2.5999999999999998E-4</v>
+        <v>-1.9999999999999999E-6</v>
       </c>
       <c r="C481" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="D481" s="10" t="s">
         <v>6</v>
@@ -10310,22 +10320,21 @@
         <v>16</v>
       </c>
       <c r="G481" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="H481" t="s">
         <v>76</v>
       </c>
-      <c r="J481" s="2"/>
     </row>
     <row r="482" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B482">
-        <v>-1.9999999999999999E-6</v>
+        <v>-2.7999999999999999E-6</v>
       </c>
       <c r="C482" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="D482" s="10" t="s">
         <v>6</v>
@@ -10334,7 +10343,7 @@
         <v>16</v>
       </c>
       <c r="G482" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="H482" t="s">
         <v>76</v>
@@ -10342,13 +10351,13 @@
     </row>
     <row r="483" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B483">
-        <v>-2.7999999999999999E-6</v>
+        <v>-1.1999999999999999E-6</v>
       </c>
       <c r="C483" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="D483" s="10" t="s">
         <v>6</v>
@@ -10357,41 +10366,32 @@
         <v>16</v>
       </c>
       <c r="G483" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H483" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A484" t="s">
-        <v>112</v>
-      </c>
-      <c r="B484">
-        <v>-1.1999999999999999E-6</v>
-      </c>
-      <c r="C484" t="s">
-        <v>131</v>
-      </c>
-      <c r="D484" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F484" t="s">
-        <v>16</v>
-      </c>
-      <c r="G484" t="s">
-        <v>137</v>
-      </c>
-      <c r="H484" t="s">
-        <v>76</v>
-      </c>
+    <row r="485" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A485" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B485" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="K485" s="16"/>
+      <c r="L485" s="16"/>
+      <c r="M485" s="16"/>
+      <c r="N485" s="16"/>
+      <c r="O485" s="16"/>
+      <c r="P485" s="16"/>
     </row>
     <row r="486" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A486" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B486" s="14" t="s">
-        <v>302</v>
+      <c r="A486" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B486" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="K486" s="16"/>
       <c r="L486" s="16"/>
@@ -10402,10 +10402,10 @@
     </row>
     <row r="487" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A487" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B487" s="15" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="B487" s="15">
+        <v>1</v>
       </c>
       <c r="K487" s="16"/>
       <c r="L487" s="16"/>
@@ -10416,10 +10416,10 @@
     </row>
     <row r="488" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A488" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B488" s="15">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B488" s="15" t="s">
+        <v>294</v>
       </c>
       <c r="K488" s="16"/>
       <c r="L488" s="16"/>
@@ -10430,10 +10430,10 @@
     </row>
     <row r="489" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A489" s="15" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B489" s="15" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
       <c r="K489" s="16"/>
       <c r="L489" s="16"/>
@@ -10444,10 +10444,10 @@
     </row>
     <row r="490" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A490" s="15" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B490" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K490" s="16"/>
       <c r="L490" s="16"/>
@@ -10458,10 +10458,10 @@
     </row>
     <row r="491" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A491" s="15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B491" s="15" t="s">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="K491" s="16"/>
       <c r="L491" s="16"/>
@@ -10472,10 +10472,10 @@
     </row>
     <row r="492" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A492" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B492" s="15" t="s">
-        <v>199</v>
+        <v>171</v>
+      </c>
+      <c r="B492" s="17">
+        <v>0.61363636363636365</v>
       </c>
       <c r="K492" s="16"/>
       <c r="L492" s="16"/>
@@ -10485,11 +10485,8 @@
       <c r="P492" s="16"/>
     </row>
     <row r="493" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A493" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="B493" s="17">
-        <v>0.61363636363636365</v>
+      <c r="A493" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="K493" s="16"/>
       <c r="L493" s="16"/>
@@ -10500,112 +10497,151 @@
     </row>
     <row r="494" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A494" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="K494" s="16"/>
-      <c r="L494" s="16"/>
-      <c r="M494" s="16"/>
-      <c r="N494" s="16"/>
-      <c r="O494" s="16"/>
-      <c r="P494" s="16"/>
+        <v>11</v>
+      </c>
+      <c r="B494" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C494" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D494" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E494" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F494" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G494" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H494" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="I494" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="J494" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="K494" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="L494" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="M494" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="N494" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="O494" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="P494" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q494" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="R494" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="S494" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="T494" s="1"/>
     </row>
     <row r="495" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A495" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B495" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C495" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D495" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E495" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F495" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G495" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H495" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I495" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="J495" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="K495" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="L495" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="M495" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="N495" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="O495" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="P495" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q495" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="R495" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="S495" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="T495" s="1"/>
+      <c r="A495" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B495" s="15">
+        <v>1</v>
+      </c>
+      <c r="C495" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D495" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F495" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G495" s="15" t="str">
+        <f>B488</f>
+        <v>carbon dioxide, captured</v>
+      </c>
+      <c r="H495" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="K495" s="16"/>
+      <c r="L495" s="16"/>
+      <c r="M495" s="16"/>
+      <c r="N495" s="16"/>
+      <c r="O495" s="16"/>
+      <c r="P495" s="16"/>
+      <c r="T495"/>
     </row>
     <row r="496" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A496" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="B496" s="15">
-        <v>1</v>
-      </c>
-      <c r="C496" s="15" t="s">
-        <v>8</v>
+        <v>184</v>
+      </c>
+      <c r="B496" s="19">
+        <v>6.7613636363636362E-2</v>
       </c>
       <c r="D496" s="15" t="s">
         <v>6</v>
       </c>
+      <c r="E496" s="15" t="s">
+        <v>85</v>
+      </c>
       <c r="F496" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G496" s="15" t="str">
-        <f>B489</f>
-        <v>carbon dioxide, captured</v>
+        <v>20</v>
       </c>
       <c r="H496" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="K496" s="16"/>
-      <c r="L496" s="16"/>
-      <c r="M496" s="16"/>
-      <c r="N496" s="16"/>
-      <c r="O496" s="16"/>
-      <c r="P496" s="16"/>
-      <c r="T496"/>
+        <v>185</v>
+      </c>
+      <c r="I496" s="15">
+        <v>2</v>
+      </c>
+      <c r="J496">
+        <v>-2.6939455949206681</v>
+      </c>
+      <c r="K496" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L496" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="M496" s="4">
+        <v>1</v>
+      </c>
+      <c r="N496" s="4">
+        <v>1.01</v>
+      </c>
+      <c r="O496" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="P496" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="Q496" s="4">
+        <v>1.05</v>
+      </c>
+      <c r="R496">
+        <v>0.16679850853156178</v>
+      </c>
     </row>
     <row r="497" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A497" s="15" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="B497" s="19">
-        <v>6.7613636363636362E-2</v>
+        <v>0.10738636363636363</v>
       </c>
       <c r="D497" s="15" t="s">
         <v>6</v>
@@ -10623,7 +10659,7 @@
         <v>2</v>
       </c>
       <c r="J497">
-        <v>-2.6939455949206681</v>
+        <v>-2.2313220729725551</v>
       </c>
       <c r="K497" s="4">
         <v>1.1000000000000001</v>
@@ -10652,10 +10688,10 @@
     </row>
     <row r="498" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A498" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B498" s="19">
-        <v>0.10738636363636363</v>
+        <v>186</v>
+      </c>
+      <c r="B498" s="20">
+        <v>1E-4</v>
       </c>
       <c r="D498" s="15" t="s">
         <v>6</v>
@@ -10666,14 +10702,11 @@
       <c r="F498" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="H498" s="15" t="s">
-        <v>185</v>
-      </c>
       <c r="I498" s="15">
         <v>2</v>
       </c>
       <c r="J498">
-        <v>-2.2313220729725551</v>
+        <v>-9.2103403719761818</v>
       </c>
       <c r="K498" s="4">
         <v>1.1000000000000001</v>
@@ -10694,33 +10727,36 @@
         <v>1.2</v>
       </c>
       <c r="Q498" s="4">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="R498">
-        <v>0.16679850853156178</v>
+        <v>0.26139455023340635</v>
       </c>
     </row>
     <row r="499" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A499" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="B499" s="20">
-        <v>1E-4</v>
+        <v>31</v>
+      </c>
+      <c r="B499" s="15">
+        <v>9.6600000000000002E-3</v>
+      </c>
+      <c r="C499" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="D499" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E499" s="15" t="s">
-        <v>85</v>
-      </c>
       <c r="F499" s="15" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="G499" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="I499" s="15">
         <v>2</v>
       </c>
       <c r="J499">
-        <v>-9.2103403719761818</v>
+        <v>-4.6397616307577101</v>
       </c>
       <c r="K499" s="4">
         <v>1.1000000000000001</v>
@@ -10740,37 +10776,37 @@
       <c r="P499" s="4">
         <v>1.2</v>
       </c>
-      <c r="Q499" s="4">
-        <v>1.5</v>
+      <c r="Q499">
+        <v>1.05</v>
       </c>
       <c r="R499">
-        <v>0.26139455023340635</v>
+        <v>0.16679850853156178</v>
       </c>
     </row>
     <row r="500" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A500" s="15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B500" s="15">
-        <v>9.6600000000000002E-3</v>
+        <v>0.1</v>
       </c>
       <c r="C500" s="15" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D500" s="15" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F500" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G500" s="15" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I500" s="15">
         <v>2</v>
       </c>
       <c r="J500">
-        <v>-4.6397616307577101</v>
+        <v>-2.3025850929940455</v>
       </c>
       <c r="K500" s="4">
         <v>1.1000000000000001</v>
@@ -10799,28 +10835,32 @@
     </row>
     <row r="501" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A501" s="15" t="s">
-        <v>34</v>
+        <v>187</v>
       </c>
       <c r="B501" s="15">
-        <v>0.1</v>
+        <f>0.4+((3.7-0.4)*0.4)</f>
+        <v>1.7200000000000002</v>
       </c>
       <c r="C501" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D501" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F501" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G501" s="15" t="s">
-        <v>24</v>
+        <v>188</v>
+      </c>
+      <c r="H501" s="15" t="s">
+        <v>197</v>
       </c>
       <c r="I501" s="15">
         <v>2</v>
       </c>
       <c r="J501">
-        <v>-2.3025850929940455</v>
+        <v>0.40546510810816438</v>
       </c>
       <c r="K501" s="4">
         <v>1.1000000000000001</v>
@@ -10849,32 +10889,28 @@
     </row>
     <row r="502" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A502" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="B502" s="15">
-        <f>0.4+((3.7-0.4)*0.4)</f>
-        <v>1.7200000000000002</v>
+        <v>90</v>
+      </c>
+      <c r="B502" s="39">
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C502" s="15" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D502" s="15" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F502" s="15" t="s">
         <v>16</v>
       </c>
       <c r="G502" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="H502" s="15" t="s">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="I502" s="15">
         <v>2</v>
       </c>
       <c r="J502">
-        <v>0.40546510810816438</v>
+        <v>-5.521460917862246</v>
       </c>
       <c r="K502" s="4">
         <v>1.1000000000000001</v>
@@ -10903,10 +10939,10 @@
     </row>
     <row r="503" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A503" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B503" s="39">
-        <v>4.0000000000000001E-3</v>
+        <v>91</v>
+      </c>
+      <c r="B503" s="15">
+        <v>1E-4</v>
       </c>
       <c r="C503" s="15" t="s">
         <v>17</v>
@@ -10918,13 +10954,13 @@
         <v>16</v>
       </c>
       <c r="G503" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I503" s="15">
         <v>2</v>
       </c>
       <c r="J503">
-        <v>-5.521460917862246</v>
+        <v>-9.2103403719761818</v>
       </c>
       <c r="K503" s="4">
         <v>1.1000000000000001</v>
@@ -10953,7 +10989,7 @@
     </row>
     <row r="504" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A504" s="15" t="s">
-        <v>91</v>
+        <v>189</v>
       </c>
       <c r="B504" s="15">
         <v>1E-4</v>
@@ -10968,7 +11004,7 @@
         <v>16</v>
       </c>
       <c r="G504" s="15" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="I504" s="15">
         <v>2</v>
@@ -11002,235 +11038,236 @@
       </c>
     </row>
     <row r="505" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A505" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B505" s="15">
-        <v>1E-4</v>
-      </c>
-      <c r="C505" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D505" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F505" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G505" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="I505" s="15">
+      <c r="K505" s="16"/>
+      <c r="L505" s="16"/>
+      <c r="M505" s="16"/>
+      <c r="N505" s="16"/>
+      <c r="O505" s="16"/>
+      <c r="P505" s="16"/>
+    </row>
+    <row r="506" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A506" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B506" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="507" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A507" t="s">
+        <v>7</v>
+      </c>
+      <c r="B507" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="508" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+      <c r="A508" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A509" t="s">
         <v>2</v>
       </c>
-      <c r="J505">
-        <v>-9.2103403719761818</v>
-      </c>
-      <c r="K505" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L505" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="M505" s="4">
-        <v>1</v>
-      </c>
-      <c r="N505" s="4">
-        <v>1.01</v>
-      </c>
-      <c r="O505" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="P505" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="Q505">
-        <v>1.05</v>
-      </c>
-      <c r="R505">
-        <v>0.16679850853156178</v>
-      </c>
-    </row>
-    <row r="506" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="K506" s="16"/>
-      <c r="L506" s="16"/>
-      <c r="M506" s="16"/>
-      <c r="N506" s="16"/>
-      <c r="O506" s="16"/>
-      <c r="P506" s="16"/>
-    </row>
-    <row r="507" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A507" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B507" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="508" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A508" t="s">
-        <v>7</v>
-      </c>
-      <c r="B508" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="509" spans="1:18" ht="16" x14ac:dyDescent="0.2">
-      <c r="A509" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B509">
-        <v>1</v>
+      <c r="B509" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="510" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B510" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
     </row>
     <row r="511" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B511" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="512" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B512" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
     </row>
     <row r="513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B513" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>9</v>
-      </c>
-      <c r="B514" t="s">
-        <v>200</v>
+        <v>171</v>
+      </c>
+      <c r="B514">
+        <v>0.06</v>
       </c>
     </row>
     <row r="515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="B515">
-        <v>0.06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>192</v>
-      </c>
-      <c r="B516">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="517" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A517" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="518" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A518" s="1" t="s">
+    <row r="517" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A517" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B518" s="1" t="s">
+      <c r="B517" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C518" s="5" t="s">
+      <c r="C517" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D518" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E518" s="5" t="s">
+      <c r="D517" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E517" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F518" s="5" t="s">
+      <c r="F517" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G518" s="5" t="s">
+      <c r="G517" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H518" s="5" t="s">
+      <c r="H517" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I518" s="5" t="s">
+      <c r="I517" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J518" s="5" t="s">
+      <c r="J517" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="K518" s="5" t="s">
+      <c r="K517" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="L518" s="5" t="s">
+      <c r="L517" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="M518" s="5" t="s">
+      <c r="M517" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="N518" s="5" t="s">
+      <c r="N517" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="O518" s="5" t="s">
+      <c r="O517" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="P518" s="5" t="s">
+      <c r="P517" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="Q518" s="5" t="s">
+      <c r="Q517" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="R518" s="5" t="s">
+      <c r="R517" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="S518" s="5" t="s">
+      <c r="S517" s="5" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="518" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A518" t="s">
+        <v>302</v>
+      </c>
+      <c r="B518">
+        <v>1</v>
+      </c>
+      <c r="C518" t="s">
+        <v>8</v>
+      </c>
+      <c r="D518" t="s">
+        <v>6</v>
+      </c>
+      <c r="F518" t="s">
+        <v>15</v>
+      </c>
+      <c r="G518" t="str">
+        <f>B509</f>
+        <v>carbon dioxide, captured</v>
       </c>
     </row>
     <row r="519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>303</v>
+        <v>184</v>
       </c>
       <c r="B519">
-        <v>1</v>
-      </c>
-      <c r="C519" t="s">
-        <v>8</v>
+        <f>0.11*(1-B514)</f>
+        <v>0.10339999999999999</v>
       </c>
       <c r="D519" t="s">
         <v>6</v>
       </c>
+      <c r="E519" t="s">
+        <v>85</v>
+      </c>
       <c r="F519" t="s">
-        <v>15</v>
-      </c>
-      <c r="G519" t="str">
-        <f>B510</f>
-        <v>carbon dioxide, captured</v>
+        <v>20</v>
+      </c>
+      <c r="H519" t="s">
+        <v>193</v>
+      </c>
+      <c r="I519">
+        <v>2</v>
+      </c>
+      <c r="J519">
+        <v>-2.2678230385440798</v>
+      </c>
+      <c r="K519">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="L519">
+        <v>1.2</v>
+      </c>
+      <c r="M519">
+        <v>1</v>
+      </c>
+      <c r="N519">
+        <v>1.01</v>
+      </c>
+      <c r="O519">
+        <v>1.2</v>
+      </c>
+      <c r="P519">
+        <v>1.2</v>
+      </c>
+      <c r="Q519">
+        <v>1.05</v>
+      </c>
+      <c r="R519">
+        <v>0.16679850853156178</v>
       </c>
     </row>
     <row r="520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="B520">
-        <f>0.11*(1-B515)</f>
-        <v>0.10339999999999999</v>
+        <f>0.11-B519</f>
+        <v>6.6000000000000086E-3</v>
       </c>
       <c r="D520" t="s">
         <v>6</v>
@@ -11248,7 +11285,7 @@
         <v>2</v>
       </c>
       <c r="J520">
-        <v>-2.2678230385440798</v>
+        <v>-5.0417129971418326</v>
       </c>
       <c r="K520">
         <v>1.1000000000000001</v>
@@ -11277,29 +11314,28 @@
     </row>
     <row r="521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B521">
-        <f>0.11-B520</f>
-        <v>6.6000000000000086E-3</v>
+        <v>9.6600000000000002E-3</v>
+      </c>
+      <c r="C521" t="s">
+        <v>131</v>
       </c>
       <c r="D521" t="s">
         <v>6</v>
       </c>
-      <c r="E521" t="s">
-        <v>85</v>
-      </c>
       <c r="F521" t="s">
-        <v>20</v>
-      </c>
-      <c r="H521" t="s">
-        <v>193</v>
+        <v>16</v>
+      </c>
+      <c r="G521" t="s">
+        <v>32</v>
       </c>
       <c r="I521">
         <v>2</v>
       </c>
       <c r="J521">
-        <v>-5.0417129971418326</v>
+        <v>-4.6397616307577101</v>
       </c>
       <c r="K521">
         <v>1.1000000000000001</v>
@@ -11328,28 +11364,28 @@
     </row>
     <row r="522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B522">
-        <v>9.6600000000000002E-3</v>
+        <v>6.9000000000000008E-3</v>
       </c>
       <c r="C522" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D522" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F522" t="s">
         <v>16</v>
       </c>
       <c r="G522" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I522">
         <v>2</v>
       </c>
       <c r="J522">
-        <v>-4.6397616307577101</v>
+        <v>-4.976233867378923</v>
       </c>
       <c r="K522">
         <v>1.1000000000000001</v>
@@ -11378,28 +11414,29 @@
     </row>
     <row r="523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>34</v>
+        <v>187</v>
       </c>
       <c r="B523">
-        <v>6.9000000000000008E-3</v>
+        <f>3.66*0.7</f>
+        <v>2.5619999999999998</v>
       </c>
       <c r="C523" t="s">
         <v>8</v>
       </c>
       <c r="D523" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F523" t="s">
         <v>16</v>
       </c>
       <c r="G523" t="s">
-        <v>24</v>
+        <v>188</v>
       </c>
       <c r="I523">
         <v>2</v>
       </c>
       <c r="J523">
-        <v>-4.976233867378923</v>
+        <v>0.99635805462935334</v>
       </c>
       <c r="K523">
         <v>1.1000000000000001</v>
@@ -11426,31 +11463,30 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A524" t="s">
-        <v>187</v>
-      </c>
-      <c r="B524">
-        <f>3.66*0.7</f>
-        <v>2.5619999999999998</v>
+    <row r="524" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A524" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B524" s="38">
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C524" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D524" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F524" t="s">
         <v>16</v>
       </c>
       <c r="G524" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="I524">
         <v>2</v>
       </c>
       <c r="J524">
-        <v>0.99635805462935334</v>
+        <v>-6.9077552789821368</v>
       </c>
       <c r="K524">
         <v>1.1000000000000001</v>
@@ -11477,168 +11513,139 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="525" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A525" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B525" s="38">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="C525" t="s">
-        <v>17</v>
-      </c>
-      <c r="D525" t="s">
-        <v>6</v>
-      </c>
-      <c r="F525" t="s">
-        <v>16</v>
-      </c>
-      <c r="G525" t="s">
-        <v>141</v>
-      </c>
-      <c r="I525">
+    <row r="526" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A526" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="527" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A527" t="s">
+        <v>7</v>
+      </c>
+      <c r="B527" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="528" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A528" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B528">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A529" t="s">
         <v>2</v>
       </c>
-      <c r="J525">
-        <v>-6.9077552789821368</v>
-      </c>
-      <c r="K525">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L525">
-        <v>1.2</v>
-      </c>
-      <c r="M525">
-        <v>1</v>
-      </c>
-      <c r="N525">
-        <v>1.01</v>
-      </c>
-      <c r="O525">
-        <v>1.2</v>
-      </c>
-      <c r="P525">
-        <v>1.2</v>
-      </c>
-      <c r="Q525">
-        <v>1.05</v>
-      </c>
-      <c r="R525">
-        <v>0.16679850853156178</v>
-      </c>
-    </row>
-    <row r="527" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A527" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B527" s="5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A528" t="s">
-        <v>7</v>
-      </c>
-      <c r="B528" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="529" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A529" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B529">
-        <v>1</v>
+      <c r="B529" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B530" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
     </row>
     <row r="531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B531" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B532" t="s">
-        <v>6</v>
+        <v>236</v>
       </c>
     </row>
     <row r="533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B533" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="535" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A535" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D535" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E535" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F535" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G535" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H535" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B534" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="535" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A535" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="536" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A536" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B536" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C536" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D536" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E536" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F536" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G536" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H536" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I536" s="5"/>
-      <c r="J536" s="5"/>
-      <c r="K536" s="5"/>
-      <c r="L536" s="5"/>
-      <c r="M536" s="5"/>
-      <c r="N536" s="5"/>
-      <c r="O536" s="5"/>
-      <c r="P536" s="5"/>
-      <c r="Q536" s="5"/>
-      <c r="R536" s="5"/>
-      <c r="S536" s="5"/>
+      <c r="I535" s="5"/>
+      <c r="J535" s="5"/>
+      <c r="K535" s="5"/>
+      <c r="L535" s="5"/>
+      <c r="M535" s="5"/>
+      <c r="N535" s="5"/>
+      <c r="O535" s="5"/>
+      <c r="P535" s="5"/>
+      <c r="Q535" s="5"/>
+      <c r="R535" s="5"/>
+      <c r="S535" s="5"/>
+    </row>
+    <row r="536" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A536" s="28" t="str">
+        <f>B526</f>
+        <v>carbon dioxide, captured, at cement production plant, using monoethanolamine</v>
+      </c>
+      <c r="B536" s="37">
+        <v>1</v>
+      </c>
+      <c r="C536" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D536" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F536" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G536" s="28" t="str">
+        <f>B529</f>
+        <v>carbon dioxide, captured</v>
+      </c>
     </row>
     <row r="537" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A537" s="28" t="str">
-        <f>B527</f>
-        <v>carbon dioxide, captured, at cement production plant, using monoethanolamine</v>
-      </c>
-      <c r="B537" s="37">
+      <c r="A537" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B537" s="29">
         <v>1</v>
       </c>
       <c r="C537" s="28" t="s">
@@ -11648,22 +11655,22 @@
         <v>6</v>
       </c>
       <c r="F537" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G537" s="28" t="str">
-        <f>B530</f>
-        <v>carbon dioxide, captured</v>
+        <v>16</v>
+      </c>
+      <c r="G537" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="538" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A538" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B538" s="29">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="B538" s="37">
+        <f>1.4/1000</f>
+        <v>1.4E-3</v>
       </c>
       <c r="C538" s="28" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D538" s="28" t="s">
         <v>6</v>
@@ -11671,17 +11678,21 @@
       <c r="F538" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G538" t="s">
-        <v>98</v>
-      </c>
+      <c r="G538" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="H538" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="N538" s="29"/>
     </row>
     <row r="539" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A539" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B539" s="37">
-        <f>1.4/1000</f>
-        <v>1.4E-3</v>
+        <v>91</v>
+      </c>
+      <c r="B539" s="29">
+        <f>0.000355*1.25*(1/0.828)</f>
+        <v>5.3592995169082129E-4</v>
       </c>
       <c r="C539" s="28" t="s">
         <v>17</v>
@@ -11693,61 +11704,61 @@
         <v>16</v>
       </c>
       <c r="G539" s="28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H539" s="28" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="N539" s="29"/>
+      <c r="P539" s="29"/>
     </row>
     <row r="540" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A540" s="28" t="s">
-        <v>91</v>
+      <c r="A540" t="s">
+        <v>317</v>
       </c>
       <c r="B540" s="29">
-        <f>0.000355*1.25*(1/0.828)</f>
-        <v>5.3592995169082129E-4</v>
-      </c>
-      <c r="C540" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D540" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F540" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G540" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="H540" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="N540" s="29"/>
-      <c r="P540" s="29"/>
-    </row>
-    <row r="541" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A541" t="s">
-        <v>318</v>
-      </c>
-      <c r="B541" s="29">
         <f>(3.76-0.11)/0.9</f>
         <v>4.0555555555555554</v>
       </c>
+      <c r="C540" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D540" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F540" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G540" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H540" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="N540" s="29"/>
+    </row>
+    <row r="541" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A541" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B541" s="29">
+        <f>188/761*0.459/3.6</f>
+        <v>3.1498028909329831E-2</v>
+      </c>
       <c r="C541" s="28" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D541" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F541" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G541" s="28" t="s">
-        <v>162</v>
+        <v>24</v>
       </c>
       <c r="H541" s="28" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N541" s="29"/>
     </row>
@@ -11756,8 +11767,8 @@
         <v>34</v>
       </c>
       <c r="B542" s="29">
-        <f>188/761*0.459/3.6</f>
-        <v>3.1498028909329831E-2</v>
+        <f>123/761*0.459/3.6</f>
+        <v>2.0607752956636003E-2</v>
       </c>
       <c r="C542" s="28" t="s">
         <v>8</v>
@@ -11781,8 +11792,8 @@
         <v>34</v>
       </c>
       <c r="B543" s="29">
-        <f>123/761*0.459/3.6</f>
-        <v>2.0607752956636003E-2</v>
+        <f>575/761*0.459/3.6</f>
+        <v>9.63370565045992E-2</v>
       </c>
       <c r="C543" s="28" t="s">
         <v>8</v>
@@ -11797,46 +11808,45 @@
         <v>24</v>
       </c>
       <c r="H543" s="28" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="N543" s="29"/>
+      <c r="Q543" s="30"/>
     </row>
     <row r="544" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A544" s="28" t="s">
-        <v>34</v>
+        <v>229</v>
       </c>
       <c r="B544" s="29">
-        <f>575/761*0.459/3.6</f>
-        <v>9.63370565045992E-2</v>
+        <f>0.473</f>
+        <v>0.47299999999999998</v>
       </c>
       <c r="C544" s="28" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D544" s="28" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F544" s="28" t="s">
         <v>16</v>
       </c>
       <c r="G544" s="28" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H544" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="N544" s="29"/>
-      <c r="Q544" s="30"/>
+        <v>230</v>
+      </c>
     </row>
     <row r="545" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A545" s="28" t="s">
-        <v>230</v>
+        <v>73</v>
       </c>
       <c r="B545" s="29">
-        <f>0.473</f>
-        <v>0.47299999999999998</v>
+        <f>-B538*0.227/(0.227+0.006)</f>
+        <v>-1.3639484978540772E-3</v>
       </c>
       <c r="C545" s="28" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D545" s="28" t="s">
         <v>6</v>
@@ -11845,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="G545" s="28" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="H545" s="28" t="s">
         <v>231</v>
@@ -11853,38 +11863,35 @@
     </row>
     <row r="546" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A546" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="B546" s="29">
-        <f>-B539*0.227/(0.227+0.006)</f>
-        <v>-1.3639484978540772E-3</v>
-      </c>
-      <c r="C546" s="28" t="s">
-        <v>131</v>
+        <v>232</v>
+      </c>
+      <c r="B546" s="37">
+        <f>1.4/1000*(0.006/0.227+0.006)</f>
+        <v>4.5404405286343617E-5</v>
       </c>
       <c r="D546" s="28" t="s">
         <v>6</v>
       </c>
+      <c r="E546" s="28" t="s">
+        <v>85</v>
+      </c>
       <c r="F546" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G546" s="28" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="H546" s="28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="547" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A547" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="B547" s="37">
-        <f>1.4/1000*(0.006/0.227+0.006)</f>
-        <v>4.5404405286343617E-5</v>
+        <v>234</v>
+      </c>
+      <c r="B547" s="29">
+        <f>B544/1000</f>
+        <v>4.7299999999999995E-4</v>
       </c>
       <c r="D547" s="28" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="E547" s="28" t="s">
         <v>85</v>
@@ -11892,141 +11899,141 @@
       <c r="F547" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H547" s="28" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="548" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A548" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="B548" s="29">
-        <f>B545/1000</f>
-        <v>4.7299999999999995E-4</v>
-      </c>
-      <c r="D548" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E548" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="F548" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G548" s="29"/>
-    </row>
-    <row r="550" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A550" s="1" t="s">
+      <c r="G547" s="29"/>
+    </row>
+    <row r="549" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A549" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B550" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="551" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A551" t="s">
+      <c r="B549" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="550" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A550" t="s">
         <v>7</v>
       </c>
-      <c r="B551" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="552" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A552" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B552">
-        <v>1</v>
+      <c r="B550" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="551" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A551" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B551">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A552" t="s">
+        <v>2</v>
+      </c>
+      <c r="B552" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B553" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
     </row>
     <row r="554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B554" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B555" t="s">
-        <v>6</v>
+        <v>236</v>
       </c>
     </row>
     <row r="556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B556" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="558" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A558" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C558" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D558" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E558" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F558" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G558" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H558" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B557" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="558" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A558" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="559" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A559" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B559" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C559" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D559" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E559" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F559" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G559" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H559" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I559" s="5"/>
-      <c r="J559" s="5"/>
-      <c r="K559" s="5"/>
-      <c r="L559" s="5"/>
-      <c r="M559" s="5"/>
-      <c r="N559" s="5"/>
-      <c r="O559" s="5"/>
-      <c r="P559" s="5"/>
-      <c r="Q559" s="5"/>
-      <c r="R559" s="5"/>
-      <c r="S559" s="5"/>
-    </row>
-    <row r="560" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A560" s="28" t="str">
-        <f>B550</f>
+      <c r="I558" s="5"/>
+      <c r="J558" s="5"/>
+      <c r="K558" s="5"/>
+      <c r="L558" s="5"/>
+      <c r="M558" s="5"/>
+      <c r="N558" s="5"/>
+      <c r="O558" s="5"/>
+      <c r="P558" s="5"/>
+      <c r="Q558" s="5"/>
+      <c r="R558" s="5"/>
+      <c r="S558" s="5"/>
+    </row>
+    <row r="559" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A559" s="28" t="str">
+        <f>B549</f>
         <v>carbon dioxide, captured, at cement production plant, using direct separation</v>
       </c>
-      <c r="B560" s="28">
+      <c r="B559" s="28">
+        <v>1</v>
+      </c>
+      <c r="C559" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D559" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F559" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G559" s="28" t="str">
+        <f>B552</f>
+        <v>carbon dioxide, captured</v>
+      </c>
+    </row>
+    <row r="560" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A560" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B560" s="29">
         <v>1</v>
       </c>
       <c r="C560" s="28" t="s">
@@ -12035,242 +12042,245 @@
       <c r="D560" s="28" t="s">
         <v>6</v>
       </c>
+      <c r="E560" s="28"/>
       <c r="F560" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G560" s="28" t="str">
-        <f>B553</f>
-        <v>carbon dioxide, captured</v>
-      </c>
-    </row>
-    <row r="561" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A561" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B561" s="29">
-        <v>1</v>
-      </c>
-      <c r="C561" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D561" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E561" s="28"/>
-      <c r="F561" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G561" t="s">
+        <v>16</v>
+      </c>
+      <c r="G560" t="s">
         <v>98</v>
       </c>
-      <c r="H561" s="28"/>
-    </row>
-    <row r="562" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A562" s="26" t="s">
+      <c r="H560" s="28"/>
+    </row>
+    <row r="561" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A561" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B562" s="32">
+      <c r="B561" s="32">
         <f>77*1/0.558/1000</f>
         <v>0.13799283154121864</v>
       </c>
-      <c r="C562" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D562" s="26" t="s">
+      <c r="C561" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D561" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F562" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G562" s="26" t="s">
+      <c r="F561" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G561" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H562" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="N562" s="32"/>
-    </row>
-    <row r="565" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A565" s="1" t="s">
+      <c r="H561" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="N561" s="32"/>
+    </row>
+    <row r="564" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A564" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B565" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="566" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A566" t="s">
+      <c r="B564" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="565" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A565" t="s">
         <v>7</v>
       </c>
-      <c r="B566" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="567" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A567" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B567">
-        <v>1</v>
+      <c r="B565" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="566" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A566" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B566">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A567" t="s">
+        <v>2</v>
+      </c>
+      <c r="B567" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B568" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
     </row>
     <row r="569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B569" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B570" t="s">
-        <v>6</v>
+        <v>236</v>
       </c>
     </row>
     <row r="571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B571" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="573" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A573" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D573" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E573" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F573" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G573" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H573" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B572" t="s">
+      <c r="I573" s="5"/>
+      <c r="J573" s="5"/>
+      <c r="K573" s="5"/>
+      <c r="L573" s="5"/>
+      <c r="M573" s="5"/>
+      <c r="N573" s="5"/>
+      <c r="O573" s="5"/>
+      <c r="P573" s="5"/>
+      <c r="Q573" s="5"/>
+      <c r="R573" s="5"/>
+      <c r="S573" s="5"/>
+    </row>
+    <row r="574" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A574" s="28" t="str">
+        <f>B564</f>
+        <v>carbon dioxide, captured, at cement production plant, using oxyfuel</v>
+      </c>
+      <c r="B574" s="28">
+        <v>1</v>
+      </c>
+      <c r="C574" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D574" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F574" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G574" s="28" t="str">
+        <f>B567</f>
+        <v>carbon dioxide, captured</v>
+      </c>
+    </row>
+    <row r="575" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A575" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B575" s="29">
+        <v>1</v>
+      </c>
+      <c r="C575" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D575" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E575" s="28"/>
+      <c r="F575" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G575" t="s">
+        <v>98</v>
+      </c>
+      <c r="H575" s="28"/>
+    </row>
+    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A576" t="s">
+        <v>248</v>
+      </c>
+      <c r="B576" s="6">
+        <f>B574*32/44/(1-0.11)</f>
+        <v>0.81716036772216549</v>
+      </c>
+      <c r="C576" t="s">
+        <v>26</v>
+      </c>
+      <c r="D576" t="s">
+        <v>6</v>
+      </c>
+      <c r="F576" t="s">
+        <v>16</v>
+      </c>
+      <c r="G576" t="s">
+        <v>246</v>
+      </c>
+      <c r="H576" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="573" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A573" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="574" spans="1:19" ht="16" x14ac:dyDescent="0.2">
-      <c r="A574" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B574" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C574" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D574" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E574" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F574" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G574" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H574" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I574" s="5"/>
-      <c r="J574" s="5"/>
-      <c r="K574" s="5"/>
-      <c r="L574" s="5"/>
-      <c r="M574" s="5"/>
-      <c r="N574" s="5"/>
-      <c r="O574" s="5"/>
-      <c r="P574" s="5"/>
-      <c r="Q574" s="5"/>
-      <c r="R574" s="5"/>
-      <c r="S574" s="5"/>
-    </row>
-    <row r="575" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A575" s="28" t="str">
-        <f>B565</f>
-        <v>carbon dioxide, captured, at cement production plant, using oxyfuel</v>
-      </c>
-      <c r="B575" s="28">
-        <v>1</v>
-      </c>
-      <c r="C575" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D575" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F575" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G575" s="28" t="str">
-        <f>B568</f>
-        <v>carbon dioxide, captured</v>
-      </c>
-    </row>
-    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A576" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B576" s="29">
-        <v>1</v>
-      </c>
-      <c r="C576" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D576" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E576" s="28"/>
-      <c r="F576" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G576" t="s">
-        <v>98</v>
-      </c>
-      <c r="H576" s="28"/>
     </row>
     <row r="577" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>249</v>
+        <v>34</v>
       </c>
       <c r="B577" s="6">
-        <f>B575*32/44/(1-0.11)</f>
-        <v>0.81716036772216549</v>
+        <f>(122-182-62)/758*0.459/3.6</f>
+        <v>-2.0521108179419524E-2</v>
       </c>
       <c r="C577" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D577" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F577" t="s">
         <v>16</v>
       </c>
       <c r="G577" t="s">
-        <v>247</v>
+        <v>24</v>
       </c>
       <c r="H577" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="578" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:22" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>34</v>
       </c>
       <c r="B578" s="6">
-        <f>(122-182-62)/758*0.459/3.6</f>
-        <v>-2.0521108179419524E-2</v>
+        <f>59/758*0.459/3.6</f>
+        <v>9.9241424802110813E-3</v>
       </c>
       <c r="C578" t="s">
         <v>8</v>
@@ -12284,17 +12294,17 @@
       <c r="G578" t="s">
         <v>24</v>
       </c>
-      <c r="H578" t="s">
+      <c r="H578" s="26" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="579" spans="1:22" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>34</v>
       </c>
       <c r="B579" s="6">
-        <f>59/758*0.459/3.6</f>
-        <v>9.9241424802110813E-3</v>
+        <f>440/3600</f>
+        <v>0.12222222222222222</v>
       </c>
       <c r="C579" t="s">
         <v>8</v>
@@ -12308,17 +12318,19 @@
       <c r="G579" t="s">
         <v>24</v>
       </c>
-      <c r="H579" s="26" t="s">
+      <c r="H579" t="s">
         <v>245</v>
       </c>
+      <c r="M579" s="27"/>
+      <c r="N579" s="31"/>
     </row>
     <row r="580" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>34</v>
       </c>
       <c r="B580" s="6">
-        <f>440/3600</f>
-        <v>0.12222222222222222</v>
+        <f>0.03/3600</f>
+        <v>8.3333333333333337E-6</v>
       </c>
       <c r="C580" t="s">
         <v>8</v>
@@ -12333,293 +12345,293 @@
         <v>24</v>
       </c>
       <c r="H580" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M580" s="27"/>
       <c r="N580" s="31"/>
     </row>
-    <row r="581" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A581" t="s">
-        <v>34</v>
-      </c>
-      <c r="B581" s="6">
-        <f>0.03/3600</f>
-        <v>8.3333333333333337E-6</v>
-      </c>
-      <c r="C581" t="s">
-        <v>8</v>
-      </c>
-      <c r="D581" t="s">
-        <v>23</v>
-      </c>
-      <c r="F581" t="s">
-        <v>16</v>
-      </c>
-      <c r="G581" t="s">
-        <v>24</v>
-      </c>
-      <c r="H581" t="s">
-        <v>248</v>
-      </c>
-      <c r="M581" s="27"/>
-      <c r="N581" s="31"/>
-    </row>
-    <row r="583" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A583" s="1" t="s">
+    <row r="582" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A582" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B583" s="34" t="s">
-        <v>307</v>
+      <c r="B582" s="34" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="583" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A583" t="s">
+        <v>9</v>
+      </c>
+      <c r="B583" s="35" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="584" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B584" s="35" t="s">
-        <v>255</v>
+        <v>8</v>
       </c>
     </row>
     <row r="585" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B585" s="35" t="s">
-        <v>8</v>
+        <v>294</v>
       </c>
     </row>
     <row r="586" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
+        <v>5</v>
+      </c>
+      <c r="B586" s="35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="587" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A587" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B587" s="35"/>
+    </row>
+    <row r="588" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A588" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B588" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F588" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G588" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B586" s="35" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="587" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A587" t="s">
-        <v>5</v>
-      </c>
-      <c r="B587" s="35" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="588" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A588" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B588" s="35"/>
-    </row>
-    <row r="589" spans="1:22" ht="16" x14ac:dyDescent="0.2">
-      <c r="A589" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B589" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C589" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D589" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E589" s="1" t="s">
+      <c r="H588" s="1"/>
+      <c r="I588" s="1"/>
+      <c r="J588" s="1"/>
+      <c r="K588" s="1"/>
+      <c r="L588" s="1"/>
+      <c r="M588" s="1"/>
+      <c r="N588" s="1"/>
+      <c r="O588" s="1"/>
+      <c r="P588" s="1"/>
+      <c r="Q588" s="1"/>
+      <c r="R588" s="1"/>
+      <c r="S588" s="1"/>
+      <c r="T588" s="1"/>
+      <c r="U588" s="1"/>
+      <c r="V588" s="1"/>
+    </row>
+    <row r="589" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A589" t="str">
+        <f>B582</f>
+        <v>carbon dioxide, captured and stored, by land-use change</v>
+      </c>
+      <c r="B589" s="35">
+        <v>1</v>
+      </c>
+      <c r="C589" t="str">
+        <f>B586</f>
+        <v>kilogram</v>
+      </c>
+      <c r="E589" t="str">
+        <f>B584</f>
+        <v>RER</v>
+      </c>
+      <c r="F589" t="s">
+        <v>15</v>
+      </c>
+      <c r="G589" t="str">
+        <f>B585</f>
+        <v>carbon dioxide, captured</v>
+      </c>
+    </row>
+    <row r="590" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A590" t="s">
+        <v>255</v>
+      </c>
+      <c r="B590" s="36">
+        <v>1</v>
+      </c>
+      <c r="C590" t="s">
+        <v>6</v>
+      </c>
+      <c r="D590" t="s">
+        <v>256</v>
+      </c>
+      <c r="F590" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="592" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A592" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="M592" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="593" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A593" t="s">
         <v>7</v>
       </c>
-      <c r="F589" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G589" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H589" s="1"/>
-      <c r="I589" s="1"/>
-      <c r="J589" s="1"/>
-      <c r="K589" s="1"/>
-      <c r="L589" s="1"/>
-      <c r="M589" s="1"/>
-      <c r="N589" s="1"/>
-      <c r="O589" s="1"/>
-      <c r="P589" s="1"/>
-      <c r="Q589" s="1"/>
-      <c r="R589" s="1"/>
-      <c r="S589" s="1"/>
-      <c r="T589" s="1"/>
-      <c r="U589" s="1"/>
-      <c r="V589" s="1"/>
-    </row>
-    <row r="590" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A590" t="str">
-        <f>B583</f>
-        <v>carbon dioxide, captured and stored, by land-use change</v>
-      </c>
-      <c r="B590" s="35">
-        <v>1</v>
-      </c>
-      <c r="C590" t="str">
-        <f>B587</f>
-        <v>kilogram</v>
-      </c>
-      <c r="E590" t="str">
-        <f>B585</f>
-        <v>RER</v>
-      </c>
-      <c r="F590" t="s">
-        <v>15</v>
-      </c>
-      <c r="G590" t="str">
-        <f>B586</f>
-        <v>carbon dioxide, captured</v>
-      </c>
-    </row>
-    <row r="591" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A591" t="s">
-        <v>256</v>
-      </c>
-      <c r="B591" s="36">
-        <v>1</v>
-      </c>
-      <c r="C591" t="s">
-        <v>6</v>
-      </c>
-      <c r="D591" t="s">
-        <v>257</v>
-      </c>
-      <c r="F591" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="593" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A593" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B593" s="1" t="s">
-        <v>282</v>
+      <c r="B593" t="s">
+        <v>8</v>
       </c>
       <c r="M593" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>7</v>
-      </c>
-      <c r="B594" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="B594">
+        <v>1</v>
       </c>
       <c r="M594" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>1</v>
-      </c>
-      <c r="B595">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B595" t="s">
+        <v>294</v>
       </c>
       <c r="M595" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B596" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
       <c r="M596" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B597" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M597" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B598" t="s">
-        <v>6</v>
+        <v>282</v>
       </c>
       <c r="M598" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B599" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="M599" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A600" t="s">
-        <v>18</v>
-      </c>
-      <c r="B600" t="s">
-        <v>258</v>
+    <row r="600" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A600" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="M600" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="601" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A601" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M601" t="s">
+    <row r="601" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A601" t="s">
+        <v>11</v>
+      </c>
+      <c r="B601" t="s">
+        <v>12</v>
+      </c>
+      <c r="C601" t="s">
+        <v>7</v>
+      </c>
+      <c r="D601" t="s">
+        <v>5</v>
+      </c>
+      <c r="E601" t="s">
+        <v>13</v>
+      </c>
+      <c r="F601" t="s">
+        <v>3</v>
+      </c>
+      <c r="G601" t="s">
+        <v>172</v>
+      </c>
+      <c r="H601" t="s">
+        <v>9</v>
+      </c>
+      <c r="I601" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="602" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A602" t="s">
+        <v>186</v>
+      </c>
+      <c r="B602">
+        <v>1.2300000000000001E-4</v>
+      </c>
+      <c r="D602" t="s">
+        <v>6</v>
+      </c>
+      <c r="E602" t="s">
+        <v>85</v>
+      </c>
+      <c r="F602" t="s">
+        <v>20</v>
+      </c>
+      <c r="G602">
+        <v>0</v>
+      </c>
+      <c r="H602" t="s">
+        <v>258</v>
+      </c>
+      <c r="I602" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A602" t="s">
-        <v>11</v>
-      </c>
-      <c r="B602" t="s">
-        <v>12</v>
-      </c>
-      <c r="C602" t="s">
-        <v>7</v>
-      </c>
-      <c r="D602" t="s">
-        <v>5</v>
-      </c>
-      <c r="E602" t="s">
-        <v>13</v>
-      </c>
-      <c r="F602" t="s">
-        <v>3</v>
-      </c>
-      <c r="G602" t="s">
-        <v>172</v>
-      </c>
-      <c r="H602" t="s">
-        <v>9</v>
-      </c>
-      <c r="I602" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
-        <v>186</v>
-      </c>
-      <c r="B603">
-        <v>1.2300000000000001E-4</v>
+        <v>232</v>
+      </c>
+      <c r="B603" s="38">
+        <v>6.0000000000000002E-6</v>
       </c>
       <c r="D603" t="s">
         <v>6</v>
@@ -12634,24 +12646,24 @@
         <v>0</v>
       </c>
       <c r="H603" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I603" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
-        <v>233</v>
-      </c>
-      <c r="B604" s="38">
-        <v>6.0000000000000002E-6</v>
+        <v>259</v>
+      </c>
+      <c r="B604">
+        <v>8.3199999999999996E-2</v>
       </c>
       <c r="D604" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="E604" t="s">
-        <v>85</v>
+        <v>260</v>
       </c>
       <c r="F604" t="s">
         <v>20</v>
@@ -12660,24 +12672,25 @@
         <v>0</v>
       </c>
       <c r="H604" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I604" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
-        <v>260</v>
-      </c>
-      <c r="B605">
-        <v>8.3199999999999996E-2</v>
+        <v>234</v>
+      </c>
+      <c r="B605" s="33">
+        <f>((B604*1000)-(600*3.78541/1000))/1000</f>
+        <v>8.0928753999999992E-2</v>
       </c>
       <c r="D605" t="s">
         <v>49</v>
       </c>
       <c r="E605" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F605" t="s">
         <v>20</v>
@@ -12686,52 +12699,55 @@
         <v>0</v>
       </c>
       <c r="H605" t="s">
-        <v>262</v>
-      </c>
-      <c r="I605" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A606" t="s">
-        <v>235</v>
-      </c>
-      <c r="B606" s="33">
-        <f>((B605*1000)-(600*3.78541/1000))/1000</f>
-        <v>8.0928753999999992E-2</v>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="606" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A606" t="str">
+        <f>B592</f>
+        <v>carbon dioxide, captured and stored, at wood burning power plant, pipeline 200km, storage 1000m</v>
+      </c>
+      <c r="B606">
+        <v>1</v>
+      </c>
+      <c r="C606" t="s">
+        <v>8</v>
       </c>
       <c r="D606" t="s">
-        <v>49</v>
-      </c>
-      <c r="E606" t="s">
-        <v>263</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G606">
         <v>0</v>
       </c>
       <c r="H606" t="s">
+        <v>183</v>
+      </c>
+      <c r="I606" t="str">
+        <f>B595</f>
+        <v>carbon dioxide, captured</v>
+      </c>
+    </row>
+    <row r="607" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A607" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B607">
+        <v>1</v>
+      </c>
+      <c r="C607" t="s">
+        <v>8</v>
+      </c>
+      <c r="D607" t="s">
+        <v>6</v>
+      </c>
+      <c r="E607" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A607" t="str">
-        <f>B593</f>
-        <v>carbon dioxide, captured and stored, at wood burning power plant, pipeline 200km, storage 1000m</v>
-      </c>
-      <c r="B607">
-        <v>1</v>
-      </c>
-      <c r="C607" t="s">
-        <v>8</v>
-      </c>
-      <c r="D607" t="s">
-        <v>6</v>
-      </c>
       <c r="F607" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G607">
         <v>0</v>
@@ -12739,47 +12755,45 @@
       <c r="H607" t="s">
         <v>183</v>
       </c>
-      <c r="I607" t="str">
-        <f>B596</f>
-        <v>carbon dioxide, captured</v>
-      </c>
-    </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I607" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="608" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A608" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B608">
-        <v>1</v>
-      </c>
-      <c r="C608" t="s">
-        <v>8</v>
-      </c>
-      <c r="D608" t="s">
-        <v>6</v>
-      </c>
-      <c r="E608" t="s">
-        <v>265</v>
-      </c>
-      <c r="F608" t="s">
-        <v>16</v>
-      </c>
-      <c r="G608">
+        <v>34</v>
+      </c>
+      <c r="B608" s="29">
+        <f>188/761*0.459/3.6</f>
+        <v>3.1498028909329831E-2</v>
+      </c>
+      <c r="C608" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D608" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F608" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G608" s="28">
         <v>0</v>
       </c>
-      <c r="H608" t="s">
-        <v>183</v>
-      </c>
-      <c r="I608" t="s">
-        <v>98</v>
-      </c>
+      <c r="H608" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="I608" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="N608" s="29"/>
     </row>
     <row r="609" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A609" s="28" t="s">
         <v>34</v>
       </c>
       <c r="B609" s="29">
-        <f>188/761*0.459/3.6</f>
-        <v>3.1498028909329831E-2</v>
+        <f>123/761*0.459/3.6</f>
+        <v>2.0607752956636003E-2</v>
       </c>
       <c r="C609" s="28" t="s">
         <v>8</v>
@@ -12806,8 +12820,8 @@
         <v>34</v>
       </c>
       <c r="B610" s="29">
-        <f>123/761*0.459/3.6</f>
-        <v>2.0607752956636003E-2</v>
+        <f>575/761*0.459/3.6</f>
+        <v>9.63370565045992E-2</v>
       </c>
       <c r="C610" s="28" t="s">
         <v>8</v>
@@ -12822,57 +12836,58 @@
         <v>0</v>
       </c>
       <c r="H610" s="28" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="I610" s="28" t="s">
         <v>24</v>
       </c>
       <c r="N610" s="29"/>
-    </row>
-    <row r="611" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A611" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B611" s="29">
-        <f>575/761*0.459/3.6</f>
-        <v>9.63370565045992E-2</v>
-      </c>
-      <c r="C611" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D611" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F611" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G611" s="28">
+      <c r="Q610" s="30"/>
+    </row>
+    <row r="611" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A611" t="s">
+        <v>284</v>
+      </c>
+      <c r="B611">
+        <v>1.9099999999999998E-9</v>
+      </c>
+      <c r="C611" t="s">
+        <v>8</v>
+      </c>
+      <c r="D611" t="s">
+        <v>5</v>
+      </c>
+      <c r="E611" t="s">
+        <v>264</v>
+      </c>
+      <c r="F611" t="s">
+        <v>16</v>
+      </c>
+      <c r="G611">
         <v>0</v>
       </c>
-      <c r="H611" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="I611" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="N611" s="29"/>
-      <c r="Q611" s="30"/>
+      <c r="H611" t="s">
+        <v>265</v>
+      </c>
+      <c r="I611" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="612" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="B612">
-        <v>1.9099999999999998E-9</v>
+        <v>1.15E-8</v>
       </c>
       <c r="C612" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D612" t="s">
         <v>5</v>
       </c>
       <c r="E612" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F612" t="s">
         <v>16</v>
@@ -12881,27 +12896,27 @@
         <v>0</v>
       </c>
       <c r="H612" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I612" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
     </row>
     <row r="613" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B613">
-        <v>1.15E-8</v>
+        <v>8.2600000000000002E-5</v>
       </c>
       <c r="C613" t="s">
         <v>17</v>
       </c>
       <c r="D613" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E613" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F613" t="s">
         <v>16</v>
@@ -12910,27 +12925,27 @@
         <v>0</v>
       </c>
       <c r="H613" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I613" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="614" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B614">
-        <v>8.2600000000000002E-5</v>
+        <v>1.9099999999999998E-9</v>
       </c>
       <c r="C614" t="s">
         <v>17</v>
       </c>
       <c r="D614" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E614" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F614" t="s">
         <v>16</v>
@@ -12939,18 +12954,18 @@
         <v>0</v>
       </c>
       <c r="H614" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I614" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="615" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B615">
-        <v>1.9099999999999998E-9</v>
+        <v>6.4400000000000005E-10</v>
       </c>
       <c r="C615" t="s">
         <v>17</v>
@@ -12959,7 +12974,7 @@
         <v>5</v>
       </c>
       <c r="E615" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F615" t="s">
         <v>16</v>
@@ -12968,27 +12983,27 @@
         <v>0</v>
       </c>
       <c r="H615" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I615" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="616" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
-        <v>275</v>
-      </c>
-      <c r="B616">
-        <v>6.4400000000000005E-10</v>
+        <v>90</v>
+      </c>
+      <c r="B616" s="38">
+        <v>1.4E-3</v>
       </c>
       <c r="C616" t="s">
         <v>17</v>
       </c>
       <c r="D616" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E616" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F616" t="s">
         <v>16</v>
@@ -12996,28 +13011,28 @@
       <c r="G616">
         <v>0</v>
       </c>
-      <c r="H616" t="s">
-        <v>276</v>
+      <c r="H616" s="28" t="s">
+        <v>226</v>
       </c>
       <c r="I616" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
     </row>
     <row r="617" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
-        <v>90</v>
-      </c>
-      <c r="B617" s="38">
-        <v>1.4E-3</v>
+        <v>277</v>
+      </c>
+      <c r="B617">
+        <v>1.3399999999999999E-8</v>
       </c>
       <c r="C617" t="s">
         <v>17</v>
       </c>
       <c r="D617" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E617" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F617" t="s">
         <v>16</v>
@@ -13025,28 +13040,28 @@
       <c r="G617">
         <v>0</v>
       </c>
-      <c r="H617" s="28" t="s">
-        <v>227</v>
+      <c r="H617" t="s">
+        <v>278</v>
       </c>
       <c r="I617" t="s">
-        <v>141</v>
+        <v>279</v>
       </c>
     </row>
     <row r="618" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
-        <v>278</v>
+        <v>91</v>
       </c>
       <c r="B618">
-        <v>1.3399999999999999E-8</v>
+        <v>3.0400000000000002E-4</v>
       </c>
       <c r="C618" t="s">
         <v>17</v>
       </c>
       <c r="D618" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E618" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F618" t="s">
         <v>16</v>
@@ -13055,27 +13070,28 @@
         <v>0</v>
       </c>
       <c r="H618" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="I618" t="s">
-        <v>280</v>
+        <v>142</v>
       </c>
     </row>
     <row r="619" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B619">
-        <v>3.0400000000000002E-4</v>
+        <f>-1*B616</f>
+        <v>-1.4E-3</v>
       </c>
       <c r="C619" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D619" t="s">
         <v>6</v>
       </c>
       <c r="E619" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="F619" t="s">
         <v>16</v>
@@ -13084,218 +13100,225 @@
         <v>0</v>
       </c>
       <c r="H619" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="I619" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="620" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="B620">
-        <f>-1*B617</f>
-        <v>-1.4E-3</v>
-      </c>
-      <c r="C620" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D620" t="s">
         <v>6</v>
       </c>
       <c r="E620" t="s">
-        <v>281</v>
+        <v>37</v>
       </c>
       <c r="F620" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G620">
         <v>0</v>
       </c>
       <c r="H620" t="s">
-        <v>259</v>
-      </c>
-      <c r="I620" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="621" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A621" t="s">
-        <v>39</v>
-      </c>
-      <c r="B621">
-        <v>1</v>
-      </c>
-      <c r="D621" t="s">
-        <v>6</v>
-      </c>
-      <c r="E621" t="s">
-        <v>37</v>
-      </c>
-      <c r="F621" t="s">
-        <v>20</v>
-      </c>
-      <c r="G621">
+        <v>283</v>
+      </c>
+      <c r="M620" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="622" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A622" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H621" t="s">
-        <v>284</v>
-      </c>
-      <c r="M621" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="623" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A623" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B623" s="1" t="s">
-        <v>308</v>
+      <c r="B622" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="623" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A623" t="s">
+        <v>1</v>
+      </c>
+      <c r="B623">
+        <v>1</v>
       </c>
     </row>
     <row r="624" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
-        <v>1</v>
-      </c>
-      <c r="B624">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B624" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="625" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B625" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
     </row>
     <row r="626" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B626" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="627" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B627" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="628" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B628" t="s">
-        <v>8</v>
+        <v>308</v>
       </c>
     </row>
     <row r="629" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B629" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A630" t="s">
+    <row r="630" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A630" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A631" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B631" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D631" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E631" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F631" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H631" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B630" t="s">
+      <c r="I631" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="J631" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="K631" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L631" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="M631" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A632" t="str">
+        <f>B622</f>
+        <v>carbon dioxide, captured and stored, from a hydrogen production plant using steam methane reforming of biomethane</v>
+      </c>
+      <c r="B632">
+        <v>1</v>
+      </c>
+      <c r="C632" t="s">
+        <v>8</v>
+      </c>
+      <c r="D632" t="s">
+        <v>6</v>
+      </c>
+      <c r="F632" t="s">
+        <v>15</v>
+      </c>
+      <c r="G632" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A633" t="s">
+        <v>34</v>
+      </c>
+      <c r="B633" s="23">
+        <f>AVERAGE(0.15,0.25)</f>
+        <v>0.2</v>
+      </c>
+      <c r="C633" t="s">
+        <v>8</v>
+      </c>
+      <c r="D633" t="s">
+        <v>23</v>
+      </c>
+      <c r="F633" t="s">
+        <v>16</v>
+      </c>
+      <c r="G633" t="s">
+        <v>24</v>
+      </c>
+      <c r="H633" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="631" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A631" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A632" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B632" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C632" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D632" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E632" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F632" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G632" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H632" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I632" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J632" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="K632" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="L632" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="M632" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A633" t="str">
-        <f>B623</f>
-        <v>carbon dioxide, captured and stored, from a hydrogen production plant using steam methane reforming of biomethane</v>
-      </c>
-      <c r="B633">
-        <v>1</v>
-      </c>
-      <c r="C633" t="s">
-        <v>8</v>
-      </c>
-      <c r="D633" t="s">
-        <v>6</v>
-      </c>
-      <c r="F633" t="s">
-        <v>15</v>
-      </c>
-      <c r="G633" t="s">
-        <v>295</v>
+      <c r="I633">
+        <v>5</v>
+      </c>
+      <c r="J633" s="23">
+        <f>B633</f>
+        <v>0.2</v>
+      </c>
+      <c r="K633">
+        <v>0.15</v>
+      </c>
+      <c r="L633">
+        <v>0.25</v>
       </c>
     </row>
     <row r="634" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
-        <v>34</v>
-      </c>
-      <c r="B634" s="23">
-        <f>AVERAGE(0.15,0.25)</f>
-        <v>0.2</v>
+        <v>31</v>
+      </c>
+      <c r="B634">
+        <f>AVERAGE(1,2)</f>
+        <v>1.5</v>
       </c>
       <c r="C634" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D634" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>16</v>
       </c>
       <c r="G634" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H634" t="s">
         <v>311</v>
@@ -13305,34 +13328,34 @@
       </c>
       <c r="J634" s="23">
         <f>B634</f>
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="K634">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="L634">
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="635" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B635">
-        <f>AVERAGE(1,2)</f>
-        <v>1.5</v>
+        <f>AVERAGE(0.1,0.15)</f>
+        <v>0.125</v>
       </c>
       <c r="C635" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D635" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F635" t="s">
         <v>16</v>
       </c>
       <c r="G635" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H635" t="s">
         <v>312</v>
@@ -13342,34 +13365,33 @@
       </c>
       <c r="J635" s="23">
         <f>B635</f>
-        <v>1.5</v>
+        <v>0.125</v>
       </c>
       <c r="K635">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L635">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A636" t="s">
-        <v>34</v>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="636" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A636" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="B636">
-        <f>AVERAGE(0.1,0.15)</f>
-        <v>0.125</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C636" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D636" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F636" t="s">
         <v>16</v>
       </c>
-      <c r="G636" t="s">
-        <v>24</v>
+      <c r="G636" s="15" t="s">
+        <v>141</v>
       </c>
       <c r="H636" t="s">
         <v>313</v>
@@ -13379,33 +13401,34 @@
       </c>
       <c r="J636" s="23">
         <f>B636</f>
-        <v>0.125</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="K636">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="L636">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A637" t="s">
+        <v>34</v>
+      </c>
+      <c r="B637">
+        <f>AVERAGE(0.08,0.12)</f>
         <v>0.1</v>
       </c>
-      <c r="L636">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="637" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A637" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B637">
-        <v>5.0000000000000001E-3</v>
-      </c>
       <c r="C637" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D637" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F637" t="s">
         <v>16</v>
       </c>
-      <c r="G637" s="15" t="s">
-        <v>141</v>
+      <c r="G637" t="s">
+        <v>24</v>
       </c>
       <c r="H637" t="s">
         <v>314</v>
@@ -13415,61 +13438,47 @@
       </c>
       <c r="J637" s="23">
         <f>B637</f>
-        <v>5.0000000000000001E-3</v>
+        <v>0.1</v>
       </c>
       <c r="K637">
-        <v>4.0000000000000001E-3</v>
+        <v>0.08</v>
       </c>
       <c r="L637">
-        <v>6.0000000000000001E-3</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="638" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
-        <v>34</v>
-      </c>
-      <c r="B638">
-        <f>AVERAGE(0.08,0.12)</f>
-        <v>0.1</v>
+        <v>42</v>
+      </c>
+      <c r="B638" s="6">
+        <v>1.2E-5</v>
       </c>
       <c r="C638" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D638" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F638" t="s">
         <v>16</v>
       </c>
       <c r="G638" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H638" t="s">
         <v>315</v>
       </c>
-      <c r="I638">
-        <v>5</v>
-      </c>
-      <c r="J638" s="23">
-        <f>B638</f>
-        <v>0.1</v>
-      </c>
-      <c r="K638">
-        <v>0.08</v>
-      </c>
-      <c r="L638">
-        <v>0.12</v>
-      </c>
     </row>
     <row r="639" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B639" s="6">
-        <v>1.2E-5</v>
+        <v>3.9999999999999998E-6</v>
       </c>
       <c r="C639" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D639" t="s">
         <v>6</v>
@@ -13478,7 +13487,7 @@
         <v>16</v>
       </c>
       <c r="G639" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H639" t="s">
         <v>316</v>
@@ -13486,312 +13495,289 @@
     </row>
     <row r="640" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
-        <v>43</v>
+        <v>195</v>
       </c>
       <c r="B640" s="6">
-        <v>3.9999999999999998E-6</v>
+        <f>B634*-1/1000</f>
+        <v>-1.5E-3</v>
       </c>
       <c r="C640" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D640" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F640" t="s">
         <v>16</v>
       </c>
       <c r="G640" t="s">
-        <v>50</v>
-      </c>
-      <c r="H640" t="s">
-        <v>317</v>
+        <v>149</v>
       </c>
     </row>
     <row r="641" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A641" t="s">
-        <v>195</v>
-      </c>
-      <c r="B641" s="6">
-        <f>B635*-1/1000</f>
-        <v>-1.5E-3</v>
+      <c r="A641" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B641">
+        <v>1</v>
       </c>
       <c r="C641" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="D641" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="F641" t="s">
         <v>16</v>
       </c>
       <c r="G641" t="s">
-        <v>149</v>
+        <v>98</v>
+      </c>
+      <c r="H641" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="642" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A642" s="28" t="s">
-        <v>97</v>
+      <c r="A642" t="s">
+        <v>39</v>
       </c>
       <c r="B642">
         <v>1</v>
       </c>
-      <c r="C642" t="s">
-        <v>8</v>
-      </c>
       <c r="D642" t="s">
         <v>6</v>
       </c>
+      <c r="E642" t="s">
+        <v>37</v>
+      </c>
       <c r="F642" t="s">
-        <v>16</v>
-      </c>
-      <c r="G642" t="s">
-        <v>98</v>
+        <v>20</v>
+      </c>
+      <c r="G642">
+        <v>0</v>
       </c>
       <c r="H642" t="s">
+        <v>283</v>
+      </c>
+      <c r="M642" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A643" t="s">
-        <v>39</v>
-      </c>
-      <c r="B643">
-        <v>1</v>
-      </c>
-      <c r="D643" t="s">
-        <v>6</v>
-      </c>
-      <c r="E643" t="s">
-        <v>37</v>
-      </c>
-      <c r="F643" t="s">
-        <v>20</v>
-      </c>
-      <c r="G643">
+    <row r="644" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A644" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H643" t="s">
-        <v>284</v>
-      </c>
-      <c r="M643" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="645" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A645" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B645" s="1" t="s">
-        <v>319</v>
+      <c r="B644" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A645" t="s">
+        <v>1</v>
+      </c>
+      <c r="B645">
+        <v>1</v>
       </c>
     </row>
     <row r="646" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
-        <v>1</v>
-      </c>
-      <c r="B646">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="B646" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="647" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B647" t="s">
-        <v>295</v>
+        <v>4</v>
       </c>
     </row>
     <row r="648" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B648" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="649" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B649" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="650" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
-        <v>7</v>
-      </c>
-      <c r="B650" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="B650" s="6" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="651" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
-        <v>18</v>
-      </c>
-      <c r="B651" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B651" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A652" t="s">
+    <row r="652" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A652" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A653" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B653" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D653" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E653" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F653" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G653" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H653" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B652" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="653" spans="1:13" ht="16" x14ac:dyDescent="0.2">
-      <c r="A653" s="1" t="s">
-        <v>10</v>
+      <c r="I653" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="J653" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="K653" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="L653" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="M653" s="5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="654" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A654" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B654" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C654" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D654" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E654" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F654" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G654" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H654" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I654" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J654" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="K654" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="L654" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="M654" s="5" t="s">
-        <v>182</v>
+      <c r="A654" t="str">
+        <f>B644</f>
+        <v>carbon dioxide, captured and stored, from a biomass fermentation plant</v>
+      </c>
+      <c r="B654">
+        <v>1</v>
+      </c>
+      <c r="C654" t="s">
+        <v>8</v>
+      </c>
+      <c r="D654" t="s">
+        <v>6</v>
+      </c>
+      <c r="F654" t="s">
+        <v>15</v>
+      </c>
+      <c r="G654" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="655" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A655" t="str">
-        <f>B645</f>
-        <v>carbon dioxide, captured and stored, from a biomass fermentation plant</v>
-      </c>
-      <c r="B655">
-        <v>1</v>
+      <c r="A655" t="s">
+        <v>34</v>
+      </c>
+      <c r="B655" s="23">
+        <v>0.11</v>
       </c>
       <c r="C655" t="s">
         <v>8</v>
       </c>
       <c r="D655" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F655" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G655" t="s">
-        <v>295</v>
+        <v>24</v>
+      </c>
+      <c r="H655" t="s">
+        <v>310</v>
+      </c>
+      <c r="I655">
+        <v>5</v>
+      </c>
+      <c r="J655" s="23">
+        <f>B655</f>
+        <v>0.11</v>
+      </c>
+      <c r="K655">
+        <v>0.1</v>
+      </c>
+      <c r="L655">
+        <v>0.2</v>
       </c>
     </row>
     <row r="656" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A656" t="s">
-        <v>34</v>
-      </c>
-      <c r="B656" s="23">
-        <v>0.11</v>
+      <c r="A656" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B656">
+        <v>1</v>
       </c>
       <c r="C656" t="s">
         <v>8</v>
       </c>
       <c r="D656" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F656" t="s">
         <v>16</v>
       </c>
       <c r="G656" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="H656" t="s">
-        <v>311</v>
-      </c>
-      <c r="I656">
-        <v>5</v>
-      </c>
-      <c r="J656" s="23">
-        <f>B656</f>
-        <v>0.11</v>
-      </c>
-      <c r="K656">
-        <v>0.1</v>
-      </c>
-      <c r="L656">
-        <v>0.2</v>
+        <v>183</v>
       </c>
     </row>
     <row r="657" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A657" s="28" t="s">
-        <v>97</v>
+      <c r="A657" t="s">
+        <v>39</v>
       </c>
       <c r="B657">
         <v>1</v>
       </c>
-      <c r="C657" t="s">
-        <v>8</v>
-      </c>
       <c r="D657" t="s">
         <v>6</v>
       </c>
+      <c r="E657" t="s">
+        <v>37</v>
+      </c>
       <c r="F657" t="s">
-        <v>16</v>
-      </c>
-      <c r="G657" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="H657" t="s">
+        <v>283</v>
+      </c>
+      <c r="M657" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A658" t="s">
-        <v>39</v>
-      </c>
-      <c r="B658">
-        <v>1</v>
-      </c>
-      <c r="D658" t="s">
-        <v>6</v>
-      </c>
-      <c r="E658" t="s">
-        <v>37</v>
-      </c>
-      <c r="F658" t="s">
-        <v>20</v>
-      </c>
-      <c r="H658" t="s">
-        <v>284</v>
-      </c>
-      <c r="M658" t="s">
-        <v>183</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V621" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:V620" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-carbon-capture.xlsx
+++ b/premise/data/additional_inventories/lci-carbon-capture.xlsx
@@ -1503,9 +1503,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V657"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
@@ -1521,7 +1521,7 @@
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ns3:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
@@ -1529,10 +1529,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ns3:dyDescent="0.2">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ns3:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1596,12 +1596,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ns3:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ns3:dyDescent="0.2">
       <c r="A13" t="str">
         <f>B3</f>
         <v>carbon dioxide, captured, with a solvent-based direct air capture system, 1MtCO2</v>
@@ -1663,7 +1663,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>6.6666666666666669E-11</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ns3:dyDescent="0.2">
       <c r="A17" t="s">
         <v>164</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="16" ns3:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>166</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ns3:dyDescent="0.2">
       <c r="A19" t="s">
         <v>73</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>317</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="16" ns3:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ns3:dyDescent="0.2">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>2</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -2017,12 +2017,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ns3:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>11</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>287</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>62</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>6.6666666666666669E-11</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>31</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>164</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A40" s="9" t="s">
         <v>166</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>73</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>77</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>317</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>97</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ns3:dyDescent="0.2">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>1</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>2</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" ns3:dyDescent="0.2">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -2460,12 +2460,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ns3:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>11</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>295</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>6.6666666666666669E-11</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>31</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ns3:dyDescent="0.2">
       <c r="A62" t="s">
         <v>164</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A63" s="9" t="s">
         <v>166</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>73</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>77</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>187</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>1</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" ns3:dyDescent="0.2">
       <c r="A72" t="s">
         <v>2</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ns3:dyDescent="0.2">
       <c r="A73" t="s">
         <v>3</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" ns3:dyDescent="0.2">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ns3:dyDescent="0.2">
       <c r="A75" t="s">
         <v>7</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" ns3:dyDescent="0.2">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" ns3:dyDescent="0.2">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -2880,12 +2880,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" ns3:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>11</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" ns3:dyDescent="0.2">
       <c r="A80" t="s">
         <v>288</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>62</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>6.6666666666666669E-11</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>64</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>31</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>164</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A85" s="9" t="s">
         <v>166</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>73</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ns3:dyDescent="0.2">
       <c r="A87" t="s">
         <v>74</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" ns3:dyDescent="0.2">
       <c r="A88" t="s">
         <v>77</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" ns3:dyDescent="0.2">
       <c r="A89" t="s">
         <v>187</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A90" t="s">
         <v>97</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ns3:dyDescent="0.2">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>0</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ns3:dyDescent="0.2">
       <c r="A94" t="s">
         <v>1</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>2</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>3</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" ns3:dyDescent="0.2">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>9</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -3323,12 +3323,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" ns3:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>11</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" ns3:dyDescent="0.2">
       <c r="A103" t="s">
         <v>296</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>62</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>6.6666666666666669E-11</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>64</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" ns3:dyDescent="0.2">
       <c r="A106" t="s">
         <v>31</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" ns3:dyDescent="0.2">
       <c r="A107" t="s">
         <v>164</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A108" s="9" t="s">
         <v>166</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>73</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>74</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>77</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>77</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>0.80172413793103448</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>39</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>0</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" ns3:dyDescent="0.2">
       <c r="A116" t="s">
         <v>1</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" ns3:dyDescent="0.2">
       <c r="A117" t="s">
         <v>2</v>
       </c>
@@ -3706,7 +3706,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" ns3:dyDescent="0.2">
       <c r="A118" t="s">
         <v>3</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" ns3:dyDescent="0.2">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>9</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -3746,12 +3746,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" ns3:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>11</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" ns3:dyDescent="0.2">
       <c r="A125" t="s">
         <v>289</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>62</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>6.6666666666666669E-11</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" ns3:dyDescent="0.2">
       <c r="A127" t="s">
         <v>64</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" ns3:dyDescent="0.2">
       <c r="A128" t="s">
         <v>31</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ns3:dyDescent="0.2">
       <c r="A129" t="s">
         <v>164</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="16" ns3:dyDescent="0.2">
       <c r="A130" s="9" t="s">
         <v>166</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>73</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ns3:dyDescent="0.2">
       <c r="A132" t="s">
         <v>74</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ns3:dyDescent="0.2">
       <c r="A133" t="s">
         <v>77</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ns3:dyDescent="0.2">
       <c r="A134" t="s">
         <v>77</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>0.80172413793103448</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="16" ns3:dyDescent="0.2">
       <c r="A135" t="s">
         <v>97</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>39</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="14" customHeight="1" ns3:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>0</v>
       </c>
@@ -4136,7 +4136,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>1</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="16" ns3:dyDescent="0.2">
       <c r="A140" t="s">
         <v>2</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ns3:dyDescent="0.2">
       <c r="A141" t="s">
         <v>3</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ns3:dyDescent="0.2">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>7</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" ns3:dyDescent="0.2">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -4192,12 +4192,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" ns3:dyDescent="0.2">
       <c r="A147" t="s">
         <v>11</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A148" t="s">
         <v>62</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" ns3:dyDescent="0.2">
       <c r="A149" t="s">
         <v>194</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" ns3:dyDescent="0.2">
       <c r="A150" t="s">
         <v>42</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" ns3:dyDescent="0.2">
       <c r="A151" t="s">
         <v>43</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A152" t="s">
         <v>44</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" ns3:dyDescent="0.2">
       <c r="A153" t="s">
         <v>45</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" ns3:dyDescent="0.2">
       <c r="A154" t="s">
         <v>46</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" ns3:dyDescent="0.2">
       <c r="A155" t="s">
         <v>47</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>194</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>43</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" ns3:dyDescent="0.2">
       <c r="A158" t="s">
         <v>194</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" ns3:dyDescent="0.2">
       <c r="A159" t="s">
         <v>42</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>55</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>194</v>
       </c>
@@ -4544,7 +4544,7 @@
       <c r="Q161" s="3"/>
       <c r="S161" s="3"/>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>58</v>
       </c>
@@ -4569,7 +4569,7 @@
       <c r="Q162" s="4"/>
       <c r="S162" s="4"/>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:19" ns3:dyDescent="0.2">
       <c r="A163" t="s">
         <v>42</v>
       </c>
@@ -4594,7 +4594,7 @@
       <c r="Q163" s="3"/>
       <c r="S163" s="3"/>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19" ns3:dyDescent="0.2">
       <c r="A164" t="s">
         <v>43</v>
       </c>
@@ -4619,7 +4619,7 @@
       <c r="Q164" s="3"/>
       <c r="S164" s="3"/>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19" ns3:dyDescent="0.2">
       <c r="A165" t="s">
         <v>59</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19" ns3:dyDescent="0.2">
       <c r="A166" t="s">
         <v>200</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19" ns3:dyDescent="0.2">
       <c r="A167" t="s">
         <v>203</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19" ns3:dyDescent="0.2">
       <c r="A168" t="s">
         <v>207</v>
       </c>
@@ -4705,11 +4705,11 @@
         <v>206</v>
       </c>
     </row>
-    <row r="169" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
     </row>
-    <row r="170" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>0</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:19" ns3:dyDescent="0.2">
       <c r="A171" t="s">
         <v>1</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A172" t="s">
         <v>2</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:19" ns3:dyDescent="0.2">
       <c r="A173" t="s">
         <v>3</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:19" ns3:dyDescent="0.2">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:19" ns3:dyDescent="0.2">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:19" ns3:dyDescent="0.2">
       <c r="A176" t="s">
         <v>9</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:19" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -4773,12 +4773,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:19" ns3:dyDescent="0.2">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A180" t="s">
         <v>64</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:19" ns3:dyDescent="0.2">
       <c r="A181" t="s">
         <v>65</v>
       </c>
@@ -4847,7 +4847,7 @@
       <c r="Q181" s="4"/>
       <c r="S181" s="4"/>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:19" ns3:dyDescent="0.2">
       <c r="A182" t="s">
         <v>66</v>
       </c>
@@ -4870,7 +4870,7 @@
       <c r="Q182" s="3"/>
       <c r="S182" s="3"/>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:19" ns3:dyDescent="0.2">
       <c r="A183" t="s">
         <v>67</v>
       </c>
@@ -4893,7 +4893,7 @@
       <c r="Q183" s="3"/>
       <c r="S183" s="3"/>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:19" ns3:dyDescent="0.2">
       <c r="A184" t="s">
         <v>68</v>
       </c>
@@ -4915,7 +4915,7 @@
       <c r="H184" s="12"/>
       <c r="I184" s="13"/>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:19" ns3:dyDescent="0.2">
       <c r="A185" t="s">
         <v>69</v>
       </c>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H185" s="12"/>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:19" ns3:dyDescent="0.2">
       <c r="A186" t="s">
         <v>70</v>
       </c>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H186" s="12"/>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:19" ns3:dyDescent="0.2">
       <c r="A187" t="s">
         <v>71</v>
       </c>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="H187" s="12"/>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:19" ns3:dyDescent="0.2">
       <c r="A188" t="s">
         <v>72</v>
       </c>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="H188" s="12"/>
     </row>
-    <row r="190" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>0</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:19" ns3:dyDescent="0.2">
       <c r="A191" t="s">
         <v>1</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:19" ns3:dyDescent="0.2">
       <c r="A192" t="s">
         <v>2</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" ns3:dyDescent="0.2">
       <c r="A193" t="s">
         <v>3</v>
       </c>
@@ -5031,7 +5031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" ns3:dyDescent="0.2">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" ns3:dyDescent="0.2">
       <c r="A195" t="s">
         <v>7</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" ns3:dyDescent="0.2">
       <c r="A196" t="s">
         <v>9</v>
       </c>
@@ -5055,7 +5055,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" ns3:dyDescent="0.2">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -5063,12 +5063,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" ns3:dyDescent="0.2">
       <c r="A199" s="5" t="s">
         <v>11</v>
       </c>
@@ -5109,7 +5109,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" ns3:dyDescent="0.2">
       <c r="A200" t="s">
         <v>297</v>
       </c>
@@ -5129,7 +5129,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="201" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A201" t="s">
         <v>79</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" ns3:dyDescent="0.2">
       <c r="A202" t="s">
         <v>114</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" ns3:dyDescent="0.2">
       <c r="A203" t="s">
         <v>129</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" ns3:dyDescent="0.2">
       <c r="A204" t="s">
         <v>77</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" ns3:dyDescent="0.2">
       <c r="A205" t="s">
         <v>317</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" ns3:dyDescent="0.2">
       <c r="A206" t="s">
         <v>39</v>
       </c>
@@ -5335,7 +5335,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="208" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>0</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" ns3:dyDescent="0.2">
       <c r="A209" t="s">
         <v>1</v>
       </c>
@@ -5351,7 +5351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" ns3:dyDescent="0.2">
       <c r="A210" t="s">
         <v>2</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" ns3:dyDescent="0.2">
       <c r="A211" t="s">
         <v>3</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" ns3:dyDescent="0.2">
       <c r="A212" t="s">
         <v>5</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" ns3:dyDescent="0.2">
       <c r="A213" t="s">
         <v>7</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" ns3:dyDescent="0.2">
       <c r="A214" t="s">
         <v>9</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" ns3:dyDescent="0.2">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -5399,12 +5399,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="216" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A216" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" ns3:dyDescent="0.2">
       <c r="A217" t="s">
         <v>11</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" ns3:dyDescent="0.2">
       <c r="A218" t="s">
         <v>290</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A219" t="s">
         <v>79</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" ns3:dyDescent="0.2">
       <c r="A220" t="s">
         <v>114</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" ns3:dyDescent="0.2">
       <c r="A221" t="s">
         <v>129</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" ns3:dyDescent="0.2">
       <c r="A222" t="s">
         <v>77</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" ns3:dyDescent="0.2">
       <c r="A223" t="s">
         <v>317</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="224" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A224" t="s">
         <v>97</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" ns3:dyDescent="0.2">
       <c r="A225" t="s">
         <v>39</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="227" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>0</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" ns3:dyDescent="0.2">
       <c r="A228" t="s">
         <v>1</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" ns3:dyDescent="0.2">
       <c r="A229" t="s">
         <v>2</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" ns3:dyDescent="0.2">
       <c r="A230" t="s">
         <v>3</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" ns3:dyDescent="0.2">
       <c r="A231" t="s">
         <v>5</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" ns3:dyDescent="0.2">
       <c r="A232" t="s">
         <v>7</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" ns3:dyDescent="0.2">
       <c r="A233" t="s">
         <v>9</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" ns3:dyDescent="0.2">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -5758,12 +5758,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" ns3:dyDescent="0.2">
       <c r="A236" s="5" t="s">
         <v>11</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" ns3:dyDescent="0.2">
       <c r="A237" t="s">
         <v>298</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A238" t="s">
         <v>79</v>
       </c>
@@ -5859,7 +5859,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" ns3:dyDescent="0.2">
       <c r="A239" t="s">
         <v>114</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" ns3:dyDescent="0.2">
       <c r="A240" t="s">
         <v>129</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" ns3:dyDescent="0.2">
       <c r="A241" t="s">
         <v>77</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" ns3:dyDescent="0.2">
       <c r="A242" t="s">
         <v>249</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" ns3:dyDescent="0.2">
       <c r="A243" t="s">
         <v>39</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="245" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>0</v>
       </c>
@@ -6038,7 +6038,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" ns3:dyDescent="0.2">
       <c r="A246" t="s">
         <v>1</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" ns3:dyDescent="0.2">
       <c r="A247" t="s">
         <v>2</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" ns3:dyDescent="0.2">
       <c r="A248" t="s">
         <v>3</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" ns3:dyDescent="0.2">
       <c r="A249" t="s">
         <v>5</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" ns3:dyDescent="0.2">
       <c r="A250" t="s">
         <v>7</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" ns3:dyDescent="0.2">
       <c r="A251" t="s">
         <v>9</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" ns3:dyDescent="0.2">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -6094,12 +6094,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="253" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A253" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" ns3:dyDescent="0.2">
       <c r="A254" t="s">
         <v>11</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" ns3:dyDescent="0.2">
       <c r="A255" t="s">
         <v>291</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="256" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A256" t="s">
         <v>79</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" ns3:dyDescent="0.2">
       <c r="A257" t="s">
         <v>114</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" ns3:dyDescent="0.2">
       <c r="A258" t="s">
         <v>129</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" ns3:dyDescent="0.2">
       <c r="A259" t="s">
         <v>77</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" ns3:dyDescent="0.2">
       <c r="A260" t="s">
         <v>249</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A261" t="s">
         <v>97</v>
       </c>
@@ -6369,7 +6369,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" ns3:dyDescent="0.2">
       <c r="A262" t="s">
         <v>39</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="264" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A264" s="1" t="s">
         <v>0</v>
       </c>
@@ -6397,7 +6397,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" ns3:dyDescent="0.2">
       <c r="A265" t="s">
         <v>1</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" ns3:dyDescent="0.2">
       <c r="A266" t="s">
         <v>2</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" ns3:dyDescent="0.2">
       <c r="A267" t="s">
         <v>3</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" ns3:dyDescent="0.2">
       <c r="A268" t="s">
         <v>5</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" ns3:dyDescent="0.2">
       <c r="A269" t="s">
         <v>7</v>
       </c>
@@ -6437,7 +6437,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" ns3:dyDescent="0.2">
       <c r="A270" t="s">
         <v>9</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" ns3:dyDescent="0.2">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -6453,12 +6453,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A272" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" ns3:dyDescent="0.2">
       <c r="A273" s="5" t="s">
         <v>11</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" ns3:dyDescent="0.2">
       <c r="A274" t="s">
         <v>299</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A275" t="s">
         <v>79</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" ns3:dyDescent="0.2">
       <c r="A276" t="s">
         <v>114</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" ns3:dyDescent="0.2">
       <c r="A277" t="s">
         <v>129</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" ns3:dyDescent="0.2">
       <c r="A278" t="s">
         <v>77</v>
       </c>
@@ -6670,7 +6670,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" ns3:dyDescent="0.2">
       <c r="A279" t="s">
         <v>187</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" ns3:dyDescent="0.2">
       <c r="A280" t="s">
         <v>39</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A282" s="1" t="s">
         <v>0</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" ns3:dyDescent="0.2">
       <c r="A283" t="s">
         <v>1</v>
       </c>
@@ -6741,7 +6741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" ns3:dyDescent="0.2">
       <c r="A284" t="s">
         <v>2</v>
       </c>
@@ -6749,7 +6749,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" ns3:dyDescent="0.2">
       <c r="A285" t="s">
         <v>3</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" ns3:dyDescent="0.2">
       <c r="A286" t="s">
         <v>5</v>
       </c>
@@ -6765,7 +6765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" ns3:dyDescent="0.2">
       <c r="A287" t="s">
         <v>7</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" ns3:dyDescent="0.2">
       <c r="A288" t="s">
         <v>9</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" ns3:dyDescent="0.2">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -6789,12 +6789,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A290" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" ns3:dyDescent="0.2">
       <c r="A291" t="s">
         <v>11</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" ns3:dyDescent="0.2">
       <c r="A292" t="s">
         <v>292</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A293" t="s">
         <v>79</v>
       </c>
@@ -6890,7 +6890,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" ns3:dyDescent="0.2">
       <c r="A294" t="s">
         <v>114</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" ns3:dyDescent="0.2">
       <c r="A295" t="s">
         <v>129</v>
       </c>
@@ -6971,7 +6971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" ns3:dyDescent="0.2">
       <c r="A296" t="s">
         <v>77</v>
       </c>
@@ -7006,7 +7006,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" ns3:dyDescent="0.2">
       <c r="A297" t="s">
         <v>187</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A298" t="s">
         <v>97</v>
       </c>
@@ -7064,7 +7064,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" ns3:dyDescent="0.2">
       <c r="A299" t="s">
         <v>39</v>
       </c>
@@ -7084,7 +7084,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>0</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" ns3:dyDescent="0.2">
       <c r="A302" t="s">
         <v>1</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" ns3:dyDescent="0.2">
       <c r="A303" t="s">
         <v>2</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" ns3:dyDescent="0.2">
       <c r="A304" t="s">
         <v>3</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" ns3:dyDescent="0.2">
       <c r="A305" t="s">
         <v>5</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" ns3:dyDescent="0.2">
       <c r="A306" t="s">
         <v>7</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" ns3:dyDescent="0.2">
       <c r="A307" t="s">
         <v>9</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" ns3:dyDescent="0.2">
       <c r="A308" t="s">
         <v>18</v>
       </c>
@@ -7148,12 +7148,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A309" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" ns3:dyDescent="0.2">
       <c r="A310" s="5" t="s">
         <v>11</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" ns3:dyDescent="0.2">
       <c r="A311" t="s">
         <v>300</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A312" t="s">
         <v>79</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" ns3:dyDescent="0.2">
       <c r="A313" t="s">
         <v>114</v>
       </c>
@@ -7288,7 +7288,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" ns3:dyDescent="0.2">
       <c r="A314" t="s">
         <v>129</v>
       </c>
@@ -7330,7 +7330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" ns3:dyDescent="0.2">
       <c r="A315" t="s">
         <v>77</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" ns3:dyDescent="0.2">
       <c r="A316" t="s">
         <v>77</v>
       </c>
@@ -7404,7 +7404,7 @@
         <v>1.1398467432950192</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" ns3:dyDescent="0.2">
       <c r="A317" t="s">
         <v>39</v>
       </c>
@@ -7424,7 +7424,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="319" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>0</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" ns3:dyDescent="0.2">
       <c r="A320" t="s">
         <v>1</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" ns3:dyDescent="0.2">
       <c r="A321" t="s">
         <v>2</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" ns3:dyDescent="0.2">
       <c r="A322" t="s">
         <v>3</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" ns3:dyDescent="0.2">
       <c r="A323" t="s">
         <v>5</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" ns3:dyDescent="0.2">
       <c r="A324" t="s">
         <v>7</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" ns3:dyDescent="0.2">
       <c r="A325" t="s">
         <v>9</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" ns3:dyDescent="0.2">
       <c r="A326" t="s">
         <v>18</v>
       </c>
@@ -7488,12 +7488,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A327" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" ns3:dyDescent="0.2">
       <c r="A328" t="s">
         <v>11</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" ns3:dyDescent="0.2">
       <c r="A329" t="s">
         <v>293</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A330" t="s">
         <v>79</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13" ns3:dyDescent="0.2">
       <c r="A331" t="s">
         <v>114</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>6.6666666666666664E-10</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" ns3:dyDescent="0.2">
       <c r="A332" t="s">
         <v>129</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13" ns3:dyDescent="0.2">
       <c r="A333" t="s">
         <v>77</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" ns3:dyDescent="0.2">
       <c r="A334" t="s">
         <v>77</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>1.1398467432950192</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A335" t="s">
         <v>97</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" ns3:dyDescent="0.2">
       <c r="A336" t="s">
         <v>39</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="338" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A338" s="1" t="s">
         <v>0</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:8" ns3:dyDescent="0.2">
       <c r="A339" t="s">
         <v>1</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A340" t="s">
         <v>2</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:8" ns3:dyDescent="0.2">
       <c r="A341" t="s">
         <v>3</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:8" ns3:dyDescent="0.2">
       <c r="A342" t="s">
         <v>5</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:8" ns3:dyDescent="0.2">
       <c r="A343" t="s">
         <v>7</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:8" ns3:dyDescent="0.2">
       <c r="A344" t="s">
         <v>9</v>
       </c>
@@ -7843,7 +7843,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:8" ns3:dyDescent="0.2">
       <c r="A345" t="s">
         <v>18</v>
       </c>
@@ -7851,12 +7851,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A346" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:8" ns3:dyDescent="0.2">
       <c r="A347" t="s">
         <v>11</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="348" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A348" t="s">
         <v>114</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:8" ns3:dyDescent="0.2">
       <c r="A349" t="s">
         <v>194</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:8" ns3:dyDescent="0.2">
       <c r="A350" t="s">
         <v>103</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:8" ns3:dyDescent="0.2">
       <c r="A351" t="s">
         <v>194</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:8" ns3:dyDescent="0.2">
       <c r="A352" t="s">
         <v>103</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:8" ns3:dyDescent="0.2">
       <c r="A353" t="s">
         <v>42</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:8" ns3:dyDescent="0.2">
       <c r="A354" t="s">
         <v>115</v>
       </c>
@@ -8040,7 +8040,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:8" ns3:dyDescent="0.2">
       <c r="A355" t="s">
         <v>59</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:8" ns3:dyDescent="0.2">
       <c r="A356" t="s">
         <v>43</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:8" ns3:dyDescent="0.2">
       <c r="A357" t="s">
         <v>115</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:8" ns3:dyDescent="0.2">
       <c r="A358" t="s">
         <v>116</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:8" ns3:dyDescent="0.2">
       <c r="A359" t="s">
         <v>152</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:8" ns3:dyDescent="0.2">
       <c r="A360" t="s">
         <v>58</v>
       </c>
@@ -8178,7 +8178,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:8" ns3:dyDescent="0.2">
       <c r="A361" t="s">
         <v>117</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:8" ns3:dyDescent="0.2">
       <c r="A362" t="s">
         <v>43</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" ns3:dyDescent="0.2">
       <c r="A363" t="s">
         <v>42</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:8" ns3:dyDescent="0.2">
       <c r="A364" t="s">
         <v>121</v>
       </c>
@@ -8270,7 +8270,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:8" ns3:dyDescent="0.2">
       <c r="A365" t="s">
         <v>116</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:8" ns3:dyDescent="0.2">
       <c r="A366" t="s">
         <v>152</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:8" ns3:dyDescent="0.2">
       <c r="A367" t="s">
         <v>43</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:8" ns3:dyDescent="0.2">
       <c r="A368" t="s">
         <v>42</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:19" ns3:dyDescent="0.2">
       <c r="A369" t="s">
         <v>200</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:19" ns3:dyDescent="0.2">
       <c r="A370" t="s">
         <v>203</v>
       </c>
@@ -8404,7 +8404,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:19" ns3:dyDescent="0.2">
       <c r="A371" t="s">
         <v>207</v>
       </c>
@@ -8425,10 +8425,10 @@
         <v>206</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:19" ns3:dyDescent="0.2">
       <c r="D372" s="10"/>
     </row>
-    <row r="373" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A373" s="1" t="s">
         <v>0</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:19" ns3:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1</v>
       </c>
@@ -8444,7 +8444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A375" t="s">
         <v>2</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:19" ns3:dyDescent="0.2">
       <c r="A376" t="s">
         <v>3</v>
       </c>
@@ -8460,7 +8460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:19" ns3:dyDescent="0.2">
       <c r="A377" t="s">
         <v>5</v>
       </c>
@@ -8468,7 +8468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:19" ns3:dyDescent="0.2">
       <c r="A378" t="s">
         <v>7</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:19" ns3:dyDescent="0.2">
       <c r="A379" t="s">
         <v>9</v>
       </c>
@@ -8484,7 +8484,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:19" ns3:dyDescent="0.2">
       <c r="A380" t="s">
         <v>18</v>
       </c>
@@ -8492,12 +8492,12 @@
         <v>221</v>
       </c>
     </row>
-    <row r="381" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A381" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:19" ns3:dyDescent="0.2">
       <c r="A382" t="s">
         <v>11</v>
       </c>
@@ -8523,7 +8523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="383" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A383" t="s">
         <v>129</v>
       </c>
@@ -8543,7 +8543,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:19" ns3:dyDescent="0.2">
       <c r="A384" t="s">
         <v>65</v>
       </c>
@@ -8567,7 +8567,7 @@
       <c r="Q384" s="4"/>
       <c r="S384" s="4"/>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:19" ns3:dyDescent="0.2">
       <c r="A385" t="s">
         <v>66</v>
       </c>
@@ -8590,7 +8590,7 @@
       <c r="Q385" s="3"/>
       <c r="S385" s="3"/>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:19" ns3:dyDescent="0.2">
       <c r="A386" t="s">
         <v>67</v>
       </c>
@@ -8613,7 +8613,7 @@
       <c r="Q386" s="3"/>
       <c r="S386" s="3"/>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:19" ns3:dyDescent="0.2">
       <c r="A387" t="s">
         <v>72</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:19" ns3:dyDescent="0.2">
       <c r="A388" t="s">
         <v>110</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:19" ns3:dyDescent="0.2">
       <c r="A389" t="s">
         <v>130</v>
       </c>
@@ -8676,10 +8676,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="390" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="G390" s="7"/>
     </row>
-    <row r="391" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A391" s="1" t="s">
         <v>0</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:19" ns3:dyDescent="0.2">
       <c r="A392" t="s">
         <v>1</v>
       </c>
@@ -8695,7 +8695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A393" t="s">
         <v>2</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:19" ns3:dyDescent="0.2">
       <c r="A394" t="s">
         <v>3</v>
       </c>
@@ -8711,7 +8711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:19" ns3:dyDescent="0.2">
       <c r="A395" t="s">
         <v>5</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:19" ns3:dyDescent="0.2">
       <c r="A396" t="s">
         <v>7</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:19" ns3:dyDescent="0.2">
       <c r="A397" t="s">
         <v>9</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:19" ns3:dyDescent="0.2">
       <c r="A398" t="s">
         <v>18</v>
       </c>
@@ -8743,12 +8743,12 @@
         <v>213</v>
       </c>
     </row>
-    <row r="399" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A399" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:19" ns3:dyDescent="0.2">
       <c r="A400" t="s">
         <v>11</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="401" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A401" t="s">
         <v>79</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="402" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A402" t="s">
         <v>211</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="403" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A403" t="s">
         <v>217</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13" ns3:dyDescent="0.2">
       <c r="A404" t="s">
         <v>25</v>
       </c>
@@ -8863,11 +8863,11 @@
         <v>76</v>
       </c>
     </row>
-    <row r="405" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A405" s="2"/>
       <c r="J405" s="2"/>
     </row>
-    <row r="406" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A406" s="1" t="s">
         <v>0</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13" ns3:dyDescent="0.2">
       <c r="A407" t="s">
         <v>1</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A408" t="s">
         <v>2</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13" ns3:dyDescent="0.2">
       <c r="A409" t="s">
         <v>3</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13" ns3:dyDescent="0.2">
       <c r="A410" t="s">
         <v>5</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13" ns3:dyDescent="0.2">
       <c r="A411" t="s">
         <v>7</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13" ns3:dyDescent="0.2">
       <c r="A412" t="s">
         <v>9</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13" ns3:dyDescent="0.2">
       <c r="A413" t="s">
         <v>18</v>
       </c>
@@ -8931,12 +8931,12 @@
         <v>213</v>
       </c>
     </row>
-    <row r="414" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A414" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13" ns3:dyDescent="0.2">
       <c r="A415" s="5" t="s">
         <v>11</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="416" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A416" t="str">
         <f>B406</f>
         <v>polyethyleneimine (PEI) production, for sorbent-based direct air capture system</v>
@@ -8999,7 +8999,7 @@
         <v>polyethyleneimine</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13" ns3:dyDescent="0.2">
       <c r="A417" t="s">
         <v>90</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" ns3:dyDescent="0.2">
       <c r="A418" t="s">
         <v>82</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" ns3:dyDescent="0.2">
       <c r="A419" t="s">
         <v>91</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" ns3:dyDescent="0.2">
       <c r="A420" t="s">
         <v>92</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" ns3:dyDescent="0.2">
       <c r="A421" t="s">
         <v>91</v>
       </c>
@@ -9169,7 +9169,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" ns3:dyDescent="0.2">
       <c r="A422" t="s">
         <v>93</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>0.20300000000000015</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" ns3:dyDescent="0.2">
       <c r="A423" t="s">
         <v>94</v>
       </c>
@@ -9247,7 +9247,7 @@
         <v>2.4240000000000022</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" ns3:dyDescent="0.2">
       <c r="A424" t="s">
         <v>84</v>
       </c>
@@ -9281,7 +9281,7 @@
         <v>17.13</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" ns3:dyDescent="0.2">
       <c r="A425" t="s">
         <v>34</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" ns3:dyDescent="0.2">
       <c r="A426" t="s">
         <v>83</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" ns3:dyDescent="0.2">
       <c r="A427" t="s">
         <v>73</v>
       </c>
@@ -9386,11 +9386,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A428" s="2"/>
       <c r="J428" s="2"/>
     </row>
-    <row r="429" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A429" s="1" t="s">
         <v>0</v>
       </c>
@@ -9398,7 +9398,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13" ns3:dyDescent="0.2">
       <c r="A430" t="s">
         <v>1</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A431" t="s">
         <v>2</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" ns3:dyDescent="0.2">
       <c r="A432" t="s">
         <v>3</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:19" ns3:dyDescent="0.2">
       <c r="A433" t="s">
         <v>5</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:19" ns3:dyDescent="0.2">
       <c r="A434" t="s">
         <v>7</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:19" ns3:dyDescent="0.2">
       <c r="A435" t="s">
         <v>9</v>
       </c>
@@ -9446,7 +9446,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:19" ns3:dyDescent="0.2">
       <c r="A436" t="s">
         <v>18</v>
       </c>
@@ -9454,12 +9454,12 @@
         <v>213</v>
       </c>
     </row>
-    <row r="437" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A437" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:19" ns3:dyDescent="0.2">
       <c r="A438" s="5" t="s">
         <v>11</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="439" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A439" t="str">
         <f>B429</f>
         <v>silica gel production, for sorbent-based direct air capture system</v>
@@ -9519,7 +9519,7 @@
         <v>silica gel</v>
       </c>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:19" ns3:dyDescent="0.2">
       <c r="A440" t="s">
         <v>81</v>
       </c>
@@ -9541,7 +9541,7 @@
       <c r="Q440" s="4"/>
       <c r="S440" s="4"/>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:19" ns3:dyDescent="0.2">
       <c r="A441" t="s">
         <v>82</v>
       </c>
@@ -9561,7 +9561,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:19" ns3:dyDescent="0.2">
       <c r="A442" t="s">
         <v>83</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:19" ns3:dyDescent="0.2">
       <c r="A443" t="s">
         <v>84</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="444" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A444" t="s">
         <v>195</v>
       </c>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="M444" s="2"/>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:19" ns3:dyDescent="0.2">
       <c r="A445" t="s">
         <v>148</v>
       </c>
@@ -9653,11 +9653,11 @@
         <v>20</v>
       </c>
     </row>
-    <row r="446" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A446" s="2"/>
       <c r="J446" s="2"/>
     </row>
-    <row r="447" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A447" s="1" t="s">
         <v>0</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:19" ns3:dyDescent="0.2">
       <c r="A448" t="s">
         <v>1</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A449" t="s">
         <v>2</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:10" ns3:dyDescent="0.2">
       <c r="A450" t="s">
         <v>3</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:10" ns3:dyDescent="0.2">
       <c r="A451" t="s">
         <v>5</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:10" ns3:dyDescent="0.2">
       <c r="A452" t="s">
         <v>7</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:10" ns3:dyDescent="0.2">
       <c r="A453" t="s">
         <v>9</v>
       </c>
@@ -9713,7 +9713,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:10" ns3:dyDescent="0.2">
       <c r="A454" t="s">
         <v>18</v>
       </c>
@@ -9721,12 +9721,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="455" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:10" ns3:dyDescent="0.2">
       <c r="A456" t="s">
         <v>11</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="457" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A457" t="s">
         <v>97</v>
       </c>
@@ -9772,7 +9772,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:10" ns3:dyDescent="0.2">
       <c r="A458" t="s">
         <v>194</v>
       </c>
@@ -9795,7 +9795,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:10" ns3:dyDescent="0.2">
       <c r="A459" t="s">
         <v>152</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:10" ns3:dyDescent="0.2">
       <c r="A460" t="s">
         <v>42</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:10" ns3:dyDescent="0.2">
       <c r="A461" t="s">
         <v>100</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:10" ns3:dyDescent="0.2">
       <c r="A462" t="s">
         <v>146</v>
       </c>
@@ -9887,7 +9887,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:10" ns3:dyDescent="0.2">
       <c r="A463" t="s">
         <v>77</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="464" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A464" t="s">
         <v>102</v>
       </c>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="J464" s="2"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:10" ns3:dyDescent="0.2">
       <c r="A465" t="s">
         <v>103</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:10" ns3:dyDescent="0.2">
       <c r="A466" t="s">
         <v>104</v>
       </c>
@@ -9980,7 +9980,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:10" ns3:dyDescent="0.2">
       <c r="A467" t="s">
         <v>105</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:10" ns3:dyDescent="0.2">
       <c r="A468" t="s">
         <v>100</v>
       </c>
@@ -10026,7 +10026,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:10" ns3:dyDescent="0.2">
       <c r="A469" t="s">
         <v>146</v>
       </c>
@@ -10049,7 +10049,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:10" ns3:dyDescent="0.2">
       <c r="A470" t="s">
         <v>35</v>
       </c>
@@ -10072,7 +10072,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:10" ns3:dyDescent="0.2">
       <c r="A471" t="s">
         <v>106</v>
       </c>
@@ -10095,7 +10095,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:10" ns3:dyDescent="0.2">
       <c r="A472" t="s">
         <v>102</v>
       </c>
@@ -10118,7 +10118,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="473" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A473" t="s">
         <v>59</v>
       </c>
@@ -10141,7 +10141,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:10" ns3:dyDescent="0.2">
       <c r="A474" t="s">
         <v>42</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:10" ns3:dyDescent="0.2">
       <c r="A475" t="s">
         <v>194</v>
       </c>
@@ -10187,7 +10187,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:10" ns3:dyDescent="0.2">
       <c r="A476" t="s">
         <v>152</v>
       </c>
@@ -10210,7 +10210,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:10" ns3:dyDescent="0.2">
       <c r="A477" t="s">
         <v>35</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:10" ns3:dyDescent="0.2">
       <c r="A478" t="s">
         <v>77</v>
       </c>
@@ -10256,7 +10256,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:10" ns3:dyDescent="0.2">
       <c r="A479" t="s">
         <v>65</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="480" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A480" t="s">
         <v>66</v>
       </c>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="J480" s="2"/>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:20" ns3:dyDescent="0.2">
       <c r="A481" t="s">
         <v>110</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:20" ns3:dyDescent="0.2">
       <c r="A482" t="s">
         <v>111</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:20" ns3:dyDescent="0.2">
       <c r="A483" t="s">
         <v>112</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="485" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A485" s="14" t="s">
         <v>0</v>
       </c>
@@ -10386,7 +10386,7 @@
       <c r="O485" s="16"/>
       <c r="P485" s="16"/>
     </row>
-    <row r="486" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A486" s="15" t="s">
         <v>7</v>
       </c>
@@ -10400,7 +10400,7 @@
       <c r="O486" s="16"/>
       <c r="P486" s="16"/>
     </row>
-    <row r="487" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A487" s="15" t="s">
         <v>1</v>
       </c>
@@ -10414,7 +10414,7 @@
       <c r="O487" s="16"/>
       <c r="P487" s="16"/>
     </row>
-    <row r="488" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A488" s="15" t="s">
         <v>2</v>
       </c>
@@ -10428,7 +10428,7 @@
       <c r="O488" s="16"/>
       <c r="P488" s="16"/>
     </row>
-    <row r="489" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A489" s="15" t="s">
         <v>3</v>
       </c>
@@ -10442,7 +10442,7 @@
       <c r="O489" s="16"/>
       <c r="P489" s="16"/>
     </row>
-    <row r="490" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A490" s="15" t="s">
         <v>5</v>
       </c>
@@ -10456,7 +10456,7 @@
       <c r="O490" s="16"/>
       <c r="P490" s="16"/>
     </row>
-    <row r="491" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A491" s="15" t="s">
         <v>9</v>
       </c>
@@ -10470,7 +10470,7 @@
       <c r="O491" s="16"/>
       <c r="P491" s="16"/>
     </row>
-    <row r="492" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A492" s="15" t="s">
         <v>171</v>
       </c>
@@ -10484,7 +10484,7 @@
       <c r="O492" s="16"/>
       <c r="P492" s="16"/>
     </row>
-    <row r="493" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A493" s="14" t="s">
         <v>10</v>
       </c>
@@ -10495,7 +10495,7 @@
       <c r="O493" s="16"/>
       <c r="P493" s="16"/>
     </row>
-    <row r="494" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A494" s="14" t="s">
         <v>11</v>
       </c>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="T494" s="1"/>
     </row>
-    <row r="495" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A495" s="15" t="s">
         <v>301</v>
       </c>
@@ -10586,7 +10586,7 @@
       <c r="P495" s="16"/>
       <c r="T495"/>
     </row>
-    <row r="496" spans="1:20" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:20" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A496" s="15" t="s">
         <v>184</v>
       </c>
@@ -10636,7 +10636,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="497" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A497" s="15" t="s">
         <v>38</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="498" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A498" s="15" t="s">
         <v>186</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>0.26139455023340635</v>
       </c>
     </row>
-    <row r="499" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A499" s="15" t="s">
         <v>31</v>
       </c>
@@ -10783,7 +10783,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="500" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A500" s="15" t="s">
         <v>34</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="501" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A501" s="15" t="s">
         <v>187</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="502" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A502" s="15" t="s">
         <v>90</v>
       </c>
@@ -10937,7 +10937,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="503" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A503" s="15" t="s">
         <v>91</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="504" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="A504" s="15" t="s">
         <v>189</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="505" spans="1:18" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:18" s="15" customFormat="1" ht="16" ns3:dyDescent="0.2">
       <c r="K505" s="16"/>
       <c r="L505" s="16"/>
       <c r="M505" s="16"/>
@@ -11045,7 +11045,7 @@
       <c r="O505" s="16"/>
       <c r="P505" s="16"/>
     </row>
-    <row r="506" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:18" ht="16" ns3:dyDescent="0.2">
       <c r="A506" s="1" t="s">
         <v>0</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="507" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:18" ns3:dyDescent="0.2">
       <c r="A507" t="s">
         <v>7</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="508" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:18" ht="16" ns3:dyDescent="0.2">
       <c r="A508" s="2" t="s">
         <v>1</v>
       </c>
@@ -11069,7 +11069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:18" ns3:dyDescent="0.2">
       <c r="A509" t="s">
         <v>2</v>
       </c>
@@ -11077,7 +11077,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="510" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:18" ns3:dyDescent="0.2">
       <c r="A510" t="s">
         <v>3</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="511" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:18" ns3:dyDescent="0.2">
       <c r="A511" t="s">
         <v>5</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="512" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:18" ns3:dyDescent="0.2">
       <c r="A512" t="s">
         <v>18</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="513" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:19" ns3:dyDescent="0.2">
       <c r="A513" t="s">
         <v>9</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:19" ns3:dyDescent="0.2">
       <c r="A514" t="s">
         <v>171</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:19" ns3:dyDescent="0.2">
       <c r="A515" t="s">
         <v>192</v>
       </c>
@@ -11125,12 +11125,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:19" ns3:dyDescent="0.2">
       <c r="A516" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="517" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A517" s="1" t="s">
         <v>11</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:19" ns3:dyDescent="0.2">
       <c r="A518" t="s">
         <v>302</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:19" ns3:dyDescent="0.2">
       <c r="A519" t="s">
         <v>184</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="520" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:19" ns3:dyDescent="0.2">
       <c r="A520" t="s">
         <v>38</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:19" ns3:dyDescent="0.2">
       <c r="A521" t="s">
         <v>31</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:19" ns3:dyDescent="0.2">
       <c r="A522" t="s">
         <v>34</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:19" ns3:dyDescent="0.2">
       <c r="A523" t="s">
         <v>187</v>
       </c>
@@ -11463,7 +11463,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="524" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A524" s="21" t="s">
         <v>90</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>0.16679850853156178</v>
       </c>
     </row>
-    <row r="526" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A526" s="1" t="s">
         <v>0</v>
       </c>
@@ -11521,7 +11521,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:19" ns3:dyDescent="0.2">
       <c r="A527" t="s">
         <v>7</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="528" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A528" s="2" t="s">
         <v>1</v>
       </c>
@@ -11537,7 +11537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:19" ns3:dyDescent="0.2">
       <c r="A529" t="s">
         <v>2</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="530" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:19" ns3:dyDescent="0.2">
       <c r="A530" t="s">
         <v>3</v>
       </c>
@@ -11553,7 +11553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:19" ns3:dyDescent="0.2">
       <c r="A531" t="s">
         <v>5</v>
       </c>
@@ -11561,7 +11561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:19" ns3:dyDescent="0.2">
       <c r="A532" t="s">
         <v>18</v>
       </c>
@@ -11569,7 +11569,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:19" ns3:dyDescent="0.2">
       <c r="A533" t="s">
         <v>9</v>
       </c>
@@ -11577,12 +11577,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="534" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:19" ns3:dyDescent="0.2">
       <c r="A534" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="535" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A535" s="1" t="s">
         <v>11</v>
       </c>
@@ -11619,7 +11619,7 @@
       <c r="R535" s="5"/>
       <c r="S535" s="5"/>
     </row>
-    <row r="536" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A536" s="28" t="str">
         <f>B526</f>
         <v>carbon dioxide, captured, at cement production plant, using monoethanolamine</v>
@@ -11641,7 +11641,7 @@
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="537" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A537" s="28" t="s">
         <v>97</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="538" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A538" s="28" t="s">
         <v>90</v>
       </c>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="N538" s="29"/>
     </row>
-    <row r="539" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A539" s="28" t="s">
         <v>91</v>
       </c>
@@ -11712,7 +11712,7 @@
       <c r="N539" s="29"/>
       <c r="P539" s="29"/>
     </row>
-    <row r="540" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A540" t="s">
         <v>317</v>
       </c>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="N540" s="29"/>
     </row>
-    <row r="541" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A541" s="28" t="s">
         <v>34</v>
       </c>
@@ -11762,7 +11762,7 @@
       </c>
       <c r="N541" s="29"/>
     </row>
-    <row r="542" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A542" s="28" t="s">
         <v>34</v>
       </c>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="N542" s="29"/>
     </row>
-    <row r="543" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A543" s="28" t="s">
         <v>34</v>
       </c>
@@ -11813,7 +11813,7 @@
       <c r="N543" s="29"/>
       <c r="Q543" s="30"/>
     </row>
-    <row r="544" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A544" s="28" t="s">
         <v>229</v>
       </c>
@@ -11837,7 +11837,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="545" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A545" s="28" t="s">
         <v>73</v>
       </c>
@@ -11861,7 +11861,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="546" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A546" s="28" t="s">
         <v>232</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="547" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A547" s="28" t="s">
         <v>234</v>
       </c>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="G547" s="29"/>
     </row>
-    <row r="549" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A549" s="1" t="s">
         <v>0</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:19" ns3:dyDescent="0.2">
       <c r="A550" t="s">
         <v>7</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="551" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A551" s="2" t="s">
         <v>1</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:19" ns3:dyDescent="0.2">
       <c r="A552" t="s">
         <v>2</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="553" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:19" ns3:dyDescent="0.2">
       <c r="A553" t="s">
         <v>3</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:19" ns3:dyDescent="0.2">
       <c r="A554" t="s">
         <v>5</v>
       </c>
@@ -11949,7 +11949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="555" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:19" ns3:dyDescent="0.2">
       <c r="A555" t="s">
         <v>18</v>
       </c>
@@ -11957,7 +11957,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="556" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:19" ns3:dyDescent="0.2">
       <c r="A556" t="s">
         <v>9</v>
       </c>
@@ -11965,12 +11965,12 @@
         <v>239</v>
       </c>
     </row>
-    <row r="557" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:19" ns3:dyDescent="0.2">
       <c r="A557" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="558" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A558" s="1" t="s">
         <v>11</v>
       </c>
@@ -12007,7 +12007,7 @@
       <c r="R558" s="5"/>
       <c r="S558" s="5"/>
     </row>
-    <row r="559" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A559" s="28" t="str">
         <f>B549</f>
         <v>carbon dioxide, captured, at cement production plant, using direct separation</v>
@@ -12029,7 +12029,7 @@
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:19" ns3:dyDescent="0.2">
       <c r="A560" s="28" t="s">
         <v>97</v>
       </c>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H560" s="28"/>
     </row>
-    <row r="561" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:19" s="26" customFormat="1" ns3:dyDescent="0.2">
       <c r="A561" s="26" t="s">
         <v>34</v>
       </c>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="N561" s="32"/>
     </row>
-    <row r="564" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A564" s="1" t="s">
         <v>0</v>
       </c>
@@ -12084,7 +12084,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="565" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:19" ns3:dyDescent="0.2">
       <c r="A565" t="s">
         <v>7</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="566" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A566" s="2" t="s">
         <v>1</v>
       </c>
@@ -12100,7 +12100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:19" ns3:dyDescent="0.2">
       <c r="A567" t="s">
         <v>2</v>
       </c>
@@ -12108,7 +12108,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="568" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:19" ns3:dyDescent="0.2">
       <c r="A568" t="s">
         <v>3</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:19" ns3:dyDescent="0.2">
       <c r="A569" t="s">
         <v>5</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="570" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:19" ns3:dyDescent="0.2">
       <c r="A570" t="s">
         <v>18</v>
       </c>
@@ -12132,20 +12132,22 @@
         <v>236</v>
       </c>
     </row>
-    <row r="571" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:19" ns3:dyDescent="0.2">
       <c r="A571" t="s">
         <v>9</v>
       </c>
-      <c r="B571" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="572" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Carbon capture with Oxyfuel technology, where fuel combustion happens in Oxygen-CO2-mix instead of air, which creates a cleaner CO2 flue gas stream. Main source: Voldsund (2019) - CEMCAP - D4.6 CEMCAP comparative techno-economic analysis. 90% CO2 capture efficiency (process+fuel CO2). Includes changes in electricity demand due to new kiln design for oxy-process, oxygen production with ASU, CO2 compression and purification, CO2 transport. Excludes changes in Non-CO2 emissions: CPU reduces SOx (99.99%), NOx (99.36%), Hg (100%) and CO (100%). Source: Amelie Müller, Carina Harpprecht, Romain Sacchi, Ben Maes, Mariësse van Sluisveld, Vassilis Daioglou, Branko Šavija, Bernhard Steubing, Decarbonizing the cement industry: Findings from coupling prospective life cycle assessment of clinker with integrated assessment model scenarios, Journal of Cleaner Production, 2024, https://doi.org/10.1016/j.jclepro.2024.141884. Oxygen demand is normalized from the CEMCAP D4.6 oxyfuel base case in Table 6.1 (31.0 t O2/h / 99 t captured CO2/h = 0.313131313 kg O2/kg CO2 captured).</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" spans="1:19" ns3:dyDescent="0.2">
       <c r="A572" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="573" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:19" ht="16" ns3:dyDescent="0.2">
       <c r="A573" s="1" t="s">
         <v>11</v>
       </c>
@@ -12182,7 +12184,7 @@
       <c r="R573" s="5"/>
       <c r="S573" s="5"/>
     </row>
-    <row r="574" spans="1:19" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:19" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A574" s="28" t="str">
         <f>B564</f>
         <v>carbon dioxide, captured, at cement production plant, using oxyfuel</v>
@@ -12204,7 +12206,7 @@
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="575" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:19" ns3:dyDescent="0.2">
       <c r="A575" s="28" t="s">
         <v>97</v>
       </c>
@@ -12226,13 +12228,12 @@
       </c>
       <c r="H575" s="28"/>
     </row>
-    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:19" ns3:dyDescent="0.2">
       <c r="A576" t="s">
         <v>248</v>
       </c>
       <c r="B576" s="6">
-        <f>B574*32/44/(1-0.11)</f>
-        <v>0.81716036772216549</v>
+        <v>0.31313131313131315</v>
       </c>
       <c r="C576" t="s">
         <v>26</v>
@@ -12246,11 +12247,13 @@
       <c r="G576" t="s">
         <v>246</v>
       </c>
-      <c r="H576" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="577" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Oxygen demand for the oxyfuel base case, normalized from CEMCAP D4.6 Table 6.1: O2 flow rate 31.0 t/h divided by captured CO2 flow rate 99 t/h = 0.313131313 kg O2 per kg CO2 captured. Source: Voldsund et al. (2019), CEMCAP D4.6 CEMCAP comparative techno-economic analysis of CO2 capture in cement plants, Table 6.1, doi:10.5281/zenodo.2597091.</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" spans="1:22" ns3:dyDescent="0.2">
       <c r="A577" t="s">
         <v>34</v>
       </c>
@@ -12274,7 +12277,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="578" spans="1:22" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:22" ht="16.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A578" t="s">
         <v>34</v>
       </c>
@@ -12298,7 +12301,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="579" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:22" ns3:dyDescent="0.2">
       <c r="A579" t="s">
         <v>34</v>
       </c>
@@ -12324,7 +12327,7 @@
       <c r="M579" s="27"/>
       <c r="N579" s="31"/>
     </row>
-    <row r="580" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:22" ns3:dyDescent="0.2">
       <c r="A580" t="s">
         <v>34</v>
       </c>
@@ -12350,7 +12353,7 @@
       <c r="M580" s="27"/>
       <c r="N580" s="31"/>
     </row>
-    <row r="582" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A582" s="1" t="s">
         <v>0</v>
       </c>
@@ -12358,7 +12361,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="583" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:22" ns3:dyDescent="0.2">
       <c r="A583" t="s">
         <v>9</v>
       </c>
@@ -12366,7 +12369,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="584" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:22" ns3:dyDescent="0.2">
       <c r="A584" t="s">
         <v>7</v>
       </c>
@@ -12374,7 +12377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="585" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:22" ns3:dyDescent="0.2">
       <c r="A585" t="s">
         <v>2</v>
       </c>
@@ -12382,7 +12385,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="586" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:22" ns3:dyDescent="0.2">
       <c r="A586" t="s">
         <v>5</v>
       </c>
@@ -12390,13 +12393,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="587" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:22" ns3:dyDescent="0.2">
       <c r="A587" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B587" s="35"/>
     </row>
-    <row r="588" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A588" s="1" t="s">
         <v>11</v>
       </c>
@@ -12434,7 +12437,7 @@
       <c r="U588" s="1"/>
       <c r="V588" s="1"/>
     </row>
-    <row r="589" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:22" ns3:dyDescent="0.2">
       <c r="A589" t="str">
         <f>B582</f>
         <v>carbon dioxide, captured and stored, by land-use change</v>
@@ -12458,7 +12461,7 @@
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="590" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:22" ns3:dyDescent="0.2">
       <c r="A590" t="s">
         <v>255</v>
       </c>
@@ -12475,7 +12478,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="592" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:22" ht="16" ns3:dyDescent="0.2">
       <c r="A592" s="1" t="s">
         <v>0</v>
       </c>
@@ -12486,7 +12489,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:14" ns3:dyDescent="0.2">
       <c r="A593" t="s">
         <v>7</v>
       </c>
@@ -12497,7 +12500,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:14" ns3:dyDescent="0.2">
       <c r="A594" t="s">
         <v>1</v>
       </c>
@@ -12508,7 +12511,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:14" ns3:dyDescent="0.2">
       <c r="A595" t="s">
         <v>2</v>
       </c>
@@ -12519,7 +12522,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="596" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:14" ns3:dyDescent="0.2">
       <c r="A596" t="s">
         <v>3</v>
       </c>
@@ -12530,7 +12533,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:14" ns3:dyDescent="0.2">
       <c r="A597" t="s">
         <v>5</v>
       </c>
@@ -12541,7 +12544,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="598" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:14" ns3:dyDescent="0.2">
       <c r="A598" t="s">
         <v>9</v>
       </c>
@@ -12552,7 +12555,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="599" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:14" ns3:dyDescent="0.2">
       <c r="A599" t="s">
         <v>18</v>
       </c>
@@ -12563,7 +12566,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="600" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A600" s="1" t="s">
         <v>10</v>
       </c>
@@ -12571,7 +12574,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="601" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:14" ns3:dyDescent="0.2">
       <c r="A601" t="s">
         <v>11</v>
       </c>
@@ -12600,7 +12603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:14" ns3:dyDescent="0.2">
       <c r="A602" t="s">
         <v>186</v>
       </c>
@@ -12626,7 +12629,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="603" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:14" ns3:dyDescent="0.2">
       <c r="A603" t="s">
         <v>232</v>
       </c>
@@ -12652,7 +12655,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="604" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:14" ns3:dyDescent="0.2">
       <c r="A604" t="s">
         <v>259</v>
       </c>
@@ -12678,7 +12681,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="605" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:14" ns3:dyDescent="0.2">
       <c r="A605" t="s">
         <v>234</v>
       </c>
@@ -12702,7 +12705,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="606" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:14" ns3:dyDescent="0.2">
       <c r="A606" t="str">
         <f>B592</f>
         <v>carbon dioxide, captured and stored, at wood burning power plant, pipeline 200km, storage 1000m</v>
@@ -12730,7 +12733,7 @@
         <v>carbon dioxide, captured</v>
       </c>
     </row>
-    <row r="607" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:14" ns3:dyDescent="0.2">
       <c r="A607" s="28" t="s">
         <v>97</v>
       </c>
@@ -12759,7 +12762,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="608" spans="1:14" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:14" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A608" s="28" t="s">
         <v>34</v>
       </c>
@@ -12787,7 +12790,7 @@
       </c>
       <c r="N608" s="29"/>
     </row>
-    <row r="609" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:17" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A609" s="28" t="s">
         <v>34</v>
       </c>
@@ -12815,7 +12818,7 @@
       </c>
       <c r="N609" s="29"/>
     </row>
-    <row r="610" spans="1:17" s="28" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:17" s="28" customFormat="1" ns3:dyDescent="0.2">
       <c r="A610" s="28" t="s">
         <v>34</v>
       </c>
@@ -12844,7 +12847,7 @@
       <c r="N610" s="29"/>
       <c r="Q610" s="30"/>
     </row>
-    <row r="611" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:17" ns3:dyDescent="0.2">
       <c r="A611" t="s">
         <v>284</v>
       </c>
@@ -12873,7 +12876,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="612" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:17" ns3:dyDescent="0.2">
       <c r="A612" t="s">
         <v>266</v>
       </c>
@@ -12902,7 +12905,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="613" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:17" ns3:dyDescent="0.2">
       <c r="A613" t="s">
         <v>269</v>
       </c>
@@ -12931,7 +12934,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="614" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:17" ns3:dyDescent="0.2">
       <c r="A614" t="s">
         <v>271</v>
       </c>
@@ -12960,7 +12963,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="615" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:17" ns3:dyDescent="0.2">
       <c r="A615" t="s">
         <v>274</v>
       </c>
@@ -12989,7 +12992,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="616" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:17" ns3:dyDescent="0.2">
       <c r="A616" t="s">
         <v>90</v>
       </c>
@@ -13018,7 +13021,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="617" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:17" ns3:dyDescent="0.2">
       <c r="A617" t="s">
         <v>277</v>
       </c>
@@ -13047,7 +13050,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="618" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:17" ns3:dyDescent="0.2">
       <c r="A618" t="s">
         <v>91</v>
       </c>
@@ -13076,7 +13079,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="619" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:17" ns3:dyDescent="0.2">
       <c r="A619" t="s">
         <v>73</v>
       </c>
@@ -13106,7 +13109,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="620" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:17" ns3:dyDescent="0.2">
       <c r="A620" t="s">
         <v>39</v>
       </c>
@@ -13132,7 +13135,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="622" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:17" ht="16" ns3:dyDescent="0.2">
       <c r="A622" s="1" t="s">
         <v>0</v>
       </c>
@@ -13140,7 +13143,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="623" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:17" ns3:dyDescent="0.2">
       <c r="A623" t="s">
         <v>1</v>
       </c>
@@ -13148,7 +13151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:17" ns3:dyDescent="0.2">
       <c r="A624" t="s">
         <v>2</v>
       </c>
@@ -13156,7 +13159,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:13" ns3:dyDescent="0.2">
       <c r="A625" t="s">
         <v>3</v>
       </c>
@@ -13164,7 +13167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:13" ns3:dyDescent="0.2">
       <c r="A626" t="s">
         <v>5</v>
       </c>
@@ -13172,7 +13175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:13" ns3:dyDescent="0.2">
       <c r="A627" t="s">
         <v>7</v>
       </c>
@@ -13180,7 +13183,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:13" ns3:dyDescent="0.2">
       <c r="A628" t="s">
         <v>18</v>
       </c>
@@ -13188,7 +13191,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:13" ns3:dyDescent="0.2">
       <c r="A629" t="s">
         <v>9</v>
       </c>
@@ -13196,12 +13199,12 @@
         <v>309</v>
       </c>
     </row>
-    <row r="630" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A630" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:13" ns3:dyDescent="0.2">
       <c r="A631" s="5" t="s">
         <v>11</v>
       </c>
@@ -13242,7 +13245,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:13" ns3:dyDescent="0.2">
       <c r="A632" t="str">
         <f>B622</f>
         <v>carbon dioxide, captured and stored, from a hydrogen production plant using steam methane reforming of biomethane</v>
@@ -13263,7 +13266,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:13" ns3:dyDescent="0.2">
       <c r="A633" t="s">
         <v>34</v>
       </c>
@@ -13300,7 +13303,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:13" ns3:dyDescent="0.2">
       <c r="A634" t="s">
         <v>31</v>
       </c>
@@ -13337,7 +13340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:13" ns3:dyDescent="0.2">
       <c r="A635" t="s">
         <v>34</v>
       </c>
@@ -13374,7 +13377,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="636" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A636" s="15" t="s">
         <v>90</v>
       </c>
@@ -13410,7 +13413,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:13" ns3:dyDescent="0.2">
       <c r="A637" t="s">
         <v>34</v>
       </c>
@@ -13447,7 +13450,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:13" ns3:dyDescent="0.2">
       <c r="A638" t="s">
         <v>42</v>
       </c>
@@ -13470,7 +13473,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:13" ns3:dyDescent="0.2">
       <c r="A639" t="s">
         <v>43</v>
       </c>
@@ -13493,7 +13496,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:13" ns3:dyDescent="0.2">
       <c r="A640" t="s">
         <v>195</v>
       </c>
@@ -13514,7 +13517,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:13" ns3:dyDescent="0.2">
       <c r="A641" s="28" t="s">
         <v>97</v>
       </c>
@@ -13537,7 +13540,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:13" ns3:dyDescent="0.2">
       <c r="A642" t="s">
         <v>39</v>
       </c>
@@ -13563,7 +13566,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="644" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A644" s="1" t="s">
         <v>0</v>
       </c>
@@ -13571,7 +13574,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:13" ns3:dyDescent="0.2">
       <c r="A645" t="s">
         <v>1</v>
       </c>
@@ -13579,7 +13582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:13" ns3:dyDescent="0.2">
       <c r="A646" t="s">
         <v>2</v>
       </c>
@@ -13587,7 +13590,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:13" ns3:dyDescent="0.2">
       <c r="A647" t="s">
         <v>3</v>
       </c>
@@ -13595,7 +13598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:13" ns3:dyDescent="0.2">
       <c r="A648" t="s">
         <v>5</v>
       </c>
@@ -13603,7 +13606,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:13" ns3:dyDescent="0.2">
       <c r="A649" t="s">
         <v>7</v>
       </c>
@@ -13611,7 +13614,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:13" ns3:dyDescent="0.2">
       <c r="A650" t="s">
         <v>18</v>
       </c>
@@ -13619,7 +13622,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:13" ns3:dyDescent="0.2">
       <c r="A651" t="s">
         <v>9</v>
       </c>
@@ -13627,12 +13630,12 @@
         <v>320</v>
       </c>
     </row>
-    <row r="652" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:13" ht="16" ns3:dyDescent="0.2">
       <c r="A652" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:13" ns3:dyDescent="0.2">
       <c r="A653" s="5" t="s">
         <v>11</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:13" ns3:dyDescent="0.2">
       <c r="A654" t="str">
         <f>B644</f>
         <v>carbon dioxide, captured and stored, from a biomass fermentation plant</v>
@@ -13694,7 +13697,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:13" ns3:dyDescent="0.2">
       <c r="A655" t="s">
         <v>34</v>
       </c>
@@ -13730,7 +13733,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:13" ns3:dyDescent="0.2">
       <c r="A656" s="28" t="s">
         <v>97</v>
       </c>
@@ -13753,7 +13756,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:13" ns3:dyDescent="0.2">
       <c r="A657" t="s">
         <v>39</v>
       </c>
@@ -13777,8 +13780,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V620" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:V620" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/premise/data/additional_inventories/lci-carbon-capture.xlsx
+++ b/premise/data/additional_inventories/lci-carbon-capture.xlsx
@@ -147,7 +147,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="171" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -213,6 +213,7 @@
     <xf numFmtId="170" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -591,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V652"/>
+  <dimension ref="A1:V678"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="47.33203125" customWidth="1" style="41" min="1" max="1"/>
@@ -16962,7 +16963,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Hydrogen production from natural gas and biomethane with carbon capture and storage - A techno-environmental analysis. Antonini et al. 2020. https://doi.org/10.1039/D0SE00222D. Values normalized from the associated ESI LCA workbook d0se00222d1_suppl.zip.</t>
+          <t>Hydrogen production from natural gas and biomethane with carbon capture and storage - A techno-environmental analysis. Antonini et al. 2020. https://doi.org/10.1039/D0SE00222D. Values normalized from the associated ESI LCA workbook d0se00222d1_suppl.zip. MDEA heat duty inferred from the Antonini equivalent-work equation and the Antonini et al. 2021 wood-gasification SI, which reuses the same MDEA model.</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16975,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>This dataset represents the pre-combustion CO2 capture module for hydrogen production by steam methane reforming of biomethane, plus the common downstream CO2 compression, transport and geological storage module. The host SMR plant, biomethane production, tail gas combustion, hydrogen production and host-process emissions are excluded. Capture is modelled as aqueous methyldiethanolamine (MDEA) absorption. Antonini et al. (2020) model the matching SMR BM, HT+LT no-CCS and SMR BM, HT+LT + CCS (MDEA), 98% average cases in their ESI LCA workbook. The CCS case stores 0.0512474 kg CO2 per MJ H2, while grid electricity changes from -0.0004662 to 0.0054776 kWh per MJ H2; the capture module therefore uses an incremental electricity penalty of 0.11598 kWh per kg CO2 stored. The same comparison shows no positive external fuel or heat penalty: total reformer/furnace energy input decreases from 1.3097 to 1.2837 MJ per MJ H2, so the former 4.0556 MJ/kg CO2 biomethane heat placeholder is removed. MDEA make-up is 3.4e-5 kg per kg CO2, normalized from the SI solvent proxy row. Final CO2 compression electricity is omitted because the common storage exchange represents compression to pipeline pressure, transport, further compression and injection.</t>
+          <t>This dataset represents the pre-combustion CO2 capture module for hydrogen production by steam methane reforming of biomethane, plus the common downstream CO2 compression, transport and geological storage module. The host SMR plant, biomethane production, tail gas combustion, hydrogen production and host-process emissions are excluded. Capture is modelled as aqueous methyldiethanolamine (MDEA) absorption. Antonini et al. (2020) model the matching SMR BM, HT+LT no-CCS and SMR BM, HT+LT + CCS (MDEA), 98% average cases in their ESI LCA workbook. The CCS case stores 0.0512474 kg CO2 per MJ H2, while grid electricity changes from -0.0004662 to 0.0054776 kWh per MJ H2; the capture module therefore uses an incremental electricity penalty of 0.11598 kWh per kg CO2 stored. The same plant-level comparison shows no positive external fuel penalty: total reformer/furnace energy input decreases from 1.3097 to 1.2837 MJ per MJ H2. Nevertheless, MDEA regeneration physically requires low-pressure heat. Because the SI does not report a standalone reboiler duty, a biomethane heat input of 0.948 MJ per kg CO2 is inferred from the Antonini equivalent-work equation u = W + Q*(1 - Tamb/(Treb + dTmin)): using u = 0.68 MJ/kg CO2 from the Antonini et al. wood-gasification SI for the same MDEA model at similar absorber pressure, W = 0.115981 kWh/kg CO2 = 0.4175 MJ/kg CO2, Tamb = 282 K, and Treb + dTmin approximately 390 K gives Q = 0.948 MJ/kg CO2. This replaces the former CEMCAP-derived 4.0556 MJ/kg CO2 biomethane heat placeholder. MDEA make-up is 3.4e-5 kg per kg CO2, normalized from the SI solvent proxy row. Final CO2 compression electricity is omitted because the common storage exchange represents compression to pipeline pressure, transport, further compression and injection.</t>
         </is>
       </c>
     </row>
@@ -17124,136 +17125,139 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
+          <t>heat production, biomethane, at boiler condensing modulating &lt;100kW</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>0.9477985069525399</v>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>heat, central or small-scale, biomethane</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Inferred low-pressure MDEA reboiler heat supplied as biomethane heat. Antonini et al. (2020) define equivalent work as u = W + Q*(1 - Tamb/(Treb + dTmin)); their SI gives the electricity penalty W = 0.115981 kWh/kg CO2 = 0.4175 MJ/kg CO2, and the Antonini et al. wood-gasification SI reports u = 0.68 MJ/kg CO2 for the same MDEA model at similar absorber pressure. With Tamb = 282 K and Treb + dTmin approximated as 390 K for low-pressure MDEA regeneration, Q = (0.68 - 0.4175)/(1 - 282/390) = 0.948 MJ/kg CO2. Inferred value, not a directly reported heat duty.</t>
+        </is>
+      </c>
+      <c r="I632" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
           <t>market for tap water</t>
         </is>
       </c>
-      <c r="B632" t="n">
+      <c r="B633" t="n">
         <v>1.5</v>
       </c>
-      <c r="C632" t="inlineStr">
+      <c r="C633" t="inlineStr">
         <is>
           <t>Europe without Switzerland</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F632" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G632" t="inlineStr">
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
         <is>
           <t>tap water</t>
         </is>
       </c>
-      <c r="H632" t="inlineStr">
+      <c r="H633" t="inlineStr">
         <is>
           <t>For condensing or cooling (varies by setup)</t>
         </is>
       </c>
-      <c r="I632" t="n">
+      <c r="I633" t="n">
         <v>5</v>
       </c>
-      <c r="J632" s="49" t="n">
+      <c r="J633" s="49" t="n">
         <v>1.5</v>
       </c>
-      <c r="K632" t="n">
+      <c r="K633" t="n">
         <v>1</v>
       </c>
-      <c r="L632" t="n">
+      <c r="L633" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" s="15" t="inlineStr">
+    <row r="634">
+      <c r="A634" s="15" t="inlineStr">
         <is>
           <t>market for methyldiethanolamine</t>
         </is>
       </c>
-      <c r="B633" t="n">
+      <c r="B634" t="n">
         <v>3.4e-05</v>
       </c>
-      <c r="C633" t="inlineStr">
+      <c r="C634" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F633" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G633" s="15" t="inlineStr">
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G634" s="15" t="inlineStr">
         <is>
           <t>methyldiethanolamine</t>
         </is>
       </c>
-      <c r="H633" t="inlineStr">
+      <c r="H634" t="inlineStr">
         <is>
           <t>MDEA make-up for solvent degradation or blowdown, normalized from Antonini et al. (2020) SI LCA workbook: 1.742412e-6 kg solvent proxy per MJ H2 / 0.051247425 kg CO2 stored per MJ H2 = 3.4e-5 kg/kg CO2. The SI uses a diethanolamine market as proxy; this inventory keeps methyldiethanolamine to match the MDEA process chemistry.</t>
         </is>
       </c>
-      <c r="I633" t="n">
+      <c r="I634" t="n">
         <v>0</v>
       </c>
-      <c r="J633" s="49" t="n"/>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>market for steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="B634" s="6" t="n">
-        <v>1.2e-05</v>
-      </c>
-      <c r="C634" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D634" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F634" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G634" t="inlineStr">
-        <is>
-          <t>steel, low-alloyed</t>
-        </is>
-      </c>
-      <c r="H634" t="inlineStr">
-        <is>
-          <t>Allocation of capital goods per kg CO₂ (25-year life, 75 kt/y plant)</t>
-        </is>
-      </c>
+      <c r="J634" s="49" t="n"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>steel production, chromium steel 18/8, hot rolled</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B635" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.2e-05</v>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -17268,316 +17272,321 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>steel, chromium steel 18/8, hot rolled</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Heat recovery &amp; regeneration infrastructure</t>
+          <t>Allocation of capital goods per kg CO₂ (25-year life, 75 kt/y plant)</t>
         </is>
       </c>
     </row>
     <row r="636" ht="16" customHeight="1" s="41">
       <c r="A636" t="inlineStr">
         <is>
+          <t>steel production, chromium steel 18/8, hot rolled</t>
+        </is>
+      </c>
+      <c r="B636" s="6" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8, hot rolled</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Heat recovery &amp; regeneration infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
           <t>treatment of wastewater, average, wastewater treatment</t>
         </is>
       </c>
-      <c r="B636" s="6" t="n">
+      <c r="B637" s="6" t="n">
         <v>-0.0015</v>
       </c>
-      <c r="C636" t="inlineStr">
+      <c r="C637" t="inlineStr">
         <is>
           <t>Europe without Switzerland</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr">
+      <c r="D637" t="inlineStr">
         <is>
           <t>cubic meter</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G636" t="inlineStr">
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
         <is>
           <t>wastewater, average</t>
         </is>
       </c>
     </row>
-    <row r="637">
-      <c r="A637" s="28" t="inlineStr">
+    <row r="638">
+      <c r="A638" s="28" t="inlineStr">
         <is>
           <t>carbon dioxide compression, transport and storage</t>
-        </is>
-      </c>
-      <c r="B637" t="n">
-        <v>1</v>
-      </c>
-      <c r="C637" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D637" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F637" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>carbon dioxide, stored</t>
-        </is>
-      </c>
-      <c r="H637" t="inlineStr">
-        <is>
-          <t>Common downstream module for CO2 compression, pipeline transport, further compression and geological injection; used once to avoid double-counting final compression electricity in the capture module.</t>
-        </is>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>Carbon dioxide, in air</t>
         </is>
       </c>
       <c r="B638" t="n">
         <v>1</v>
       </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
       <c r="D638" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr">
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>carbon dioxide, stored</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Common downstream module for CO2 compression, pipeline transport, further compression and geological injection; used once to avoid double-counting final compression electricity in the capture module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, in air</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>1</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
         <is>
           <t>natural resource::in air</t>
         </is>
       </c>
-      <c r="F638" t="inlineStr">
+      <c r="F639" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="G638" t="n">
+      <c r="G639" t="n">
         <v>0</v>
       </c>
-      <c r="H638" t="inlineStr">
+      <c r="H639" t="inlineStr">
         <is>
           <t>Biogenic CO2 uptake associated with the biomethane feedstock; the host SMR process itself is outside the cut-off capture-module boundary.</t>
         </is>
       </c>
     </row>
-    <row r="639"/>
-    <row r="640">
-      <c r="A640" s="1" t="inlineStr">
+    <row r="640"/>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B640" s="1" t="inlineStr">
+      <c r="B641" s="1" t="inlineStr">
         <is>
           <t>carbon dioxide, captured and stored, from a biomass fermentation plant</t>
         </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B641" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>carbon dioxide, captured</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>carbon dioxide, captured</t>
         </is>
       </c>
     </row>
     <row r="644" ht="16" customHeight="1" s="41">
       <c r="A644" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>process</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>kilogram</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B646" s="6" t="inlineStr">
-        <is>
-          <t>Dees J, Oke K, Goldstein H, McCoy ST, Sanchez DL, Simon AJ, Li W. Cost and Life Cycle Emissions of Ethanol Produced with an Oxyfuel Boiler and Carbon Capture and Storage. Environ Sci Technol. 2023 Apr 4;57(13):5391-5403. doi: 10.1021/acs.est.2c04784. Epub 2023 Mar 21. PMID: 36943504; PMCID: PMC10077580.</t>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>RER</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B647" s="6" t="inlineStr">
+        <is>
+          <t>Dees J, Oke K, Goldstein H, McCoy ST, Sanchez DL, Simon AJ, Li W. Cost and Life Cycle Emissions of Ethanol Produced with an Oxyfuel Boiler and Carbon Capture and Storage. Environ Sci Technol. 2023 Apr 4;57(13):5391-5403. doi: 10.1021/acs.est.2c04784. Epub 2023 Mar 21. PMID: 36943504; PMCID: PMC10077580.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t>This dataset represents capture of an already high-purity fermentation CO2 stream plus the common downstream CO2 compression, transport and geological storage module. The host ethanol fermentation plant, biomass supply and host-process emissions are excluded. Because fermentation CO2 is assumed to be essentially pure, no solvent, sorbent or regeneration heat is modelled. The original Dees et al. CPU electricity demand of 110 kWh/t CO2 includes dehydration, compression, liquefaction and pumping to transport/storage pressure; it is omitted here to avoid double-counting compression with the common storage exchange. Only the common storage exchange represents CO2 compression, transport, further compression and injection.</t>
         </is>
       </c>
     </row>
-    <row r="648">
-      <c r="A648" s="1" t="inlineStr">
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" s="5" t="inlineStr">
+    <row r="650">
+      <c r="A650" s="5" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B649" s="5" t="inlineStr">
+      <c r="B650" s="5" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C649" s="5" t="inlineStr">
+      <c r="C650" s="5" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D649" s="5" t="inlineStr">
+      <c r="D650" s="5" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E649" s="5" t="inlineStr">
+      <c r="E650" s="5" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F649" s="5" t="inlineStr">
+      <c r="F650" s="5" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G649" s="5" t="inlineStr">
+      <c r="G650" s="5" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H649" s="5" t="inlineStr">
+      <c r="H650" s="5" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I649" s="5" t="inlineStr">
+      <c r="I650" s="5" t="inlineStr">
         <is>
           <t>uncertainty type</t>
         </is>
       </c>
-      <c r="J649" s="5" t="inlineStr">
+      <c r="J650" s="5" t="inlineStr">
         <is>
           <t>loc</t>
         </is>
       </c>
-      <c r="K649" s="5" t="inlineStr">
+      <c r="K650" s="5" t="inlineStr">
         <is>
           <t>minimum</t>
         </is>
       </c>
-      <c r="L649" s="5" t="inlineStr">
+      <c r="L650" s="5" t="inlineStr">
         <is>
           <t>maximum</t>
         </is>
       </c>
-      <c r="M649" s="5" t="inlineStr">
+      <c r="M650" s="5" t="inlineStr">
         <is>
           <t>negative</t>
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t>carbon dioxide, captured and stored, from a biomass fermentation plant</t>
-        </is>
-      </c>
-      <c r="B650" t="n">
-        <v>1</v>
-      </c>
-      <c r="C650" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D650" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F650" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G650" t="inlineStr">
-        <is>
-          <t>carbon dioxide, captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" s="28" t="inlineStr">
-        <is>
-          <t>carbon dioxide compression, transport and storage</t>
         </is>
       </c>
       <c r="B651" t="n">
@@ -17595,49 +17604,1067 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>carbon dioxide, stored</t>
-        </is>
-      </c>
-      <c r="H651" t="inlineStr">
-        <is>
-          <t>Common downstream module for CO2 compression, pipeline transport, further compression and geological injection; the source CPU electricity row is omitted to avoid double-counting compression.</t>
+          <t>carbon dioxide, captured</t>
         </is>
       </c>
     </row>
     <row r="652" ht="16" customHeight="1" s="41">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>Carbon dioxide, in air</t>
+      <c r="A652" s="28" t="inlineStr">
+        <is>
+          <t>carbon dioxide compression, transport and storage</t>
         </is>
       </c>
       <c r="B652" t="n">
         <v>1</v>
       </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
       <c r="D652" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E652" t="inlineStr">
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>carbon dioxide, stored</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Common downstream module for CO2 compression, pipeline transport, further compression and geological injection; the source CPU electricity row is omitted to avoid double-counting compression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, in air</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>1</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
         <is>
           <t>natural resource::in air</t>
         </is>
       </c>
-      <c r="F652" t="inlineStr">
+      <c r="F653" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr">
+      <c r="H653" t="inlineStr">
         <is>
           <t>Biogenic CO2 uptake associated with the biomass fermentation feedstock; the host fermentation process itself is outside the cut-off capture-module boundary.</t>
         </is>
       </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B655" s="5" t="inlineStr">
+        <is>
+          <t>carbon dioxide, captured and stored, at cement production plant, from non-fossil carbon dioxide, using monoethanolamine</t>
+        </is>
+      </c>
+      <c r="C655" s="57" t="n"/>
+      <c r="D655" s="57" t="n"/>
+      <c r="E655" s="57" t="n"/>
+      <c r="F655" s="57" t="n"/>
+      <c r="G655" s="57" t="n"/>
+      <c r="H655" s="57" t="n"/>
+      <c r="I655" s="57" t="n"/>
+      <c r="J655" s="57" t="n"/>
+      <c r="K655" s="57" t="n"/>
+      <c r="L655" s="57" t="n"/>
+      <c r="M655" s="57" t="n"/>
+      <c r="N655" s="57" t="n"/>
+      <c r="O655" s="57" t="n"/>
+      <c r="P655" s="57" t="n"/>
+      <c r="Q655" s="57" t="n"/>
+      <c r="R655" s="57" t="n"/>
+      <c r="S655" s="57" t="n"/>
+      <c r="T655" s="57" t="n"/>
+      <c r="U655" s="57" t="n"/>
+      <c r="V655" s="57" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="57" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B656" s="57" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="C656" s="57" t="n"/>
+      <c r="D656" s="57" t="n"/>
+      <c r="E656" s="57" t="n"/>
+      <c r="F656" s="57" t="n"/>
+      <c r="G656" s="57" t="n"/>
+      <c r="H656" s="57" t="n"/>
+      <c r="I656" s="57" t="n"/>
+      <c r="J656" s="57" t="n"/>
+      <c r="K656" s="57" t="n"/>
+      <c r="L656" s="57" t="n"/>
+      <c r="M656" s="57" t="n"/>
+      <c r="N656" s="57" t="n"/>
+      <c r="O656" s="57" t="n"/>
+      <c r="P656" s="57" t="n"/>
+      <c r="Q656" s="57" t="n"/>
+      <c r="R656" s="57" t="n"/>
+      <c r="S656" s="57" t="n"/>
+      <c r="T656" s="57" t="n"/>
+      <c r="U656" s="57" t="n"/>
+      <c r="V656" s="57" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B657" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C657" s="57" t="n"/>
+      <c r="D657" s="57" t="n"/>
+      <c r="E657" s="57" t="n"/>
+      <c r="F657" s="57" t="n"/>
+      <c r="G657" s="57" t="n"/>
+      <c r="H657" s="57" t="n"/>
+      <c r="I657" s="57" t="n"/>
+      <c r="J657" s="57" t="n"/>
+      <c r="K657" s="57" t="n"/>
+      <c r="L657" s="57" t="n"/>
+      <c r="M657" s="57" t="n"/>
+      <c r="N657" s="57" t="n"/>
+      <c r="O657" s="57" t="n"/>
+      <c r="P657" s="57" t="n"/>
+      <c r="Q657" s="57" t="n"/>
+      <c r="R657" s="57" t="n"/>
+      <c r="S657" s="57" t="n"/>
+      <c r="T657" s="57" t="n"/>
+      <c r="U657" s="57" t="n"/>
+      <c r="V657" s="57" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="57" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B658" s="57" t="inlineStr">
+        <is>
+          <t>carbon dioxide, captured</t>
+        </is>
+      </c>
+      <c r="C658" s="57" t="n"/>
+      <c r="D658" s="57" t="n"/>
+      <c r="E658" s="57" t="n"/>
+      <c r="F658" s="57" t="n"/>
+      <c r="G658" s="57" t="n"/>
+      <c r="H658" s="57" t="n"/>
+      <c r="I658" s="57" t="n"/>
+      <c r="J658" s="57" t="n"/>
+      <c r="K658" s="57" t="n"/>
+      <c r="L658" s="57" t="n"/>
+      <c r="M658" s="57" t="n"/>
+      <c r="N658" s="57" t="n"/>
+      <c r="O658" s="57" t="n"/>
+      <c r="P658" s="57" t="n"/>
+      <c r="Q658" s="57" t="n"/>
+      <c r="R658" s="57" t="n"/>
+      <c r="S658" s="57" t="n"/>
+      <c r="T658" s="57" t="n"/>
+      <c r="U658" s="57" t="n"/>
+      <c r="V658" s="57" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="57" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B659" s="57" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="C659" s="57" t="n"/>
+      <c r="D659" s="57" t="n"/>
+      <c r="E659" s="57" t="n"/>
+      <c r="F659" s="57" t="n"/>
+      <c r="G659" s="57" t="n"/>
+      <c r="H659" s="57" t="n"/>
+      <c r="I659" s="57" t="n"/>
+      <c r="J659" s="57" t="n"/>
+      <c r="K659" s="57" t="n"/>
+      <c r="L659" s="57" t="n"/>
+      <c r="M659" s="57" t="n"/>
+      <c r="N659" s="57" t="n"/>
+      <c r="O659" s="57" t="n"/>
+      <c r="P659" s="57" t="n"/>
+      <c r="Q659" s="57" t="n"/>
+      <c r="R659" s="57" t="n"/>
+      <c r="S659" s="57" t="n"/>
+      <c r="T659" s="57" t="n"/>
+      <c r="U659" s="57" t="n"/>
+      <c r="V659" s="57" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="57" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B660" s="57" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="C660" s="57" t="n"/>
+      <c r="D660" s="57" t="n"/>
+      <c r="E660" s="57" t="n"/>
+      <c r="F660" s="57" t="n"/>
+      <c r="G660" s="57" t="n"/>
+      <c r="H660" s="57" t="n"/>
+      <c r="I660" s="57" t="n"/>
+      <c r="J660" s="57" t="n"/>
+      <c r="K660" s="57" t="n"/>
+      <c r="L660" s="57" t="n"/>
+      <c r="M660" s="57" t="n"/>
+      <c r="N660" s="57" t="n"/>
+      <c r="O660" s="57" t="n"/>
+      <c r="P660" s="57" t="n"/>
+      <c r="Q660" s="57" t="n"/>
+      <c r="R660" s="57" t="n"/>
+      <c r="S660" s="57" t="n"/>
+      <c r="T660" s="57" t="n"/>
+      <c r="U660" s="57" t="n"/>
+      <c r="V660" s="57" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="57" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B661" s="57" t="inlineStr">
+        <is>
+          <t>Amelie Müller, Carina Harpprecht, Romain Sacchi, Ben Maes, Mariësse van Sluisveld, Vassilis Daioglou, Branko Šavija, Bernhard Steubing, Decarbonizing the cement industry: Findings from coupling prospective life cycle assessment of clinker with integrated assessment model scenarios, Journal of Cleaner Production, 2024, https://doi.org/10.1016/j.jclepro.2024.141884.</t>
+        </is>
+      </c>
+      <c r="C661" s="57" t="n"/>
+      <c r="D661" s="57" t="n"/>
+      <c r="E661" s="57" t="n"/>
+      <c r="F661" s="57" t="n"/>
+      <c r="G661" s="57" t="n"/>
+      <c r="H661" s="57" t="n"/>
+      <c r="I661" s="57" t="n"/>
+      <c r="J661" s="57" t="n"/>
+      <c r="K661" s="57" t="n"/>
+      <c r="L661" s="57" t="n"/>
+      <c r="M661" s="57" t="n"/>
+      <c r="N661" s="57" t="n"/>
+      <c r="O661" s="57" t="n"/>
+      <c r="P661" s="57" t="n"/>
+      <c r="Q661" s="57" t="n"/>
+      <c r="R661" s="57" t="n"/>
+      <c r="S661" s="57" t="n"/>
+      <c r="T661" s="57" t="n"/>
+      <c r="U661" s="57" t="n"/>
+      <c r="V661" s="57" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="57" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B662" s="57" t="inlineStr">
+        <is>
+          <t>Variant of the cement MEA capture and storage module for CDR accounting of non-fossil CO2 only. The activity is derived from the existing dataset "carbon dioxide, captured, at cement production plant, using monoethanolamine" and keeps the same per-kg CO2 capture, compression, transport and geological storage requirements from Müller et al. (2024) and CEMCAP/Voldsund. The functional unit is 1 kg of non-fossil CO2 permanently stored from cement flue gas; any fossil CO2 co-captured in the real flue gas is intentionally ignored here and receives neither a storage credit nor residual-emission accounting. A 1 kg biosphere input of "Carbon dioxide, in air" represents the removal of the stored non-fossil carbon.</t>
+        </is>
+      </c>
+      <c r="C662" s="57" t="n"/>
+      <c r="D662" s="57" t="n"/>
+      <c r="E662" s="57" t="n"/>
+      <c r="F662" s="57" t="n"/>
+      <c r="G662" s="57" t="n"/>
+      <c r="H662" s="57" t="n"/>
+      <c r="I662" s="57" t="n"/>
+      <c r="J662" s="57" t="n"/>
+      <c r="K662" s="57" t="n"/>
+      <c r="L662" s="57" t="n"/>
+      <c r="M662" s="57" t="n"/>
+      <c r="N662" s="57" t="n"/>
+      <c r="O662" s="57" t="n"/>
+      <c r="P662" s="57" t="n"/>
+      <c r="Q662" s="57" t="n"/>
+      <c r="R662" s="57" t="n"/>
+      <c r="S662" s="57" t="n"/>
+      <c r="T662" s="57" t="n"/>
+      <c r="U662" s="57" t="n"/>
+      <c r="V662" s="57" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="57" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+      <c r="B663" s="57" t="n"/>
+      <c r="C663" s="57" t="n"/>
+      <c r="D663" s="57" t="n"/>
+      <c r="E663" s="57" t="n"/>
+      <c r="F663" s="57" t="n"/>
+      <c r="G663" s="57" t="n"/>
+      <c r="H663" s="57" t="n"/>
+      <c r="I663" s="57" t="n"/>
+      <c r="J663" s="57" t="n"/>
+      <c r="K663" s="57" t="n"/>
+      <c r="L663" s="57" t="n"/>
+      <c r="M663" s="57" t="n"/>
+      <c r="N663" s="57" t="n"/>
+      <c r="O663" s="57" t="n"/>
+      <c r="P663" s="57" t="n"/>
+      <c r="Q663" s="57" t="n"/>
+      <c r="R663" s="57" t="n"/>
+      <c r="S663" s="57" t="n"/>
+      <c r="T663" s="57" t="n"/>
+      <c r="U663" s="57" t="n"/>
+      <c r="V663" s="57" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B664" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C664" s="5" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D664" s="5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E664" s="5" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F664" s="5" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G664" s="5" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H664" s="5" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I664" s="5" t="n"/>
+      <c r="J664" s="5" t="n"/>
+      <c r="K664" s="5" t="n"/>
+      <c r="L664" s="5" t="n"/>
+      <c r="M664" s="5" t="n"/>
+      <c r="N664" s="5" t="n"/>
+      <c r="O664" s="5" t="n"/>
+      <c r="P664" s="5" t="n"/>
+      <c r="Q664" s="5" t="n"/>
+      <c r="R664" s="5" t="n"/>
+      <c r="S664" s="5" t="n"/>
+      <c r="T664" s="57" t="n"/>
+      <c r="U664" s="57" t="n"/>
+      <c r="V664" s="57" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="28" t="inlineStr">
+        <is>
+          <t>carbon dioxide, captured and stored, at cement production plant, from non-fossil carbon dioxide, using monoethanolamine</t>
+        </is>
+      </c>
+      <c r="B665" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C665" s="28" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D665" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E665" s="57" t="n"/>
+      <c r="F665" s="28" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G665" s="28" t="inlineStr">
+        <is>
+          <t>carbon dioxide, captured</t>
+        </is>
+      </c>
+      <c r="H665" s="57" t="n"/>
+      <c r="I665" s="57" t="n"/>
+      <c r="J665" s="57" t="n"/>
+      <c r="K665" s="57" t="n"/>
+      <c r="L665" s="57" t="n"/>
+      <c r="M665" s="57" t="n"/>
+      <c r="N665" s="57" t="n"/>
+      <c r="O665" s="57" t="n"/>
+      <c r="P665" s="57" t="n"/>
+      <c r="Q665" s="57" t="n"/>
+      <c r="R665" s="57" t="n"/>
+      <c r="S665" s="57" t="n"/>
+      <c r="T665" s="57" t="n"/>
+      <c r="U665" s="57" t="n"/>
+      <c r="V665" s="57" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="28" t="inlineStr">
+        <is>
+          <t>carbon dioxide compression, transport and storage</t>
+        </is>
+      </c>
+      <c r="B666" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C666" s="28" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D666" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E666" s="57" t="n"/>
+      <c r="F666" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G666" s="57" t="inlineStr">
+        <is>
+          <t>carbon dioxide, stored</t>
+        </is>
+      </c>
+      <c r="H666" s="57" t="n"/>
+      <c r="I666" s="57" t="n"/>
+      <c r="J666" s="57" t="n"/>
+      <c r="K666" s="57" t="n"/>
+      <c r="L666" s="57" t="n"/>
+      <c r="M666" s="57" t="n"/>
+      <c r="N666" s="57" t="n"/>
+      <c r="O666" s="57" t="n"/>
+      <c r="P666" s="57" t="n"/>
+      <c r="Q666" s="57" t="n"/>
+      <c r="R666" s="57" t="n"/>
+      <c r="S666" s="57" t="n"/>
+      <c r="T666" s="57" t="n"/>
+      <c r="U666" s="57" t="n"/>
+      <c r="V666" s="57" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="28" t="inlineStr">
+        <is>
+          <t>market for monoethanolamine</t>
+        </is>
+      </c>
+      <c r="B667" s="54" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="C667" s="28" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D667" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E667" s="57" t="n"/>
+      <c r="F667" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G667" s="28" t="inlineStr">
+        <is>
+          <t>monoethanolamine</t>
+        </is>
+      </c>
+      <c r="H667" s="28" t="inlineStr">
+        <is>
+          <t>MEA mark-up, lost in reclaimer (1.4 kg MEA/tCO2) CEMCAP - D4.6 CEMCAP comparative techno-economic analysis, p. 26</t>
+        </is>
+      </c>
+      <c r="I667" s="57" t="n"/>
+      <c r="J667" s="57" t="n"/>
+      <c r="K667" s="57" t="n"/>
+      <c r="L667" s="57" t="n"/>
+      <c r="M667" s="57" t="n"/>
+      <c r="N667" s="29" t="n"/>
+      <c r="O667" s="57" t="n"/>
+      <c r="P667" s="57" t="n"/>
+      <c r="Q667" s="57" t="n"/>
+      <c r="R667" s="57" t="n"/>
+      <c r="S667" s="57" t="n"/>
+      <c r="T667" s="57" t="n"/>
+      <c r="U667" s="57" t="n"/>
+      <c r="V667" s="57" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="28" t="inlineStr">
+        <is>
+          <t>market for sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="B668" s="29" t="n">
+        <v>0.0005359299516908213</v>
+      </c>
+      <c r="C668" s="28" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D668" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E668" s="57" t="n"/>
+      <c r="F668" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G668" s="28" t="inlineStr">
+        <is>
+          <t>sodium hydroxide, without water, in 50% solution state</t>
+        </is>
+      </c>
+      <c r="H668" s="28" t="inlineStr">
+        <is>
+          <t>SOx removal, needed so that MEA doesn't form amine salts. Stochiometric amount of 1.25 kg NaOH/kg SOx is sufficient (Cempcap 4.6). 0.00035 kg SOx/kg clinker (ecoinvent), 0.828 kg CO2/kg clinker from GCCA data.</t>
+        </is>
+      </c>
+      <c r="I668" s="57" t="n"/>
+      <c r="J668" s="57" t="n"/>
+      <c r="K668" s="57" t="n"/>
+      <c r="L668" s="57" t="n"/>
+      <c r="M668" s="57" t="n"/>
+      <c r="N668" s="29" t="n"/>
+      <c r="O668" s="57" t="n"/>
+      <c r="P668" s="29" t="n"/>
+      <c r="Q668" s="57" t="n"/>
+      <c r="R668" s="57" t="n"/>
+      <c r="S668" s="57" t="n"/>
+      <c r="T668" s="57" t="n"/>
+      <c r="U668" s="57" t="n"/>
+      <c r="V668" s="57" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="57" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B669" s="29" t="n">
+        <v>4.055555555555555</v>
+      </c>
+      <c r="C669" s="28" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D669" s="28" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="E669" s="57" t="n"/>
+      <c r="F669" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G669" s="28" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="H669" s="28" t="inlineStr">
+        <is>
+          <t>Steam for MEA regeneration (3.76 MJ/kg CO2, of which 0.11 can be recuberated from waste heat).</t>
+        </is>
+      </c>
+      <c r="I669" s="57" t="n"/>
+      <c r="J669" s="57" t="n"/>
+      <c r="K669" s="57" t="n"/>
+      <c r="L669" s="57" t="n"/>
+      <c r="M669" s="57" t="n"/>
+      <c r="N669" s="29" t="n"/>
+      <c r="O669" s="57" t="n"/>
+      <c r="P669" s="57" t="n"/>
+      <c r="Q669" s="57" t="n"/>
+      <c r="R669" s="57" t="n"/>
+      <c r="S669" s="57" t="n"/>
+      <c r="T669" s="57" t="n"/>
+      <c r="U669" s="57" t="n"/>
+      <c r="V669" s="57" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="28" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B670" s="29" t="n">
+        <v>0.03149802890932983</v>
+      </c>
+      <c r="C670" s="28" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D670" s="28" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="E670" s="57" t="n"/>
+      <c r="F670" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G670" s="28" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="H670" s="28" t="inlineStr">
+        <is>
+          <t>Electricity consumption for fans, pumps and thermal reclaimer (188 MJ/tclk [primary energy], 761 kg CO2/tclk, 0.459 conversion factor primary to secondary energy, 3.6 MJ/kWh) CEMCAP - D4.6 CEMCAP comparative techno-economic analysis, Table 5.3</t>
+        </is>
+      </c>
+      <c r="I670" s="57" t="n"/>
+      <c r="J670" s="57" t="n"/>
+      <c r="K670" s="57" t="n"/>
+      <c r="L670" s="57" t="n"/>
+      <c r="M670" s="57" t="n"/>
+      <c r="N670" s="29" t="n"/>
+      <c r="O670" s="57" t="n"/>
+      <c r="P670" s="57" t="n"/>
+      <c r="Q670" s="57" t="n"/>
+      <c r="R670" s="57" t="n"/>
+      <c r="S670" s="57" t="n"/>
+      <c r="T670" s="57" t="n"/>
+      <c r="U670" s="57" t="n"/>
+      <c r="V670" s="57" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="28" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B671" s="29" t="n">
+        <v>0.020607752956636</v>
+      </c>
+      <c r="C671" s="28" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D671" s="28" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="E671" s="57" t="n"/>
+      <c r="F671" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G671" s="28" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="H671" s="28" t="inlineStr">
+        <is>
+          <t>Electricity consumption for cooling water system (123 MJ/tclk [primary energy], 761 kg CO2/tclk, 0.459 conversion factor primary to secondary energy, 3.6 MJ/kWh) CEMCAP - D4.6 CEMCAP comparative techno-economic analysis, Table 5.3</t>
+        </is>
+      </c>
+      <c r="I671" s="57" t="n"/>
+      <c r="J671" s="57" t="n"/>
+      <c r="K671" s="57" t="n"/>
+      <c r="L671" s="57" t="n"/>
+      <c r="M671" s="57" t="n"/>
+      <c r="N671" s="29" t="n"/>
+      <c r="O671" s="57" t="n"/>
+      <c r="P671" s="57" t="n"/>
+      <c r="Q671" s="57" t="n"/>
+      <c r="R671" s="57" t="n"/>
+      <c r="S671" s="57" t="n"/>
+      <c r="T671" s="57" t="n"/>
+      <c r="U671" s="57" t="n"/>
+      <c r="V671" s="57" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="28" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B672" s="29" t="n">
+        <v>0.0963370565045992</v>
+      </c>
+      <c r="C672" s="28" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D672" s="28" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="E672" s="57" t="n"/>
+      <c r="F672" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G672" s="28" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="H672" s="28" t="inlineStr">
+        <is>
+          <t>Energy needed for compression and liquefication of CO2 (CPU): (CEMCAP D4.6, table 5.3)</t>
+        </is>
+      </c>
+      <c r="I672" s="57" t="n"/>
+      <c r="J672" s="57" t="n"/>
+      <c r="K672" s="57" t="n"/>
+      <c r="L672" s="57" t="n"/>
+      <c r="M672" s="57" t="n"/>
+      <c r="N672" s="29" t="n"/>
+      <c r="O672" s="57" t="n"/>
+      <c r="P672" s="57" t="n"/>
+      <c r="Q672" s="55" t="n"/>
+      <c r="R672" s="57" t="n"/>
+      <c r="S672" s="57" t="n"/>
+      <c r="T672" s="57" t="n"/>
+      <c r="U672" s="57" t="n"/>
+      <c r="V672" s="57" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="28" t="inlineStr">
+        <is>
+          <t>market group for tap water</t>
+        </is>
+      </c>
+      <c r="B673" s="29" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="C673" s="28" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D673" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E673" s="57" t="n"/>
+      <c r="F673" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G673" s="28" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="H673" s="28" t="inlineStr">
+        <is>
+          <t>Process water mark-up. CEMCAP - D4.6 CEMCAP comparative techno-economic analysis, Table 5.1</t>
+        </is>
+      </c>
+      <c r="I673" s="57" t="n"/>
+      <c r="J673" s="57" t="n"/>
+      <c r="K673" s="57" t="n"/>
+      <c r="L673" s="57" t="n"/>
+      <c r="M673" s="57" t="n"/>
+      <c r="N673" s="57" t="n"/>
+      <c r="O673" s="57" t="n"/>
+      <c r="P673" s="57" t="n"/>
+      <c r="Q673" s="57" t="n"/>
+      <c r="R673" s="57" t="n"/>
+      <c r="S673" s="57" t="n"/>
+      <c r="T673" s="57" t="n"/>
+      <c r="U673" s="57" t="n"/>
+      <c r="V673" s="57" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="28" t="inlineStr">
+        <is>
+          <t>treatment of spent solvent mixture, hazardous waste incineration</t>
+        </is>
+      </c>
+      <c r="B674" s="29" t="n">
+        <v>-0.001363948497854077</v>
+      </c>
+      <c r="C674" s="28" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D674" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E674" s="57" t="n"/>
+      <c r="F674" s="28" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G674" s="28" t="inlineStr">
+        <is>
+          <t>spent solvent mixture</t>
+        </is>
+      </c>
+      <c r="H674" s="28" t="inlineStr">
+        <is>
+          <t>Spent MEA solvent: Share of airborne emission and solid emissions from Moser 2011</t>
+        </is>
+      </c>
+      <c r="I674" s="57" t="n"/>
+      <c r="J674" s="57" t="n"/>
+      <c r="K674" s="57" t="n"/>
+      <c r="L674" s="57" t="n"/>
+      <c r="M674" s="57" t="n"/>
+      <c r="N674" s="57" t="n"/>
+      <c r="O674" s="57" t="n"/>
+      <c r="P674" s="57" t="n"/>
+      <c r="Q674" s="57" t="n"/>
+      <c r="R674" s="57" t="n"/>
+      <c r="S674" s="57" t="n"/>
+      <c r="T674" s="57" t="n"/>
+      <c r="U674" s="57" t="n"/>
+      <c r="V674" s="57" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="28" t="inlineStr">
+        <is>
+          <t>Monoethanolamine</t>
+        </is>
+      </c>
+      <c r="B675" s="54" t="n">
+        <v>4.540440528634362e-05</v>
+      </c>
+      <c r="C675" s="57" t="n"/>
+      <c r="D675" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E675" s="28" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F675" s="28" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G675" s="57" t="n"/>
+      <c r="H675" s="28" t="inlineStr">
+        <is>
+          <t>MEA emissions, rest is regenerated. Share of airborne emission and solid emissions (process: treatment of spent solvent mixture) from Moser 2011</t>
+        </is>
+      </c>
+      <c r="I675" s="57" t="n"/>
+      <c r="J675" s="57" t="n"/>
+      <c r="K675" s="57" t="n"/>
+      <c r="L675" s="57" t="n"/>
+      <c r="M675" s="57" t="n"/>
+      <c r="N675" s="57" t="n"/>
+      <c r="O675" s="57" t="n"/>
+      <c r="P675" s="57" t="n"/>
+      <c r="Q675" s="57" t="n"/>
+      <c r="R675" s="57" t="n"/>
+      <c r="S675" s="57" t="n"/>
+      <c r="T675" s="57" t="n"/>
+      <c r="U675" s="57" t="n"/>
+      <c r="V675" s="57" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="28" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B676" s="29" t="n">
+        <v>0.000473</v>
+      </c>
+      <c r="C676" s="57" t="n"/>
+      <c r="D676" s="28" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E676" s="28" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F676" s="28" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G676" s="29" t="n"/>
+      <c r="H676" s="57" t="n"/>
+      <c r="I676" s="57" t="n"/>
+      <c r="J676" s="57" t="n"/>
+      <c r="K676" s="57" t="n"/>
+      <c r="L676" s="57" t="n"/>
+      <c r="M676" s="57" t="n"/>
+      <c r="N676" s="57" t="n"/>
+      <c r="O676" s="57" t="n"/>
+      <c r="P676" s="57" t="n"/>
+      <c r="Q676" s="57" t="n"/>
+      <c r="R676" s="57" t="n"/>
+      <c r="S676" s="57" t="n"/>
+      <c r="T676" s="57" t="n"/>
+      <c r="U676" s="57" t="n"/>
+      <c r="V676" s="57" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="28" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, in air</t>
+        </is>
+      </c>
+      <c r="B677" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C677" s="57" t="n"/>
+      <c r="D677" s="28" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E677" s="28" t="inlineStr">
+        <is>
+          <t>natural resource::in air</t>
+        </is>
+      </c>
+      <c r="F677" s="28" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="G677" s="29" t="n"/>
+      <c r="H677" s="57" t="inlineStr">
+        <is>
+          <t>Permanent storage of 1 kg non-fossil CO2 from cement flue gas; fossil CO2 co-capture is ignored in this CDR variant.</t>
+        </is>
+      </c>
+      <c r="I677" s="57" t="n"/>
+      <c r="J677" s="57" t="n"/>
+      <c r="K677" s="57" t="n"/>
+      <c r="L677" s="57" t="n"/>
+      <c r="M677" s="57" t="n"/>
+      <c r="N677" s="57" t="n"/>
+      <c r="O677" s="57" t="n"/>
+      <c r="P677" s="57" t="n"/>
+      <c r="Q677" s="57" t="n"/>
+      <c r="R677" s="57" t="n"/>
+      <c r="S677" s="57" t="n"/>
+      <c r="T677" s="57" t="n"/>
+      <c r="U677" s="57" t="n"/>
+      <c r="V677" s="57" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="57" t="n"/>
+      <c r="B678" s="57" t="n"/>
+      <c r="C678" s="57" t="n"/>
+      <c r="D678" s="57" t="n"/>
+      <c r="E678" s="57" t="n"/>
+      <c r="F678" s="57" t="n"/>
+      <c r="G678" s="57" t="n"/>
+      <c r="H678" s="57" t="n"/>
+      <c r="I678" s="57" t="n"/>
+      <c r="J678" s="57" t="n"/>
+      <c r="K678" s="57" t="n"/>
+      <c r="L678" s="57" t="n"/>
+      <c r="M678" s="57" t="n"/>
+      <c r="N678" s="57" t="n"/>
+      <c r="O678" s="57" t="n"/>
+      <c r="P678" s="57" t="n"/>
+      <c r="Q678" s="57" t="n"/>
+      <c r="R678" s="57" t="n"/>
+      <c r="S678" s="57" t="n"/>
+      <c r="T678" s="57" t="n"/>
+      <c r="U678" s="57" t="n"/>
+      <c r="V678" s="57" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V620"/>

--- a/premise/data/additional_inventories/lci-carbon-capture.xlsx
+++ b/premise/data/additional_inventories/lci-carbon-capture.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFEC7685-3449-6B40-86FB-B8FF4FEF99CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7930783-60D7-7540-BB1A-7ECFB40059AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3085" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3021" uniqueCount="351">
   <si>
     <t>database</t>
   </si>
@@ -1006,12 +1006,6 @@
     <t>For condensing or cooling (varies by setup)</t>
   </si>
   <si>
-    <t>market for methyldiethanolamine</t>
-  </si>
-  <si>
-    <t>methyldiethanolamine</t>
-  </si>
-  <si>
     <t>MDEA make-up for solvent degradation or blowdown, normalized from Antonini et al. (2020) SI LCA workbook: 1.742412e-6 kg solvent proxy per MJ H2 / 0.051247425 kg CO2 stored per MJ H2 = 3.4e-5 kg/kg CO2. The SI uses a diethanolamine market as proxy; this inventory keeps methyldiethanolamine to match the MDEA process chemistry.</t>
   </si>
   <si>
@@ -1049,27 +1043,6 @@
   </si>
   <si>
     <t>Permanent storage of 1 kg non-fossil CO2 from cement flue gas; fossil CO2 co-capture is ignored in this CDR variant.</t>
-  </si>
-  <si>
-    <t>carbon dioxide, captured and stored, by re/afforestation, eucalyptus</t>
-  </si>
-  <si>
-    <t>Simple datasets that models the capture and sequestration of 1 kg of atmopsheric CO2 in biomass.</t>
-  </si>
-  <si>
-    <t>hardwood forestry, eucalyptus ssp., planted forest management</t>
-  </si>
-  <si>
-    <t>cleft timber, green, measured as dry mass</t>
-  </si>
-  <si>
-    <t>carbon dioxide, captured and stored, by re/afforestation, willow</t>
-  </si>
-  <si>
-    <t>willow production, short rotation coppice</t>
-  </si>
-  <si>
-    <t>wood chips and particles, willow, dry, measured as dry mass</t>
   </si>
   <si>
     <t>carbon dioxide, captured, with a solvent-based direct air capture system, 1MtCO2, with hydrogen heat, and grid electricity</t>
@@ -1112,7 +1085,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0.0E+00"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -1121,7 +1094,6 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="0.00000"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -1243,7 +1215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1284,7 +1256,6 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1608,7 +1579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V773"/>
+  <dimension ref="A1:V772"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" customWidth="1"/>
@@ -12782,13 +12753,13 @@
     </row>
     <row r="624" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="15" t="s">
-        <v>326</v>
+        <v>184</v>
       </c>
       <c r="B624">
         <v>3.4E-5</v>
       </c>
       <c r="C624" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D624" t="s">
         <v>10</v>
@@ -12797,10 +12768,10 @@
         <v>28</v>
       </c>
       <c r="G624" s="15" t="s">
-        <v>327</v>
+        <v>185</v>
       </c>
       <c r="H624" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="I624">
         <v>0</v>
@@ -12827,7 +12798,7 @@
         <v>79</v>
       </c>
       <c r="H625" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="626" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -12850,7 +12821,7 @@
         <v>81</v>
       </c>
       <c r="H626" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="627" spans="1:13" x14ac:dyDescent="0.2">
@@ -12893,7 +12864,7 @@
         <v>61</v>
       </c>
       <c r="H628" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="629" spans="1:13" x14ac:dyDescent="0.2">
@@ -12916,7 +12887,7 @@
         <v>0</v>
       </c>
       <c r="H629" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="631" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -12924,7 +12895,7 @@
         <v>2</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="632" spans="1:13" x14ac:dyDescent="0.2">
@@ -12972,7 +12943,7 @@
         <v>15</v>
       </c>
       <c r="B637" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="638" spans="1:13" x14ac:dyDescent="0.2">
@@ -12980,7 +12951,7 @@
         <v>13</v>
       </c>
       <c r="B638" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="639" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -13031,7 +13002,7 @@
     </row>
     <row r="641" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B641">
         <v>1</v>
@@ -13069,7 +13040,7 @@
         <v>61</v>
       </c>
       <c r="H642" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="643" spans="1:22" x14ac:dyDescent="0.2">
@@ -13089,7 +13060,7 @@
         <v>57</v>
       </c>
       <c r="H643" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="645" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -13097,7 +13068,7 @@
         <v>2</v>
       </c>
       <c r="B645" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C645" s="37"/>
       <c r="D645" s="37"/>
@@ -13293,7 +13264,7 @@
         <v>13</v>
       </c>
       <c r="B652" s="37" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C652" s="37"/>
       <c r="D652" s="37"/>
@@ -13384,7 +13355,7 @@
     </row>
     <row r="655" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A655" s="28" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B655" s="34">
         <v>1</v>
@@ -13847,7 +13818,7 @@
       </c>
       <c r="G667" s="29"/>
       <c r="H667" s="37" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I667" s="37"/>
       <c r="J667" s="37"/>
@@ -13892,850 +13863,668 @@
       <c r="A669" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B669" s="5" t="s">
+      <c r="B669" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="670" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A670" t="s">
+        <v>4</v>
+      </c>
+      <c r="B670">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A671" t="s">
+        <v>5</v>
+      </c>
+      <c r="B671" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="672" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A672" t="s">
+        <v>7</v>
+      </c>
+      <c r="B672" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="673" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A673" t="s">
+        <v>9</v>
+      </c>
+      <c r="B673" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="674" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A674" t="s">
+        <v>11</v>
+      </c>
+      <c r="B674" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="675" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A675" t="s">
+        <v>13</v>
+      </c>
+      <c r="B675" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="676" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A676" t="s">
+        <v>15</v>
+      </c>
+      <c r="B676" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="677" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A677" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="678" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A678" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B678" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C678" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D678" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E678" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F678" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G678" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H678" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I678" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J678" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K678" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L678" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M678" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="679" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A679" t="s">
+        <v>339</v>
+      </c>
+      <c r="B679">
+        <v>1</v>
+      </c>
+      <c r="C679" t="s">
+        <v>12</v>
+      </c>
+      <c r="D679" t="s">
+        <v>10</v>
+      </c>
+      <c r="F679" t="s">
+        <v>26</v>
+      </c>
+      <c r="G679" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="680" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A680" t="s">
+        <v>27</v>
+      </c>
+      <c r="B680">
+        <v>5.0000000000000002E-11</v>
+      </c>
+      <c r="C680" t="s">
+        <v>12</v>
+      </c>
+      <c r="D680" t="s">
+        <v>9</v>
+      </c>
+      <c r="F680" t="s">
+        <v>28</v>
+      </c>
+      <c r="G680" t="s">
+        <v>29</v>
+      </c>
+      <c r="H680" t="s">
+        <v>30</v>
+      </c>
+      <c r="I680">
+        <v>5</v>
+      </c>
+      <c r="J680" s="38">
+        <v>5.0000000000000002E-11</v>
+      </c>
+      <c r="K680" s="38">
+        <v>3.9999999999999998E-11</v>
+      </c>
+      <c r="L680" s="38">
+        <v>6.6666666666666669E-11</v>
+      </c>
+    </row>
+    <row r="681" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A681" t="s">
+        <v>31</v>
+      </c>
+      <c r="B681">
+        <v>-5.0000000000000002E-11</v>
+      </c>
+      <c r="C681" t="s">
+        <v>12</v>
+      </c>
+      <c r="D681" t="s">
+        <v>9</v>
+      </c>
+      <c r="F681" t="s">
+        <v>28</v>
+      </c>
+      <c r="G681" t="s">
+        <v>29</v>
+      </c>
+      <c r="H681" t="s">
+        <v>32</v>
+      </c>
+      <c r="I681">
+        <v>5</v>
+      </c>
+      <c r="J681">
+        <v>-5.0000000000000002E-11</v>
+      </c>
+      <c r="K681" s="38">
+        <v>-6.6666666666666669E-11</v>
+      </c>
+      <c r="L681" s="38">
+        <v>-3.9999999999999998E-11</v>
+      </c>
+      <c r="M681" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A682" t="s">
+        <v>33</v>
+      </c>
+      <c r="B682">
+        <v>3.4369999999999998</v>
+      </c>
+      <c r="C682" t="s">
+        <v>34</v>
+      </c>
+      <c r="D682" t="s">
+        <v>10</v>
+      </c>
+      <c r="F682" t="s">
+        <v>28</v>
+      </c>
+      <c r="G682" t="s">
+        <v>35</v>
+      </c>
+      <c r="H682" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="683" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A683" t="s">
+        <v>37</v>
+      </c>
+      <c r="B683">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="C683" t="s">
+        <v>38</v>
+      </c>
+      <c r="D683" t="s">
+        <v>10</v>
+      </c>
+      <c r="F683" t="s">
+        <v>28</v>
+      </c>
+      <c r="G683" t="s">
+        <v>39</v>
+      </c>
+      <c r="H683" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="684" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A684" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B684">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="C684" t="s">
+        <v>41</v>
+      </c>
+      <c r="D684" t="s">
+        <v>10</v>
+      </c>
+      <c r="F684" t="s">
+        <v>28</v>
+      </c>
+      <c r="G684" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="H684" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="685" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A685" t="s">
+        <v>43</v>
+      </c>
+      <c r="B685" s="40">
+        <v>-4.0000000000000001E-3</v>
+      </c>
+      <c r="C685" t="s">
+        <v>34</v>
+      </c>
+      <c r="D685" t="s">
+        <v>10</v>
+      </c>
+      <c r="F685" t="s">
+        <v>28</v>
+      </c>
+      <c r="G685" t="s">
+        <v>44</v>
+      </c>
+      <c r="H685" s="41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="686" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A686" t="s">
+        <v>45</v>
+      </c>
+      <c r="B686" s="42">
+        <v>-3.5000000000000001E-3</v>
+      </c>
+      <c r="C686" t="s">
+        <v>41</v>
+      </c>
+      <c r="D686" t="s">
+        <v>10</v>
+      </c>
+      <c r="F686" t="s">
+        <v>28</v>
+      </c>
+      <c r="G686" t="s">
+        <v>46</v>
+      </c>
+      <c r="H686" s="41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="687" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A687" t="s">
+        <v>47</v>
+      </c>
+      <c r="B687">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="C687" t="s">
+        <v>12</v>
+      </c>
+      <c r="D687" t="s">
+        <v>48</v>
+      </c>
+      <c r="F687" t="s">
+        <v>28</v>
+      </c>
+      <c r="G687" t="s">
+        <v>49</v>
+      </c>
+      <c r="H687" t="s">
+        <v>50</v>
+      </c>
+      <c r="I687">
+        <v>5</v>
+      </c>
+      <c r="J687">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="K687">
+        <v>0.33</v>
+      </c>
+      <c r="L687">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="688" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A688" t="s">
         <v>341</v>
       </c>
-      <c r="C669" s="37"/>
-      <c r="D669" s="37"/>
-      <c r="E669" s="37"/>
-      <c r="F669" s="37"/>
-      <c r="G669" s="37"/>
-      <c r="H669" s="37"/>
-      <c r="I669" s="37"/>
-      <c r="J669" s="37"/>
-      <c r="K669" s="37"/>
-      <c r="L669" s="37"/>
-      <c r="M669" s="37"/>
-      <c r="N669" s="37"/>
-      <c r="O669" s="37"/>
-      <c r="P669" s="37"/>
-      <c r="Q669" s="37"/>
-      <c r="R669" s="37"/>
-      <c r="S669" s="37"/>
-      <c r="T669" s="37"/>
-      <c r="U669" s="37"/>
-      <c r="V669" s="37"/>
-    </row>
-    <row r="670" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A670" s="37" t="s">
+      <c r="B688">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="C688" t="s">
+        <v>12</v>
+      </c>
+      <c r="D688" t="s">
+        <v>10</v>
+      </c>
+      <c r="F688" t="s">
+        <v>28</v>
+      </c>
+      <c r="G688" t="s">
+        <v>342</v>
+      </c>
+      <c r="H688" t="s">
+        <v>343</v>
+      </c>
+      <c r="I688">
+        <v>5</v>
+      </c>
+      <c r="J688">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="K688">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L688">
+        <v>0.1127777777777778</v>
+      </c>
+    </row>
+    <row r="689" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A689" t="s">
+        <v>55</v>
+      </c>
+      <c r="B689">
+        <v>1</v>
+      </c>
+      <c r="D689" t="s">
+        <v>10</v>
+      </c>
+      <c r="E689" t="s">
+        <v>56</v>
+      </c>
+      <c r="F689" t="s">
+        <v>57</v>
+      </c>
+      <c r="H689" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="691" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A691" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="692" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A692" t="s">
+        <v>4</v>
+      </c>
+      <c r="B692">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A693" t="s">
+        <v>5</v>
+      </c>
+      <c r="B693" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="694" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A694" t="s">
+        <v>7</v>
+      </c>
+      <c r="B694" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="695" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A695" t="s">
+        <v>9</v>
+      </c>
+      <c r="B695" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="696" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A696" t="s">
         <v>11</v>
       </c>
-      <c r="B670" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C670" s="37"/>
-      <c r="D670" s="37"/>
-      <c r="E670" s="37"/>
-      <c r="F670" s="37"/>
-      <c r="G670" s="37"/>
-      <c r="H670" s="37"/>
-      <c r="I670" s="37"/>
-      <c r="J670" s="37"/>
-      <c r="K670" s="37"/>
-      <c r="L670" s="37"/>
-      <c r="M670" s="37"/>
-      <c r="N670" s="37"/>
-      <c r="O670" s="37"/>
-      <c r="P670" s="37"/>
-      <c r="Q670" s="37"/>
-      <c r="R670" s="37"/>
-      <c r="S670" s="37"/>
-      <c r="T670" s="37"/>
-      <c r="U670" s="37"/>
-      <c r="V670" s="37"/>
-    </row>
-    <row r="671" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A671" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B671" s="37">
+      <c r="B696" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="697" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A697" t="s">
+        <v>13</v>
+      </c>
+      <c r="B697" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="698" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A698" t="s">
+        <v>15</v>
+      </c>
+      <c r="B698" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="699" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A699" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="700" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A700" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B700" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C700" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D700" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E700" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F700" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G700" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H700" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I700" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J700" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K700" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L700" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M700" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="701" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A701" t="s">
+        <v>344</v>
+      </c>
+      <c r="B701">
         <v>1</v>
       </c>
-      <c r="C671" s="37"/>
-      <c r="D671" s="37"/>
-      <c r="E671" s="37"/>
-      <c r="F671" s="37"/>
-      <c r="G671" s="37"/>
-      <c r="H671" s="37"/>
-      <c r="I671" s="37"/>
-      <c r="J671" s="37"/>
-      <c r="K671" s="37"/>
-      <c r="L671" s="37"/>
-      <c r="M671" s="37"/>
-      <c r="N671" s="37"/>
-      <c r="O671" s="37"/>
-      <c r="P671" s="37"/>
-      <c r="Q671" s="37"/>
-      <c r="R671" s="37"/>
-      <c r="S671" s="37"/>
-      <c r="T671" s="37"/>
-      <c r="U671" s="37"/>
-      <c r="V671" s="37"/>
-    </row>
-    <row r="672" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A672" s="37" t="s">
+      <c r="C701" t="s">
+        <v>12</v>
+      </c>
+      <c r="D701" t="s">
+        <v>10</v>
+      </c>
+      <c r="F701" t="s">
+        <v>26</v>
+      </c>
+      <c r="G701" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="702" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A702" t="s">
+        <v>27</v>
+      </c>
+      <c r="B702">
+        <v>5.0000000000000002E-11</v>
+      </c>
+      <c r="C702" t="s">
+        <v>12</v>
+      </c>
+      <c r="D702" t="s">
+        <v>9</v>
+      </c>
+      <c r="F702" t="s">
+        <v>28</v>
+      </c>
+      <c r="G702" t="s">
+        <v>29</v>
+      </c>
+      <c r="H702" t="s">
+        <v>30</v>
+      </c>
+      <c r="I702">
         <v>5</v>
       </c>
-      <c r="B672" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C672" s="37"/>
-      <c r="D672" s="37"/>
-      <c r="E672" s="37"/>
-      <c r="F672" s="37"/>
-      <c r="G672" s="37"/>
-      <c r="H672" s="37"/>
-      <c r="I672" s="37"/>
-      <c r="J672" s="37"/>
-      <c r="K672" s="37"/>
-      <c r="L672" s="37"/>
-      <c r="M672" s="37"/>
-      <c r="N672" s="37"/>
-      <c r="O672" s="37"/>
-      <c r="P672" s="37"/>
-      <c r="Q672" s="37"/>
-      <c r="R672" s="37"/>
-      <c r="S672" s="37"/>
-      <c r="T672" s="37"/>
-      <c r="U672" s="37"/>
-      <c r="V672" s="37"/>
-    </row>
-    <row r="673" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A673" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B673" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C673" s="37"/>
-      <c r="D673" s="37"/>
-      <c r="E673" s="37"/>
-      <c r="F673" s="37"/>
-      <c r="G673" s="37"/>
-      <c r="H673" s="37"/>
-      <c r="I673" s="37"/>
-      <c r="J673" s="37"/>
-      <c r="K673" s="37"/>
-      <c r="L673" s="37"/>
-      <c r="M673" s="37"/>
-      <c r="N673" s="37"/>
-      <c r="O673" s="37"/>
-      <c r="P673" s="37"/>
-      <c r="Q673" s="37"/>
-      <c r="R673" s="37"/>
-      <c r="S673" s="37"/>
-      <c r="T673" s="37"/>
-      <c r="U673" s="37"/>
-      <c r="V673" s="37"/>
-    </row>
-    <row r="674" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A674" s="37" t="s">
+      <c r="J702" s="38">
+        <v>5.0000000000000002E-11</v>
+      </c>
+      <c r="K702" s="38">
+        <v>3.9999999999999998E-11</v>
+      </c>
+      <c r="L702" s="38">
+        <v>6.6666666666666669E-11</v>
+      </c>
+    </row>
+    <row r="703" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A703" t="s">
+        <v>31</v>
+      </c>
+      <c r="B703">
+        <v>-5.0000000000000002E-11</v>
+      </c>
+      <c r="C703" t="s">
+        <v>12</v>
+      </c>
+      <c r="D703" t="s">
         <v>9</v>
       </c>
-      <c r="B674" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C674" s="37"/>
-      <c r="D674" s="37"/>
-      <c r="E674" s="37"/>
-      <c r="F674" s="37"/>
-      <c r="G674" s="37"/>
-      <c r="H674" s="37"/>
-      <c r="I674" s="37"/>
-      <c r="J674" s="37"/>
-      <c r="K674" s="37"/>
-      <c r="L674" s="37"/>
-      <c r="M674" s="37"/>
-      <c r="N674" s="37"/>
-      <c r="O674" s="37"/>
-      <c r="P674" s="37"/>
-      <c r="Q674" s="37"/>
-      <c r="R674" s="37"/>
-      <c r="S674" s="37"/>
-      <c r="T674" s="37"/>
-      <c r="U674" s="37"/>
-      <c r="V674" s="37"/>
-    </row>
-    <row r="675" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A675" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B675" t="s">
-        <v>342</v>
-      </c>
-      <c r="C675" s="37"/>
-      <c r="D675" s="37"/>
-      <c r="E675" s="37"/>
-      <c r="F675" s="37"/>
-      <c r="G675" s="37"/>
-      <c r="H675" s="37"/>
-      <c r="I675" s="37"/>
-      <c r="J675" s="37"/>
-      <c r="K675" s="37"/>
-      <c r="L675" s="37"/>
-      <c r="M675" s="37"/>
-      <c r="N675" s="37"/>
-      <c r="O675" s="37"/>
-      <c r="P675" s="37"/>
-      <c r="Q675" s="37"/>
-      <c r="R675" s="37"/>
-      <c r="S675" s="37"/>
-      <c r="T675" s="37"/>
-      <c r="U675" s="37"/>
-      <c r="V675" s="37"/>
-    </row>
-    <row r="676" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A676" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="B676" s="37"/>
-      <c r="C676" s="37"/>
-      <c r="D676" s="37"/>
-      <c r="E676" s="37"/>
-      <c r="F676" s="37"/>
-      <c r="G676" s="37"/>
-      <c r="H676" s="37"/>
-      <c r="I676" s="37"/>
-      <c r="J676" s="37"/>
-      <c r="K676" s="37"/>
-      <c r="L676" s="37"/>
-      <c r="M676" s="37"/>
-      <c r="N676" s="37"/>
-      <c r="O676" s="37"/>
-      <c r="P676" s="37"/>
-      <c r="Q676" s="37"/>
-      <c r="R676" s="37"/>
-      <c r="S676" s="37"/>
-      <c r="T676" s="37"/>
-      <c r="U676" s="37"/>
-      <c r="V676" s="37"/>
-    </row>
-    <row r="677" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A677" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B677" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C677" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D677" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E677" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F677" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G677" s="5" t="s">
+      <c r="F703" t="s">
+        <v>28</v>
+      </c>
+      <c r="G703" t="s">
+        <v>29</v>
+      </c>
+      <c r="H703" t="s">
+        <v>32</v>
+      </c>
+      <c r="I703">
         <v>5</v>
       </c>
-      <c r="H677" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I677" s="5"/>
-      <c r="J677" s="5"/>
-      <c r="K677" s="5"/>
-      <c r="L677" s="5"/>
-      <c r="M677" s="5"/>
-      <c r="N677" s="5"/>
-      <c r="O677" s="5"/>
-      <c r="P677" s="5"/>
-      <c r="Q677" s="5"/>
-      <c r="R677" s="5"/>
-      <c r="S677" s="5"/>
-      <c r="T677" s="37"/>
-      <c r="U677" s="37"/>
-      <c r="V677" s="37"/>
-    </row>
-    <row r="678" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A678" s="28" t="s">
-        <v>341</v>
-      </c>
-      <c r="B678" s="38">
+      <c r="J703" s="38">
+        <v>-5.0000000000000002E-11</v>
+      </c>
+      <c r="K703" s="38">
+        <v>-6.6666666666666669E-11</v>
+      </c>
+      <c r="L703" s="38">
+        <v>-3.9999999999999998E-11</v>
+      </c>
+      <c r="M703" t="b">
         <v>1</v>
       </c>
-      <c r="C678" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D678" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E678" s="37"/>
-      <c r="F678" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G678" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="H678" s="37"/>
-      <c r="I678" s="37"/>
-      <c r="J678" s="37"/>
-      <c r="K678" s="37"/>
-      <c r="L678" s="37"/>
-      <c r="M678" s="37"/>
-      <c r="N678" s="37"/>
-      <c r="O678" s="37"/>
-      <c r="P678" s="37"/>
-      <c r="Q678" s="37"/>
-      <c r="R678" s="37"/>
-      <c r="S678" s="37"/>
-      <c r="T678" s="37"/>
-      <c r="U678" s="37"/>
-      <c r="V678" s="37"/>
-    </row>
-    <row r="679" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A679" t="s">
-        <v>343</v>
-      </c>
-      <c r="B679">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="C679" t="s">
-        <v>74</v>
-      </c>
-      <c r="D679" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F679" t="s">
-        <v>28</v>
-      </c>
-      <c r="G679" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="681" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A681" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B681" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="C681" s="37"/>
-      <c r="D681" s="37"/>
-      <c r="E681" s="37"/>
-      <c r="F681" s="37"/>
-      <c r="G681" s="37"/>
-      <c r="H681" s="37"/>
-      <c r="I681" s="37"/>
-      <c r="J681" s="37"/>
-      <c r="K681" s="37"/>
-      <c r="L681" s="37"/>
-      <c r="M681" s="37"/>
-      <c r="N681" s="37"/>
-      <c r="O681" s="37"/>
-      <c r="P681" s="37"/>
-      <c r="Q681" s="37"/>
-      <c r="R681" s="37"/>
-      <c r="S681" s="37"/>
-      <c r="T681" s="37"/>
-      <c r="U681" s="37"/>
-      <c r="V681" s="37"/>
-    </row>
-    <row r="682" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A682" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B682" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C682" s="37"/>
-      <c r="D682" s="37"/>
-      <c r="E682" s="37"/>
-      <c r="F682" s="37"/>
-      <c r="G682" s="37"/>
-      <c r="H682" s="37"/>
-      <c r="I682" s="37"/>
-      <c r="J682" s="37"/>
-      <c r="K682" s="37"/>
-      <c r="L682" s="37"/>
-      <c r="M682" s="37"/>
-      <c r="N682" s="37"/>
-      <c r="O682" s="37"/>
-      <c r="P682" s="37"/>
-      <c r="Q682" s="37"/>
-      <c r="R682" s="37"/>
-      <c r="S682" s="37"/>
-      <c r="T682" s="37"/>
-      <c r="U682" s="37"/>
-      <c r="V682" s="37"/>
-    </row>
-    <row r="683" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A683" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B683" s="37">
-        <v>1</v>
-      </c>
-      <c r="C683" s="37"/>
-      <c r="D683" s="37"/>
-      <c r="E683" s="37"/>
-      <c r="F683" s="37"/>
-      <c r="G683" s="37"/>
-      <c r="H683" s="37"/>
-      <c r="I683" s="37"/>
-      <c r="J683" s="37"/>
-      <c r="K683" s="37"/>
-      <c r="L683" s="37"/>
-      <c r="M683" s="37"/>
-      <c r="N683" s="37"/>
-      <c r="O683" s="37"/>
-      <c r="P683" s="37"/>
-      <c r="Q683" s="37"/>
-      <c r="R683" s="37"/>
-      <c r="S683" s="37"/>
-      <c r="T683" s="37"/>
-      <c r="U683" s="37"/>
-      <c r="V683" s="37"/>
-    </row>
-    <row r="684" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A684" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B684" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C684" s="37"/>
-      <c r="D684" s="37"/>
-      <c r="E684" s="37"/>
-      <c r="F684" s="37"/>
-      <c r="G684" s="37"/>
-      <c r="H684" s="37"/>
-      <c r="I684" s="37"/>
-      <c r="J684" s="37"/>
-      <c r="K684" s="37"/>
-      <c r="L684" s="37"/>
-      <c r="M684" s="37"/>
-      <c r="N684" s="37"/>
-      <c r="O684" s="37"/>
-      <c r="P684" s="37"/>
-      <c r="Q684" s="37"/>
-      <c r="R684" s="37"/>
-      <c r="S684" s="37"/>
-      <c r="T684" s="37"/>
-      <c r="U684" s="37"/>
-      <c r="V684" s="37"/>
-    </row>
-    <row r="685" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A685" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B685" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C685" s="37"/>
-      <c r="D685" s="37"/>
-      <c r="E685" s="37"/>
-      <c r="F685" s="37"/>
-      <c r="G685" s="37"/>
-      <c r="H685" s="37"/>
-      <c r="I685" s="37"/>
-      <c r="J685" s="37"/>
-      <c r="K685" s="37"/>
-      <c r="L685" s="37"/>
-      <c r="M685" s="37"/>
-      <c r="N685" s="37"/>
-      <c r="O685" s="37"/>
-      <c r="P685" s="37"/>
-      <c r="Q685" s="37"/>
-      <c r="R685" s="37"/>
-      <c r="S685" s="37"/>
-      <c r="T685" s="37"/>
-      <c r="U685" s="37"/>
-      <c r="V685" s="37"/>
-    </row>
-    <row r="686" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A686" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B686" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C686" s="37"/>
-      <c r="D686" s="37"/>
-      <c r="E686" s="37"/>
-      <c r="F686" s="37"/>
-      <c r="G686" s="37"/>
-      <c r="H686" s="37"/>
-      <c r="I686" s="37"/>
-      <c r="J686" s="37"/>
-      <c r="K686" s="37"/>
-      <c r="L686" s="37"/>
-      <c r="M686" s="37"/>
-      <c r="N686" s="37"/>
-      <c r="O686" s="37"/>
-      <c r="P686" s="37"/>
-      <c r="Q686" s="37"/>
-      <c r="R686" s="37"/>
-      <c r="S686" s="37"/>
-      <c r="T686" s="37"/>
-      <c r="U686" s="37"/>
-      <c r="V686" s="37"/>
-    </row>
-    <row r="687" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A687" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="B687" t="s">
-        <v>342</v>
-      </c>
-      <c r="C687" s="37"/>
-      <c r="D687" s="37"/>
-      <c r="E687" s="37"/>
-      <c r="F687" s="37"/>
-      <c r="G687" s="37"/>
-      <c r="H687" s="37"/>
-      <c r="I687" s="37"/>
-      <c r="J687" s="37"/>
-      <c r="K687" s="37"/>
-      <c r="L687" s="37"/>
-      <c r="M687" s="37"/>
-      <c r="N687" s="37"/>
-      <c r="O687" s="37"/>
-      <c r="P687" s="37"/>
-      <c r="Q687" s="37"/>
-      <c r="R687" s="37"/>
-      <c r="S687" s="37"/>
-      <c r="T687" s="37"/>
-      <c r="U687" s="37"/>
-      <c r="V687" s="37"/>
-    </row>
-    <row r="688" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A688" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="B688" s="37"/>
-      <c r="C688" s="37"/>
-      <c r="D688" s="37"/>
-      <c r="E688" s="37"/>
-      <c r="F688" s="37"/>
-      <c r="G688" s="37"/>
-      <c r="H688" s="37"/>
-      <c r="I688" s="37"/>
-      <c r="J688" s="37"/>
-      <c r="K688" s="37"/>
-      <c r="L688" s="37"/>
-      <c r="M688" s="37"/>
-      <c r="N688" s="37"/>
-      <c r="O688" s="37"/>
-      <c r="P688" s="37"/>
-      <c r="Q688" s="37"/>
-      <c r="R688" s="37"/>
-      <c r="S688" s="37"/>
-      <c r="T688" s="37"/>
-      <c r="U688" s="37"/>
-      <c r="V688" s="37"/>
-    </row>
-    <row r="689" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A689" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B689" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C689" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D689" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E689" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F689" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G689" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H689" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I689" s="5"/>
-      <c r="J689" s="5"/>
-      <c r="K689" s="5"/>
-      <c r="L689" s="5"/>
-      <c r="M689" s="5"/>
-      <c r="N689" s="5"/>
-      <c r="O689" s="5"/>
-      <c r="P689" s="5"/>
-      <c r="Q689" s="5"/>
-      <c r="R689" s="5"/>
-      <c r="S689" s="5"/>
-      <c r="T689" s="37"/>
-      <c r="U689" s="37"/>
-      <c r="V689" s="37"/>
-    </row>
-    <row r="690" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A690" s="28" t="s">
-        <v>345</v>
-      </c>
-      <c r="B690" s="38">
-        <v>1</v>
-      </c>
-      <c r="C690" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D690" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E690" s="37"/>
-      <c r="F690" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="G690" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="H690" s="37"/>
-      <c r="I690" s="37"/>
-      <c r="J690" s="37"/>
-      <c r="K690" s="37"/>
-      <c r="L690" s="37"/>
-      <c r="M690" s="37"/>
-      <c r="N690" s="37"/>
-      <c r="O690" s="37"/>
-      <c r="P690" s="37"/>
-      <c r="Q690" s="37"/>
-      <c r="R690" s="37"/>
-      <c r="S690" s="37"/>
-      <c r="T690" s="37"/>
-      <c r="U690" s="37"/>
-      <c r="V690" s="37"/>
-    </row>
-    <row r="691" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A691" t="s">
-        <v>346</v>
-      </c>
-      <c r="B691">
-        <v>0.56818181818181823</v>
-      </c>
-      <c r="C691" t="s">
-        <v>74</v>
-      </c>
-      <c r="D691" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F691" t="s">
-        <v>28</v>
-      </c>
-      <c r="G691" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="693" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A693" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B693" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="694" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A694" t="s">
-        <v>4</v>
-      </c>
-      <c r="B694">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="695" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A695" t="s">
-        <v>5</v>
-      </c>
-      <c r="B695" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="696" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A696" t="s">
-        <v>7</v>
-      </c>
-      <c r="B696" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="697" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A697" t="s">
-        <v>9</v>
-      </c>
-      <c r="B697" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="698" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A698" t="s">
-        <v>11</v>
-      </c>
-      <c r="B698" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="699" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A699" t="s">
-        <v>13</v>
-      </c>
-      <c r="B699" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="700" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A700" t="s">
-        <v>15</v>
-      </c>
-      <c r="B700" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="701" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A701" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="702" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A702" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B702" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C702" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D702" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E702" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F702" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G702" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H702" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I702" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J702" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K702" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L702" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M702" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="703" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A703" t="s">
-        <v>348</v>
-      </c>
-      <c r="B703">
-        <v>1</v>
-      </c>
-      <c r="C703" t="s">
-        <v>12</v>
-      </c>
-      <c r="D703" t="s">
-        <v>10</v>
-      </c>
-      <c r="F703" t="s">
-        <v>26</v>
-      </c>
-      <c r="G703" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="704" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="704" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B704">
-        <v>5.0000000000000002E-11</v>
+        <v>3.4369999999999998</v>
       </c>
       <c r="C704" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D704" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F704" t="s">
         <v>28</v>
       </c>
       <c r="G704" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H704" t="s">
-        <v>30</v>
-      </c>
-      <c r="I704">
-        <v>5</v>
-      </c>
-      <c r="J704" s="39">
-        <v>5.0000000000000002E-11</v>
-      </c>
-      <c r="K704" s="39">
-        <v>3.9999999999999998E-11</v>
-      </c>
-      <c r="L704" s="39">
-        <v>6.6666666666666669E-11</v>
-      </c>
-    </row>
-    <row r="705" spans="1:13" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="705" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B705">
-        <v>-5.0000000000000002E-11</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C705" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D705" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F705" t="s">
         <v>28</v>
       </c>
       <c r="G705" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H705" t="s">
-        <v>32</v>
-      </c>
-      <c r="I705">
-        <v>5</v>
-      </c>
-      <c r="J705">
-        <v>-5.0000000000000002E-11</v>
-      </c>
-      <c r="K705" s="39">
-        <v>-6.6666666666666669E-11</v>
-      </c>
-      <c r="L705" s="39">
-        <v>-3.9999999999999998E-11</v>
-      </c>
-      <c r="M705" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="706" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A706" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="706" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A706" s="39" t="s">
+        <v>40</v>
       </c>
       <c r="B706">
-        <v>3.4369999999999998</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="C706" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D706" t="s">
         <v>10</v>
@@ -14743,22 +14532,22 @@
       <c r="F706" t="s">
         <v>28</v>
       </c>
-      <c r="G706" t="s">
-        <v>35</v>
+      <c r="G706" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="H706" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="707" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
-        <v>37</v>
-      </c>
-      <c r="B707">
-        <v>4.0000000000000001E-3</v>
+        <v>43</v>
+      </c>
+      <c r="B707" s="40">
+        <v>-4.0000000000000001E-3</v>
       </c>
       <c r="C707" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D707" t="s">
         <v>10</v>
@@ -14767,18 +14556,18 @@
         <v>28</v>
       </c>
       <c r="G707" t="s">
-        <v>39</v>
-      </c>
-      <c r="H707" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="708" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A708" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B708">
-        <v>3.5000000000000001E-3</v>
+        <v>44</v>
+      </c>
+      <c r="H707" s="41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="708" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A708" t="s">
+        <v>45</v>
+      </c>
+      <c r="B708" s="42">
+        <v>-3.5000000000000001E-3</v>
       </c>
       <c r="C708" t="s">
         <v>41</v>
@@ -14789,45 +14578,57 @@
       <c r="F708" t="s">
         <v>28</v>
       </c>
-      <c r="G708" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="H708" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="709" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G708" t="s">
+        <v>46</v>
+      </c>
+      <c r="H708" s="41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="709" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
-        <v>43</v>
-      </c>
-      <c r="B709" s="41">
-        <v>-4.0000000000000001E-3</v>
+        <v>47</v>
+      </c>
+      <c r="B709">
+        <v>0.34499999999999997</v>
       </c>
       <c r="C709" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D709" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F709" t="s">
         <v>28</v>
       </c>
       <c r="G709" t="s">
-        <v>44</v>
-      </c>
-      <c r="H709" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="710" spans="1:13" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="H709" t="s">
+        <v>50</v>
+      </c>
+      <c r="I709">
+        <v>5</v>
+      </c>
+      <c r="J709">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="K709">
+        <v>0.33</v>
+      </c>
+      <c r="L709">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="710" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
-        <v>45</v>
-      </c>
-      <c r="B710" s="43">
-        <v>-3.5000000000000001E-3</v>
+        <v>341</v>
+      </c>
+      <c r="B710">
+        <v>8.4999999999999992E-2</v>
       </c>
       <c r="C710" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D710" t="s">
         <v>10</v>
@@ -14836,238 +14637,238 @@
         <v>28</v>
       </c>
       <c r="G710" t="s">
-        <v>46</v>
-      </c>
-      <c r="H710" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="711" spans="1:13" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+      <c r="H710" t="s">
+        <v>343</v>
+      </c>
+      <c r="I710">
+        <v>5</v>
+      </c>
+      <c r="J710">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="K710">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L710">
+        <v>0.1127777777777778</v>
+      </c>
+    </row>
+    <row r="711" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B711">
-        <v>0.34499999999999997</v>
+        <v>1</v>
       </c>
       <c r="C711" t="s">
         <v>12</v>
       </c>
       <c r="D711" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="F711" t="s">
         <v>28</v>
       </c>
-      <c r="G711" t="s">
-        <v>49</v>
+      <c r="G711" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="H711" t="s">
-        <v>50</v>
-      </c>
-      <c r="I711">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="712" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A712" t="s">
+        <v>55</v>
+      </c>
+      <c r="B712">
+        <v>1</v>
+      </c>
+      <c r="D712" t="s">
+        <v>10</v>
+      </c>
+      <c r="E712" t="s">
+        <v>56</v>
+      </c>
+      <c r="F712" t="s">
+        <v>57</v>
+      </c>
+      <c r="H712" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="714" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A714" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B714" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="715" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A715" t="s">
+        <v>4</v>
+      </c>
+      <c r="B715">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="716" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A716" t="s">
         <v>5</v>
       </c>
-      <c r="J711">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="K711">
-        <v>0.33</v>
-      </c>
-      <c r="L711">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="712" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A712" t="s">
-        <v>350</v>
-      </c>
-      <c r="B712">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="C712" t="s">
-        <v>12</v>
-      </c>
-      <c r="D712" t="s">
-        <v>10</v>
-      </c>
-      <c r="F712" t="s">
-        <v>28</v>
-      </c>
-      <c r="G712" t="s">
-        <v>351</v>
-      </c>
-      <c r="H712" t="s">
-        <v>352</v>
-      </c>
-      <c r="I712">
-        <v>5</v>
-      </c>
-      <c r="J712">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="K712">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="L712">
-        <v>0.1127777777777778</v>
-      </c>
-    </row>
-    <row r="713" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A713" t="s">
-        <v>55</v>
-      </c>
-      <c r="B713">
-        <v>1</v>
-      </c>
-      <c r="D713" t="s">
-        <v>10</v>
-      </c>
-      <c r="E713" t="s">
-        <v>56</v>
-      </c>
-      <c r="F713" t="s">
-        <v>57</v>
-      </c>
-      <c r="H713" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="715" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A715" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B715" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="716" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A716" t="s">
-        <v>4</v>
-      </c>
-      <c r="B716">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="717" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B716" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="717" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B717" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="718" spans="1:13" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="718" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B718" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="719" spans="1:13" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="719" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B719" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="720" spans="1:13" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="720" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B720" t="s">
-        <v>12</v>
+        <v>346</v>
       </c>
     </row>
     <row r="721" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
+        <v>15</v>
+      </c>
+      <c r="B721" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="722" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A722" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="723" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A723" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B723" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C723" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D723" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E723" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F723" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G723" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H723" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B721" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="722" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A722" t="s">
-        <v>15</v>
-      </c>
-      <c r="B722" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="723" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A723" s="1" t="s">
-        <v>17</v>
+      <c r="I723" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J723" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K723" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L723" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M723" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="724" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A724" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B724" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C724" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D724" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E724" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F724" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G724" s="5" t="s">
+      <c r="A724" t="s">
+        <v>345</v>
+      </c>
+      <c r="B724">
+        <v>1</v>
+      </c>
+      <c r="C724" t="s">
+        <v>12</v>
+      </c>
+      <c r="D724" t="s">
+        <v>10</v>
+      </c>
+      <c r="F724" t="s">
+        <v>26</v>
+      </c>
+      <c r="G724" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="725" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A725" t="s">
+        <v>125</v>
+      </c>
+      <c r="B725">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C725" t="s">
+        <v>12</v>
+      </c>
+      <c r="D725" t="s">
+        <v>10</v>
+      </c>
+      <c r="F725" t="s">
+        <v>28</v>
+      </c>
+      <c r="G725" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H725" t="s">
+        <v>127</v>
+      </c>
+      <c r="I725">
         <v>5</v>
       </c>
-      <c r="H724" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I724" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J724" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K724" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L724" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M724" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="725" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A725" t="s">
-        <v>353</v>
-      </c>
-      <c r="B725">
-        <v>1</v>
-      </c>
-      <c r="C725" t="s">
-        <v>12</v>
-      </c>
-      <c r="D725" t="s">
-        <v>10</v>
-      </c>
-      <c r="F725" t="s">
-        <v>26</v>
-      </c>
-      <c r="G725" t="s">
-        <v>6</v>
+      <c r="J725" s="43">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K725">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L725">
+        <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="726" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="B726">
-        <v>5.0000000000000002E-11</v>
+        <v>5.0000000000000003E-10</v>
       </c>
       <c r="C726" t="s">
         <v>12</v>
@@ -15087,22 +14888,22 @@
       <c r="I726">
         <v>5</v>
       </c>
-      <c r="J726" s="39">
-        <v>5.0000000000000002E-11</v>
-      </c>
-      <c r="K726" s="39">
-        <v>3.9999999999999998E-11</v>
-      </c>
-      <c r="L726" s="39">
-        <v>6.6666666666666669E-11</v>
+      <c r="J726" s="38">
+        <v>5.0000000000000003E-10</v>
+      </c>
+      <c r="K726">
+        <v>4.0000000000000001E-10</v>
+      </c>
+      <c r="L726" s="38">
+        <v>6.6666666666666664E-10</v>
       </c>
     </row>
     <row r="727" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="B727">
-        <v>-5.0000000000000002E-11</v>
+        <v>-5.0000000000000003E-10</v>
       </c>
       <c r="C727" t="s">
         <v>12</v>
@@ -15122,14 +14923,14 @@
       <c r="I727">
         <v>5</v>
       </c>
-      <c r="J727" s="39">
-        <v>-5.0000000000000002E-11</v>
-      </c>
-      <c r="K727" s="39">
-        <v>-6.6666666666666669E-11</v>
-      </c>
-      <c r="L727" s="39">
-        <v>-3.9999999999999998E-11</v>
+      <c r="J727">
+        <v>-5.0000000000000003E-10</v>
+      </c>
+      <c r="K727">
+        <v>-6.6666666666666664E-10</v>
+      </c>
+      <c r="L727">
+        <v>-4.0000000000000001E-10</v>
       </c>
       <c r="M727" t="b">
         <v>1</v>
@@ -15137,36 +14938,48 @@
     </row>
     <row r="728" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B728">
-        <v>3.4369999999999998</v>
+        <v>0.7</v>
       </c>
       <c r="C728" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D728" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F728" t="s">
         <v>28</v>
       </c>
       <c r="G728" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="H728" t="s">
-        <v>36</v>
+        <v>347</v>
+      </c>
+      <c r="I728">
+        <v>5</v>
+      </c>
+      <c r="J728">
+        <v>0.5</v>
+      </c>
+      <c r="K728">
+        <v>0.5</v>
+      </c>
+      <c r="L728">
+        <v>0.7</v>
       </c>
     </row>
     <row r="729" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
-        <v>37</v>
+        <v>341</v>
       </c>
       <c r="B729">
-        <v>4.0000000000000001E-3</v>
+        <v>0.11018518518518521</v>
       </c>
       <c r="C729" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D729" t="s">
         <v>10</v>
@@ -15175,307 +14988,355 @@
         <v>28</v>
       </c>
       <c r="G729" t="s">
-        <v>39</v>
+        <v>342</v>
       </c>
       <c r="H729" t="s">
-        <v>36</v>
+        <v>348</v>
+      </c>
+      <c r="I729">
+        <v>5</v>
+      </c>
+      <c r="J729">
+        <v>0.05</v>
+      </c>
+      <c r="K729">
+        <v>0.05</v>
+      </c>
+      <c r="L729">
+        <v>0.11018518518518521</v>
       </c>
     </row>
     <row r="730" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A730" s="40" t="s">
-        <v>40</v>
+      <c r="A730" t="s">
+        <v>55</v>
       </c>
       <c r="B730">
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="C730" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D730" t="s">
         <v>10</v>
       </c>
+      <c r="E730" t="s">
+        <v>56</v>
+      </c>
       <c r="F730" t="s">
-        <v>28</v>
-      </c>
-      <c r="G730" s="40" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="H730" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="731" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A731" t="s">
-        <v>43</v>
-      </c>
-      <c r="B731" s="41">
-        <v>-4.0000000000000001E-3</v>
-      </c>
-      <c r="C731" t="s">
-        <v>34</v>
-      </c>
-      <c r="D731" t="s">
-        <v>10</v>
-      </c>
-      <c r="F731" t="s">
-        <v>28</v>
-      </c>
-      <c r="G731" t="s">
-        <v>44</v>
-      </c>
-      <c r="H731" s="42" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="732" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A732" t="s">
-        <v>45</v>
-      </c>
-      <c r="B732" s="43">
-        <v>-3.5000000000000001E-3</v>
-      </c>
-      <c r="C732" t="s">
-        <v>41</v>
-      </c>
-      <c r="D732" t="s">
-        <v>10</v>
-      </c>
-      <c r="F732" t="s">
-        <v>28</v>
-      </c>
-      <c r="G732" t="s">
-        <v>46</v>
-      </c>
-      <c r="H732" s="42" t="s">
-        <v>32</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="732" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A732" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B732" s="1" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="733" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B733">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="C733" t="s">
-        <v>12</v>
-      </c>
-      <c r="D733" t="s">
-        <v>48</v>
-      </c>
-      <c r="F733" t="s">
-        <v>28</v>
-      </c>
-      <c r="G733" t="s">
-        <v>49</v>
-      </c>
-      <c r="H733" t="s">
-        <v>50</v>
-      </c>
-      <c r="I733">
-        <v>5</v>
-      </c>
-      <c r="J733">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="K733">
-        <v>0.33</v>
-      </c>
-      <c r="L733">
-        <v>0.44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="734" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
-        <v>350</v>
-      </c>
-      <c r="B734">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="C734" t="s">
-        <v>12</v>
-      </c>
-      <c r="D734" t="s">
-        <v>10</v>
-      </c>
-      <c r="F734" t="s">
-        <v>28</v>
-      </c>
-      <c r="G734" t="s">
-        <v>351</v>
-      </c>
-      <c r="H734" t="s">
-        <v>352</v>
-      </c>
-      <c r="I734">
         <v>5</v>
       </c>
-      <c r="J734">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="K734">
-        <v>8.4999999999999992E-2</v>
-      </c>
-      <c r="L734">
-        <v>0.1127777777777778</v>
+      <c r="B734" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="735" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
-        <v>60</v>
-      </c>
-      <c r="B735">
-        <v>1</v>
-      </c>
-      <c r="C735" t="s">
-        <v>12</v>
-      </c>
-      <c r="D735" t="s">
-        <v>10</v>
-      </c>
-      <c r="F735" t="s">
-        <v>28</v>
-      </c>
-      <c r="G735" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H735" t="s">
-        <v>62</v>
+        <v>7</v>
+      </c>
+      <c r="B735" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="736" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
-        <v>55</v>
-      </c>
-      <c r="B736">
-        <v>1</v>
-      </c>
-      <c r="D736" t="s">
-        <v>10</v>
-      </c>
-      <c r="E736" t="s">
-        <v>56</v>
-      </c>
-      <c r="F736" t="s">
-        <v>57</v>
-      </c>
-      <c r="H736" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="B736" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="737" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A737" t="s">
+        <v>11</v>
+      </c>
+      <c r="B737" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="738" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A738" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B738" s="1" t="s">
-        <v>354</v>
+      <c r="A738" t="s">
+        <v>13</v>
+      </c>
+      <c r="B738" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="739" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
-        <v>4</v>
-      </c>
-      <c r="B739">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="740" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A740" t="s">
-        <v>5</v>
-      </c>
-      <c r="B740" t="s">
-        <v>6</v>
+        <v>15</v>
+      </c>
+      <c r="B739" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="740" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+      <c r="A740" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="741" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
+        <v>18</v>
+      </c>
+      <c r="B741" t="s">
+        <v>19</v>
+      </c>
+      <c r="C741" t="s">
+        <v>11</v>
+      </c>
+      <c r="D741" t="s">
+        <v>9</v>
+      </c>
+      <c r="E741" t="s">
+        <v>20</v>
+      </c>
+      <c r="F741" t="s">
         <v>7</v>
       </c>
-      <c r="B741" t="s">
-        <v>8</v>
+      <c r="G741" t="s">
+        <v>5</v>
+      </c>
+      <c r="H741" t="s">
+        <v>13</v>
+      </c>
+      <c r="I741" t="s">
+        <v>21</v>
+      </c>
+      <c r="J741" t="s">
+        <v>22</v>
+      </c>
+      <c r="K741" t="s">
+        <v>23</v>
+      </c>
+      <c r="L741" t="s">
+        <v>24</v>
+      </c>
+      <c r="M741" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="742" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
-        <v>9</v>
-      </c>
-      <c r="B742" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="743" spans="1:13" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+      <c r="B742">
+        <v>1</v>
+      </c>
+      <c r="C742" t="s">
+        <v>12</v>
+      </c>
+      <c r="D742" t="s">
+        <v>10</v>
+      </c>
+      <c r="F742" t="s">
+        <v>26</v>
+      </c>
+      <c r="G742" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="743" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
-        <v>11</v>
-      </c>
-      <c r="B743" t="s">
-        <v>12</v>
+        <v>125</v>
+      </c>
+      <c r="B743">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C743" t="s">
+        <v>12</v>
+      </c>
+      <c r="D743" t="s">
+        <v>10</v>
+      </c>
+      <c r="F743" t="s">
+        <v>28</v>
+      </c>
+      <c r="G743" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H743" t="s">
+        <v>36</v>
+      </c>
+      <c r="I743">
+        <v>5</v>
+      </c>
+      <c r="J743">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K743">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L743">
+        <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="744" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
-        <v>13</v>
-      </c>
-      <c r="B744" t="s">
-        <v>355</v>
+        <v>128</v>
+      </c>
+      <c r="B744">
+        <v>5.0000000000000003E-10</v>
+      </c>
+      <c r="C744" t="s">
+        <v>12</v>
+      </c>
+      <c r="D744" t="s">
+        <v>9</v>
+      </c>
+      <c r="F744" t="s">
+        <v>28</v>
+      </c>
+      <c r="G744" t="s">
+        <v>29</v>
+      </c>
+      <c r="H744" t="s">
+        <v>30</v>
+      </c>
+      <c r="I744">
+        <v>5</v>
+      </c>
+      <c r="J744" s="38">
+        <v>5.0000000000000003E-10</v>
+      </c>
+      <c r="K744">
+        <v>4.0000000000000001E-10</v>
+      </c>
+      <c r="L744" s="38">
+        <v>6.6666666666666664E-10</v>
       </c>
     </row>
     <row r="745" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
-        <v>15</v>
-      </c>
-      <c r="B745" t="s">
-        <v>16</v>
+        <v>129</v>
+      </c>
+      <c r="B745">
+        <v>-5.0000000000000003E-10</v>
+      </c>
+      <c r="C745" t="s">
+        <v>12</v>
+      </c>
+      <c r="D745" t="s">
+        <v>9</v>
+      </c>
+      <c r="F745" t="s">
+        <v>28</v>
+      </c>
+      <c r="G745" t="s">
+        <v>29</v>
+      </c>
+      <c r="H745" t="s">
+        <v>32</v>
+      </c>
+      <c r="I745">
+        <v>5</v>
+      </c>
+      <c r="J745">
+        <v>-5.0000000000000003E-10</v>
+      </c>
+      <c r="K745">
+        <v>-6.6666666666666664E-10</v>
+      </c>
+      <c r="L745">
+        <v>-4.0000000000000001E-10</v>
+      </c>
+      <c r="M745" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="746" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A746" s="1" t="s">
-        <v>17</v>
+      <c r="A746" t="s">
+        <v>47</v>
+      </c>
+      <c r="B746">
+        <v>0.7</v>
+      </c>
+      <c r="C746" t="s">
+        <v>12</v>
+      </c>
+      <c r="D746" t="s">
+        <v>48</v>
+      </c>
+      <c r="F746" t="s">
+        <v>28</v>
+      </c>
+      <c r="G746" t="s">
+        <v>49</v>
+      </c>
+      <c r="H746" t="s">
+        <v>347</v>
+      </c>
+      <c r="I746">
+        <v>5</v>
+      </c>
+      <c r="J746">
+        <v>0.5</v>
+      </c>
+      <c r="K746">
+        <v>0.5</v>
+      </c>
+      <c r="L746">
+        <v>0.7</v>
       </c>
     </row>
     <row r="747" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A747" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B747" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C747" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D747" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E747" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F747" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G747" s="5" t="s">
+      <c r="A747" t="s">
+        <v>341</v>
+      </c>
+      <c r="B747">
+        <v>0.11018518518518521</v>
+      </c>
+      <c r="C747" t="s">
+        <v>12</v>
+      </c>
+      <c r="D747" t="s">
+        <v>10</v>
+      </c>
+      <c r="F747" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" t="s">
+        <v>342</v>
+      </c>
+      <c r="H747" t="s">
+        <v>348</v>
+      </c>
+      <c r="I747">
         <v>5</v>
       </c>
-      <c r="H747" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I747" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J747" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K747" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L747" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M747" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="748" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="J747">
+        <v>0.05</v>
+      </c>
+      <c r="K747">
+        <v>0.05</v>
+      </c>
+      <c r="L747">
+        <v>0.11018518518518521</v>
+      </c>
+    </row>
+    <row r="748" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
-        <v>354</v>
+        <v>60</v>
       </c>
       <c r="B748">
         <v>1</v>
@@ -15487,561 +15348,39 @@
         <v>10</v>
       </c>
       <c r="F748" t="s">
-        <v>26</v>
-      </c>
-      <c r="G748" t="s">
-        <v>6</v>
+        <v>28</v>
+      </c>
+      <c r="G748" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H748" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="749" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="B749">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C749" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D749" t="s">
         <v>10</v>
       </c>
+      <c r="E749" t="s">
+        <v>56</v>
+      </c>
       <c r="F749" t="s">
-        <v>28</v>
-      </c>
-      <c r="G749" s="2" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="H749" t="s">
-        <v>127</v>
-      </c>
-      <c r="I749">
-        <v>5</v>
-      </c>
-      <c r="J749" s="44">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="K749">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="L749">
-        <v>7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="750" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A750" t="s">
-        <v>128</v>
-      </c>
-      <c r="B750">
-        <v>5.0000000000000003E-10</v>
-      </c>
-      <c r="C750" t="s">
-        <v>12</v>
-      </c>
-      <c r="D750" t="s">
-        <v>9</v>
-      </c>
-      <c r="F750" t="s">
-        <v>28</v>
-      </c>
-      <c r="G750" t="s">
-        <v>29</v>
-      </c>
-      <c r="H750" t="s">
-        <v>30</v>
-      </c>
-      <c r="I750">
-        <v>5</v>
-      </c>
-      <c r="J750" s="39">
-        <v>5.0000000000000003E-10</v>
-      </c>
-      <c r="K750">
-        <v>4.0000000000000001E-10</v>
-      </c>
-      <c r="L750" s="39">
-        <v>6.6666666666666664E-10</v>
-      </c>
-    </row>
-    <row r="751" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A751" t="s">
-        <v>129</v>
-      </c>
-      <c r="B751">
-        <v>-5.0000000000000003E-10</v>
-      </c>
-      <c r="C751" t="s">
-        <v>12</v>
-      </c>
-      <c r="D751" t="s">
-        <v>9</v>
-      </c>
-      <c r="F751" t="s">
-        <v>28</v>
-      </c>
-      <c r="G751" t="s">
-        <v>29</v>
-      </c>
-      <c r="H751" t="s">
-        <v>32</v>
-      </c>
-      <c r="I751">
-        <v>5</v>
-      </c>
-      <c r="J751">
-        <v>-5.0000000000000003E-10</v>
-      </c>
-      <c r="K751">
-        <v>-6.6666666666666664E-10</v>
-      </c>
-      <c r="L751">
-        <v>-4.0000000000000001E-10</v>
-      </c>
-      <c r="M751" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="752" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A752" t="s">
-        <v>47</v>
-      </c>
-      <c r="B752">
-        <v>0.7</v>
-      </c>
-      <c r="C752" t="s">
-        <v>12</v>
-      </c>
-      <c r="D752" t="s">
-        <v>48</v>
-      </c>
-      <c r="F752" t="s">
-        <v>28</v>
-      </c>
-      <c r="G752" t="s">
-        <v>49</v>
-      </c>
-      <c r="H752" t="s">
-        <v>356</v>
-      </c>
-      <c r="I752">
-        <v>5</v>
-      </c>
-      <c r="J752">
-        <v>0.5</v>
-      </c>
-      <c r="K752">
-        <v>0.5</v>
-      </c>
-      <c r="L752">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="753" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A753" t="s">
-        <v>350</v>
-      </c>
-      <c r="B753">
-        <v>0.11018518518518521</v>
-      </c>
-      <c r="C753" t="s">
-        <v>12</v>
-      </c>
-      <c r="D753" t="s">
-        <v>10</v>
-      </c>
-      <c r="F753" t="s">
-        <v>28</v>
-      </c>
-      <c r="G753" t="s">
-        <v>351</v>
-      </c>
-      <c r="H753" t="s">
-        <v>357</v>
-      </c>
-      <c r="I753">
-        <v>5</v>
-      </c>
-      <c r="J753">
-        <v>0.05</v>
-      </c>
-      <c r="K753">
-        <v>0.05</v>
-      </c>
-      <c r="L753">
-        <v>0.11018518518518521</v>
-      </c>
-    </row>
-    <row r="754" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A754" t="s">
-        <v>55</v>
-      </c>
-      <c r="B754">
-        <v>1</v>
-      </c>
-      <c r="D754" t="s">
-        <v>10</v>
-      </c>
-      <c r="E754" t="s">
-        <v>56</v>
-      </c>
-      <c r="F754" t="s">
-        <v>57</v>
-      </c>
-      <c r="H754" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="756" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A756" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B756" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="757" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A757" t="s">
-        <v>4</v>
-      </c>
-      <c r="B757">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="758" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A758" t="s">
-        <v>5</v>
-      </c>
-      <c r="B758" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="759" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A759" t="s">
-        <v>7</v>
-      </c>
-      <c r="B759" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="760" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A760" t="s">
-        <v>9</v>
-      </c>
-      <c r="B760" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="761" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A761" t="s">
-        <v>11</v>
-      </c>
-      <c r="B761" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="762" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A762" t="s">
-        <v>13</v>
-      </c>
-      <c r="B762" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="763" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A763" t="s">
-        <v>15</v>
-      </c>
-      <c r="B763" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="764" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A764" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="765" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A765" t="s">
-        <v>18</v>
-      </c>
-      <c r="B765" t="s">
-        <v>19</v>
-      </c>
-      <c r="C765" t="s">
-        <v>11</v>
-      </c>
-      <c r="D765" t="s">
-        <v>9</v>
-      </c>
-      <c r="E765" t="s">
-        <v>20</v>
-      </c>
-      <c r="F765" t="s">
-        <v>7</v>
-      </c>
-      <c r="G765" t="s">
-        <v>5</v>
-      </c>
-      <c r="H765" t="s">
-        <v>13</v>
-      </c>
-      <c r="I765" t="s">
-        <v>21</v>
-      </c>
-      <c r="J765" t="s">
-        <v>22</v>
-      </c>
-      <c r="K765" t="s">
-        <v>23</v>
-      </c>
-      <c r="L765" t="s">
-        <v>24</v>
-      </c>
-      <c r="M765" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="766" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A766" t="s">
-        <v>358</v>
-      </c>
-      <c r="B766">
-        <v>1</v>
-      </c>
-      <c r="C766" t="s">
-        <v>12</v>
-      </c>
-      <c r="D766" t="s">
-        <v>10</v>
-      </c>
-      <c r="F766" t="s">
-        <v>26</v>
-      </c>
-      <c r="G766" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="767" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A767" t="s">
-        <v>125</v>
-      </c>
-      <c r="B767">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="C767" t="s">
-        <v>12</v>
-      </c>
-      <c r="D767" t="s">
-        <v>10</v>
-      </c>
-      <c r="F767" t="s">
-        <v>28</v>
-      </c>
-      <c r="G767" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H767" t="s">
-        <v>36</v>
-      </c>
-      <c r="I767">
-        <v>5</v>
-      </c>
-      <c r="J767">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="K767">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="L767">
-        <v>7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="768" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A768" t="s">
-        <v>128</v>
-      </c>
-      <c r="B768">
-        <v>5.0000000000000003E-10</v>
-      </c>
-      <c r="C768" t="s">
-        <v>12</v>
-      </c>
-      <c r="D768" t="s">
-        <v>9</v>
-      </c>
-      <c r="F768" t="s">
-        <v>28</v>
-      </c>
-      <c r="G768" t="s">
-        <v>29</v>
-      </c>
-      <c r="H768" t="s">
-        <v>30</v>
-      </c>
-      <c r="I768">
-        <v>5</v>
-      </c>
-      <c r="J768" s="39">
-        <v>5.0000000000000003E-10</v>
-      </c>
-      <c r="K768">
-        <v>4.0000000000000001E-10</v>
-      </c>
-      <c r="L768" s="39">
-        <v>6.6666666666666664E-10</v>
-      </c>
-    </row>
-    <row r="769" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A769" t="s">
-        <v>129</v>
-      </c>
-      <c r="B769">
-        <v>-5.0000000000000003E-10</v>
-      </c>
-      <c r="C769" t="s">
-        <v>12</v>
-      </c>
-      <c r="D769" t="s">
-        <v>9</v>
-      </c>
-      <c r="F769" t="s">
-        <v>28</v>
-      </c>
-      <c r="G769" t="s">
-        <v>29</v>
-      </c>
-      <c r="H769" t="s">
-        <v>32</v>
-      </c>
-      <c r="I769">
-        <v>5</v>
-      </c>
-      <c r="J769">
-        <v>-5.0000000000000003E-10</v>
-      </c>
-      <c r="K769">
-        <v>-6.6666666666666664E-10</v>
-      </c>
-      <c r="L769">
-        <v>-4.0000000000000001E-10</v>
-      </c>
-      <c r="M769" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="770" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A770" t="s">
-        <v>47</v>
-      </c>
-      <c r="B770">
-        <v>0.7</v>
-      </c>
-      <c r="C770" t="s">
-        <v>12</v>
-      </c>
-      <c r="D770" t="s">
-        <v>48</v>
-      </c>
-      <c r="F770" t="s">
-        <v>28</v>
-      </c>
-      <c r="G770" t="s">
-        <v>49</v>
-      </c>
-      <c r="H770" t="s">
-        <v>356</v>
-      </c>
-      <c r="I770">
-        <v>5</v>
-      </c>
-      <c r="J770">
-        <v>0.5</v>
-      </c>
-      <c r="K770">
-        <v>0.5</v>
-      </c>
-      <c r="L770">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="771" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A771" t="s">
-        <v>350</v>
-      </c>
-      <c r="B771">
-        <v>0.11018518518518521</v>
-      </c>
-      <c r="C771" t="s">
-        <v>12</v>
-      </c>
-      <c r="D771" t="s">
-        <v>10</v>
-      </c>
-      <c r="F771" t="s">
-        <v>28</v>
-      </c>
-      <c r="G771" t="s">
-        <v>351</v>
-      </c>
-      <c r="H771" t="s">
-        <v>357</v>
-      </c>
-      <c r="I771">
-        <v>5</v>
-      </c>
-      <c r="J771">
-        <v>0.05</v>
-      </c>
-      <c r="K771">
-        <v>0.05</v>
-      </c>
-      <c r="L771">
-        <v>0.11018518518518521</v>
-      </c>
-    </row>
-    <row r="772" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A772" t="s">
-        <v>60</v>
-      </c>
-      <c r="B772">
-        <v>1</v>
-      </c>
-      <c r="C772" t="s">
-        <v>12</v>
-      </c>
-      <c r="D772" t="s">
-        <v>10</v>
-      </c>
-      <c r="F772" t="s">
-        <v>28</v>
-      </c>
-      <c r="G772" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H772" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="773" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A773" t="s">
-        <v>55</v>
-      </c>
-      <c r="B773">
-        <v>1</v>
-      </c>
-      <c r="D773" t="s">
-        <v>10</v>
-      </c>
-      <c r="E773" t="s">
-        <v>56</v>
-      </c>
-      <c r="F773" t="s">
-        <v>57</v>
-      </c>
-      <c r="H773" t="s">
-        <v>58</v>
-      </c>
-    </row>
+    <row r="756" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:V610" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
